--- a/outputs/fortress_screener.xlsx
+++ b/outputs/fortress_screener.xlsx
@@ -1752,11 +1752,11 @@
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>55.6</v>
+        <v>57.8</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 55.6%</t>
+          <t>⚠️ MC survival 57.8%</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -1978,7 +1978,7 @@
         <v>1270</v>
       </c>
       <c r="D4" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E4" t="n">
         <v>200</v>
@@ -2006,7 +2006,7 @@
         <v>15</v>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="M4" t="n">
         <v>1279.08</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>Results just 1td ago — fresh data</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -2201,11 +2201,11 @@
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>59.8</v>
+        <v>62.2</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 59.8%</t>
+          <t>⚠️ MC survival 62.2%</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -2650,11 +2650,11 @@
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>33.2</v>
+        <v>32.6</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 33.2%</t>
+          <t>⚠️ MC survival 32.6%</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -3984,7 +3984,7 @@
         <v>2245.4</v>
       </c>
       <c r="D3" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E3" t="n">
         <v>200</v>
@@ -4012,7 +4012,7 @@
         <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M3" t="n">
         <v>2219.82</v>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Results in 60td — safe runway ✓</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -4207,11 +4207,11 @@
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>81</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>✅ MC survival 81.0% (500 sims, 20d)</t>
+          <t>✅ MC survival 83.6% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; clear of earnings risk; 2/3 fortress layers at vpoc floor; sector truth boost (1.15x)</t>
+          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor; sector truth boost (1.15x)</t>
         </is>
       </c>
       <c r="CF3" t="b">
@@ -4656,11 +4656,11 @@
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>57.2</v>
+        <v>54.2</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 57.2%</t>
+          <t>⚠️ MC survival 54.2%</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -5109,11 +5109,11 @@
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>55.6</v>
+        <v>57.8</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 55.6%</t>
+          <t>⚠️ MC survival 57.8%</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -5323,19 +5323,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>TATACHEM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1270</v>
+        <v>770.25</v>
       </c>
       <c r="D6" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E6" t="n">
         <v>200</v>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I6" t="n">
         <v>14</v>
@@ -5363,44 +5363,44 @@
         <v>15</v>
       </c>
       <c r="L6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M6" t="n">
-        <v>1279.08</v>
+        <v>765.9</v>
       </c>
       <c r="N6" t="n">
-        <v>1317.64</v>
+        <v>819.35</v>
       </c>
       <c r="O6" t="n">
-        <v>1214.41</v>
+        <v>724.42</v>
       </c>
       <c r="P6" t="n">
-        <v>1662.8</v>
+        <v>995.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>2046.53</v>
+        <v>1225.44</v>
       </c>
       <c r="R6" t="n">
-        <v>2558.16</v>
+        <v>1531.8</v>
       </c>
       <c r="S6" t="n">
-        <v>4.38</v>
+        <v>5.95</v>
       </c>
       <c r="T6" t="n">
-        <v>3.43</v>
+        <v>2.52</v>
       </c>
       <c r="U6" t="n">
-        <v>70.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>41.4</v>
+        <v>49.8</v>
       </c>
       <c r="W6" t="n">
-        <v>24.1</v>
+        <v>47.6</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>TRANSITION</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -5420,19 +5420,19 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>₹1253.49–₹1307.87</t>
+          <t>₹739.86–₹789.83</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ATR-1.75× stop</t>
+          <t>ATR-1.40× stop</t>
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.9</v>
+        <v>-4.99</v>
       </c>
       <c r="AF6" t="b">
         <v>1</v>
@@ -5444,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>248.66</v>
+        <v>193.58</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>Results in 52td — safe runway ✓</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -5489,22 +5489,22 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>52W: 8.0% from ₹1380 [NEAR 52W HIGH] +5pts</t>
+          <t>52W: 25.0% from ₹1027 [25% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>ATR-V: 17% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: -7% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="n">
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1214.41</v>
+        <v>724.42</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>Initial stop ₹1214.41</t>
+          <t>Initial stop ₹724.42</t>
         </is>
       </c>
       <c r="BF6" t="b">
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="BH6" t="n">
-        <v>170180</v>
+        <v>125550.75</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>134 shares · ₹170,180  (risk ₹7,500)</t>
+          <t>163 shares · ₹125,551  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ6" t="n">
@@ -5558,11 +5558,11 @@
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>59.8</v>
+        <v>54.4</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 59.8%</t>
+          <t>⚠️ MC survival 54.4%</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -5592,19 +5592,19 @@
       </c>
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.76</v>
+        <v>7.34</v>
       </c>
       <c r="CA6" t="n">
-        <v>31.76</v>
+        <v>32.73</v>
       </c>
       <c r="CB6" t="n">
-        <v>2966821</v>
+        <v>2871119</v>
       </c>
       <c r="CC6" t="n">
-        <v>1279.08</v>
+        <v>765.9</v>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor; sector truth boost (1.15x)</t>
+          <t>Recent filing: no recent filing; clear of earnings risk; 2/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CF6" t="b">
@@ -5648,24 +5648,24 @@
         <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.315</v>
+        <v>0.603</v>
       </c>
       <c r="CR6" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="CS6" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 32% — LOW</t>
+          <t>🧠 Sniper Bayes 60% — moderate</t>
         </is>
       </c>
       <c r="CU6" t="n">
         <v>62</v>
       </c>
       <c r="CV6" t="n">
-        <v>1342.6</v>
+        <v>831.36</v>
       </c>
       <c r="CW6" t="b">
         <v>0</v>
@@ -5674,23 +5674,23 @@
         <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>1214.41</v>
+        <v>724.42</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1214.41</v>
+        <v>724.42</v>
       </c>
       <c r="DA6" t="n">
-        <v>1662.8</v>
+        <v>995.67</v>
       </c>
       <c r="DB6" t="n">
-        <v>2046.53</v>
+        <v>1225.44</v>
       </c>
       <c r="DC6" t="n">
-        <v>2558.16</v>
+        <v>1531.8</v>
       </c>
       <c r="DD6" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹1279.08</t>
+          <t>Sell 30% | Move stop to T1 ₹765.90</t>
         </is>
       </c>
       <c r="DE6" t="inlineStr">
@@ -5704,11 +5704,11 @@
         </is>
       </c>
       <c r="DG6" t="n">
-        <v>-0.7</v>
+        <v>0.6</v>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>🔵 PROBE — SMALL BUY ₹1266.29</t>
+          <t>🔵 PROBE — SMALL BUY ₹758.24</t>
         </is>
       </c>
       <c r="DI6" t="inlineStr">
@@ -5720,7 +5720,7 @@
         <v>25</v>
       </c>
       <c r="DK6" t="n">
-        <v>1266.2892</v>
+        <v>758.241</v>
       </c>
       <c r="DL6" t="b">
         <v>0</v>
@@ -5738,21 +5738,21 @@
         <v>0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="DR6" t="n">
-        <v>33020</v>
+        <v>19256</v>
       </c>
       <c r="DS6" t="inlineStr">
         <is>
-          <t>26 sh | ₹33,020 | 25% deploy | Risk ₹1,652</t>
+          <t>25 sh | ₹19,256 | 25% deploy | Risk ₹1,636</t>
         </is>
       </c>
       <c r="DT6" t="n">
         <v>0.33</v>
       </c>
       <c r="DU6" t="n">
-        <v>63.52</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="DV6" t="inlineStr">
         <is>
@@ -5772,35 +5772,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>770.25</v>
+        <v>1270</v>
       </c>
       <c r="D7" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E7" t="n">
         <v>200</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟠 MODERATE</t>
+          <t>🟡 HIGH</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>QTR 25%</t>
+          <t>HALF 50%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I7" t="n">
         <v>14</v>
@@ -5812,44 +5812,44 @@
         <v>15</v>
       </c>
       <c r="L7" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="M7" t="n">
-        <v>765.9</v>
+        <v>1279.08</v>
       </c>
       <c r="N7" t="n">
-        <v>819.35</v>
+        <v>1317.64</v>
       </c>
       <c r="O7" t="n">
-        <v>724.42</v>
+        <v>1214.41</v>
       </c>
       <c r="P7" t="n">
-        <v>995.67</v>
+        <v>1662.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>1225.44</v>
+        <v>2046.53</v>
       </c>
       <c r="R7" t="n">
-        <v>1531.8</v>
+        <v>2558.16</v>
       </c>
       <c r="S7" t="n">
-        <v>5.95</v>
+        <v>4.38</v>
       </c>
       <c r="T7" t="n">
-        <v>2.52</v>
+        <v>3.43</v>
       </c>
       <c r="U7" t="n">
-        <v>82.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>49.8</v>
+        <v>41.4</v>
       </c>
       <c r="W7" t="n">
-        <v>47.6</v>
+        <v>24.1</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>TRANSITION</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -5869,19 +5869,19 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>₹739.86–₹789.83</t>
+          <t>₹1253.49–₹1307.87</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ATR-1.40× stop</t>
+          <t>ATR-1.75× stop</t>
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AE7" t="n">
-        <v>-4.99</v>
+        <v>0.9</v>
       </c>
       <c r="AF7" t="b">
         <v>1</v>
@@ -5893,7 +5893,7 @@
         <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>193.58</v>
+        <v>248.66</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>Results just 1td ago — fresh data</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>52W: 25.0% from ₹1027 [25% from 52W high] +0pts</t>
+          <t>52W: 8.0% from ₹1380 [NEAR 52W HIGH] +5pts</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>ATR-V: -7% compressed [EXPANDING]</t>
+          <t>ATR-V: 17% compressed [🌀 COILING (+4pts)]</t>
         </is>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="n">
@@ -5974,25 +5974,25 @@
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>724.42</v>
+        <v>1214.41</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>Initial stop ₹724.42</t>
+          <t>Initial stop ₹1214.41</t>
         </is>
       </c>
       <c r="BF7" t="b">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="BH7" t="n">
-        <v>125550.75</v>
+        <v>170180</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>163 shares · ₹125,551  (risk ₹7,500)</t>
+          <t>134 shares · ₹170,180  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ7" t="n">
@@ -6007,11 +6007,11 @@
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>54.4</v>
+        <v>62.2</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 54.4%</t>
+          <t>⚠️ MC survival 62.2%</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -6041,19 +6041,19 @@
       </c>
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ7" t="n">
-        <v>7.34</v>
+        <v>2.76</v>
       </c>
       <c r="CA7" t="n">
-        <v>32.73</v>
+        <v>31.76</v>
       </c>
       <c r="CB7" t="n">
-        <v>2871119</v>
+        <v>2966821</v>
       </c>
       <c r="CC7" t="n">
-        <v>765.9</v>
+        <v>1279.08</v>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor</t>
+          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor; sector truth boost (1.15x)</t>
         </is>
       </c>
       <c r="CF7" t="b">
@@ -6097,24 +6097,24 @@
         <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.603</v>
+        <v>0.315</v>
       </c>
       <c r="CR7" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="CS7" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 60% — moderate</t>
+          <t>🧠 Sniper Bayes 32% — LOW</t>
         </is>
       </c>
       <c r="CU7" t="n">
         <v>62</v>
       </c>
       <c r="CV7" t="n">
-        <v>831.36</v>
+        <v>1342.6</v>
       </c>
       <c r="CW7" t="b">
         <v>0</v>
@@ -6123,23 +6123,23 @@
         <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>724.42</v>
+        <v>1214.41</v>
       </c>
       <c r="CZ7" t="n">
-        <v>724.42</v>
+        <v>1214.41</v>
       </c>
       <c r="DA7" t="n">
-        <v>995.67</v>
+        <v>1662.8</v>
       </c>
       <c r="DB7" t="n">
-        <v>1225.44</v>
+        <v>2046.53</v>
       </c>
       <c r="DC7" t="n">
-        <v>1531.8</v>
+        <v>2558.16</v>
       </c>
       <c r="DD7" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹765.90</t>
+          <t>Sell 30% | Move stop to T1 ₹1279.08</t>
         </is>
       </c>
       <c r="DE7" t="inlineStr">
@@ -6153,11 +6153,11 @@
         </is>
       </c>
       <c r="DG7" t="n">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
-          <t>🔵 PROBE — SMALL BUY ₹758.24</t>
+          <t>🔵 PROBE — SMALL BUY ₹1266.29</t>
         </is>
       </c>
       <c r="DI7" t="inlineStr">
@@ -6169,7 +6169,7 @@
         <v>25</v>
       </c>
       <c r="DK7" t="n">
-        <v>758.241</v>
+        <v>1266.2892</v>
       </c>
       <c r="DL7" t="b">
         <v>0</v>
@@ -6187,21 +6187,21 @@
         <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DR7" t="n">
-        <v>19256</v>
+        <v>33020</v>
       </c>
       <c r="DS7" t="inlineStr">
         <is>
-          <t>25 sh | ₹19,256 | 25% deploy | Risk ₹1,636</t>
+          <t>26 sh | ₹33,020 | 25% deploy | Risk ₹1,652</t>
         </is>
       </c>
       <c r="DT7" t="n">
         <v>0.33</v>
       </c>
       <c r="DU7" t="n">
-        <v>65.45999999999999</v>
+        <v>63.52</v>
       </c>
       <c r="DV7" t="inlineStr">
         <is>
@@ -6456,11 +6456,11 @@
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>65.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 65.6%</t>
+          <t>⚠️ MC survival 64.8%</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -6909,11 +6909,11 @@
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>38.2</v>
+        <v>31.6</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 38.2%</t>
+          <t>⚠️ MC survival 31.6%</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>Results 57td ago</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -7362,11 +7362,11 @@
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>61.6</v>
+        <v>61.8</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 61.6%</t>
+          <t>⚠️ MC survival 61.8%</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -7811,11 +7811,11 @@
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>51.4</v>
+        <v>57.6</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 51.4%</t>
+          <t>⚠️ MC survival 57.6%</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
@@ -8258,11 +8258,11 @@
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>72.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>✅ MC survival 72.4% (500 sims, 20d)</t>
+          <t>✅ MC survival 76.0% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
@@ -8709,11 +8709,11 @@
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>83.2</v>
+        <v>83.8</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>✅ MC survival 83.2% (500 sims, 20d)</t>
+          <t>✅ MC survival 83.8% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
@@ -9156,11 +9156,11 @@
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>29.2</v>
+        <v>25</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 29.2%</t>
+          <t>⚠️ MC survival 25.0%</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
@@ -9609,11 +9609,11 @@
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>45</v>
+        <v>45.4</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 45.0%</t>
+          <t>⚠️ MC survival 45.4%</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
@@ -10056,11 +10056,11 @@
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 46.0%</t>
+          <t>⚠️ MC survival 45.0%</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
@@ -10272,7 +10272,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -10281,10 +10281,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>166.34</v>
+        <v>418.4</v>
       </c>
       <c r="D17" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E17" t="n">
         <v>200</v>
@@ -10300,7 +10300,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I17" t="n">
         <v>14</v>
@@ -10312,40 +10312,40 @@
         <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="M17" t="n">
-        <v>160.38</v>
+        <v>388.33</v>
       </c>
       <c r="N17" t="n">
-        <v>177.78</v>
+        <v>433.58</v>
       </c>
       <c r="O17" t="n">
-        <v>158.71</v>
+        <v>404.23</v>
       </c>
       <c r="P17" t="n">
-        <v>208.49</v>
+        <v>504.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>256.61</v>
+        <v>621.33</v>
       </c>
       <c r="R17" t="n">
-        <v>320.76</v>
+        <v>776.66</v>
       </c>
       <c r="S17" t="n">
-        <v>4.59</v>
+        <v>3.39</v>
       </c>
       <c r="T17" t="n">
-        <v>3.27</v>
+        <v>4.43</v>
       </c>
       <c r="U17" t="n">
-        <v>62.3</v>
+        <v>45.4</v>
       </c>
       <c r="V17" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="W17" t="n">
-        <v>51.4</v>
+        <v>26.2</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>DISTRIBUTION 🔴</t>
+          <t>NEUTRAL ↔</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -10369,19 +10369,19 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>₹154.50–₹165.66</t>
+          <t>₹380.81–₹396.91</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ATR-1.00× stop</t>
+          <t>ATR-1.40× stop</t>
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.22</v>
+        <v>7.28</v>
       </c>
       <c r="AF17" t="b">
         <v>0</v>
@@ -10393,7 +10393,7 @@
         <v>1</v>
       </c>
       <c r="AI17" t="n">
-        <v>8.16</v>
+        <v>288.38</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>Results just 1td ago — fresh data</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -10438,22 +10438,22 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>52W: 21.2% from ₹211 [21% from 52W high] +0pts</t>
+          <t>52W: 10.0% from ₹465 [APPROACHING HIGH] +3pts</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>ATR-V: -19% compressed [EXPANDING]</t>
+          <t>ATR-V: 4% compressed [🌀 COILING (+4pts)]</t>
         </is>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX17" t="inlineStr"/>
       <c r="AY17" t="n">
@@ -10474,25 +10474,25 @@
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>158.71</v>
+        <v>404.23</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>Initial stop ₹158.71</t>
+          <t>Initial stop ₹404.23</t>
         </is>
       </c>
       <c r="BF17" t="b">
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>982</v>
+        <v>529</v>
       </c>
       <c r="BH17" t="n">
-        <v>163345.88</v>
+        <v>221333.6</v>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>982 shares · ₹163,346  (risk ₹7,500)</t>
+          <t>529 shares · ₹221,334  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ17" t="n">
@@ -10507,11 +10507,11 @@
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>40.8</v>
+        <v>53.6</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 40.8%</t>
+          <t>⚠️ MC survival 53.6%</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
@@ -10544,20 +10544,20 @@
         <v>0</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-2.29</v>
+        <v>2.16</v>
       </c>
       <c r="CA17" t="n">
-        <v>7.63</v>
+        <v>10.12</v>
       </c>
       <c r="CB17" t="n">
-        <v>954619</v>
+        <v>8219980</v>
       </c>
       <c r="CC17" t="n">
-        <v>160.38</v>
+        <v>388.33</v>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>Smallcap circuit breaker: data unavailable (pass)</t>
+          <t>N/A (large-cap)</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>⚠️ ROUND_TRIP_RISK — close 166 &lt; 90% of 192</t>
+          <t>⚠️ ROUND_TRIP_RISK — close 418 &lt; 90% of 465</t>
         </is>
       </c>
       <c r="CH17" t="b">
@@ -10618,32 +10618,32 @@
         <v>55</v>
       </c>
       <c r="CV17" t="n">
-        <v>175.64</v>
+        <v>408.57</v>
       </c>
       <c r="CW17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX17" t="b">
         <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>158.71</v>
+        <v>404.23</v>
       </c>
       <c r="CZ17" t="n">
-        <v>158.71</v>
+        <v>404.23</v>
       </c>
       <c r="DA17" t="n">
-        <v>208.49</v>
+        <v>504.83</v>
       </c>
       <c r="DB17" t="n">
-        <v>256.61</v>
+        <v>621.33</v>
       </c>
       <c r="DC17" t="n">
-        <v>320.76</v>
+        <v>776.66</v>
       </c>
       <c r="DD17" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹160.38</t>
+          <t>Sell 30% | Move stop to T1 ₹388.33</t>
         </is>
       </c>
       <c r="DE17" t="inlineStr">
@@ -10657,11 +10657,11 @@
         </is>
       </c>
       <c r="DG17" t="n">
-        <v>3.7</v>
+        <v>7.7</v>
       </c>
       <c r="DH17" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 55/100 · +3.7% vs T1</t>
+          <t>👁️ WATCHING — score 55/100 · +7.7% vs T1</t>
         </is>
       </c>
       <c r="DI17" t="inlineStr">
@@ -10703,7 +10703,7 @@
         <v>0</v>
       </c>
       <c r="DU17" t="n">
-        <v>15.26</v>
+        <v>20.24</v>
       </c>
       <c r="DV17" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>NOCIL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -10732,10 +10732,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3574.4</v>
+        <v>166.34</v>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E18" t="n">
         <v>200</v>
@@ -10751,7 +10751,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I18" t="n">
         <v>14</v>
@@ -10766,37 +10766,37 @@
         <v>20</v>
       </c>
       <c r="M18" t="n">
-        <v>3261.39</v>
+        <v>160.38</v>
       </c>
       <c r="N18" t="n">
-        <v>3752.94</v>
+        <v>177.78</v>
       </c>
       <c r="O18" t="n">
-        <v>3366.1</v>
+        <v>158.71</v>
       </c>
       <c r="P18" t="n">
-        <v>4239.81</v>
+        <v>208.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>5218.22</v>
+        <v>256.61</v>
       </c>
       <c r="R18" t="n">
-        <v>6522.78</v>
+        <v>320.76</v>
       </c>
       <c r="S18" t="n">
-        <v>5.83</v>
+        <v>4.59</v>
       </c>
       <c r="T18" t="n">
-        <v>2.57</v>
+        <v>3.27</v>
       </c>
       <c r="U18" t="n">
-        <v>37.6</v>
+        <v>62.3</v>
       </c>
       <c r="V18" t="n">
-        <v>29.6</v>
+        <v>27.6</v>
       </c>
       <c r="W18" t="n">
-        <v>43.3</v>
+        <v>51.4</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>ACCUMULATION 🟢</t>
+          <t>DISTRIBUTION 🔴</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -10820,19 +10820,19 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>₹3174.51–₹3348.31</t>
+          <t>₹154.50–₹165.66</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ATR-1.75× stop</t>
+          <t>ATR-1.00× stop</t>
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
-        <v>11.47</v>
+        <v>0.22</v>
       </c>
       <c r="AF18" t="b">
         <v>0</v>
@@ -10844,7 +10844,7 @@
         <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>138.75</v>
+        <v>8.16</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -10889,22 +10889,22 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>52W: 9.0% from ₹3930 [NEAR 52W HIGH] +5pts</t>
+          <t>52W: 21.2% from ₹211 [21% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>ATR-V: -11% compressed [EXPANDING]</t>
+          <t>ATR-V: -19% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="inlineStr"/>
       <c r="AY18" t="n">
@@ -10925,25 +10925,25 @@
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>3366.1</v>
+        <v>158.71</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>Initial stop ₹3366.10</t>
+          <t>Initial stop ₹158.71</t>
         </is>
       </c>
       <c r="BF18" t="b">
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>36</v>
+        <v>982</v>
       </c>
       <c r="BH18" t="n">
-        <v>128678.4</v>
+        <v>163345.88</v>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>36 shares · ₹128,678  (risk ₹7,500)</t>
+          <t>982 shares · ₹163,346  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ18" t="n">
@@ -10958,11 +10958,11 @@
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>66.8</v>
+        <v>45</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 66.8%</t>
+          <t>⚠️ MC survival 45.0%</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
@@ -10995,20 +10995,20 @@
         <v>0</v>
       </c>
       <c r="BZ18" t="n">
-        <v>6.91</v>
+        <v>-2.29</v>
       </c>
       <c r="CA18" t="n">
-        <v>119.03</v>
+        <v>7.63</v>
       </c>
       <c r="CB18" t="n">
-        <v>589924</v>
+        <v>954619</v>
       </c>
       <c r="CC18" t="n">
-        <v>3261.39</v>
+        <v>160.38</v>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>N/A (large-cap)</t>
+          <t>Smallcap circuit breaker: data unavailable (pass)</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -11017,9 +11017,13 @@
         </is>
       </c>
       <c r="CF18" t="b">
-        <v>0</v>
-      </c>
-      <c r="CG18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
+          <t>⚠️ ROUND_TRIP_RISK — close 166 &lt; 90% of 192</t>
+        </is>
+      </c>
       <c r="CH18" t="b">
         <v>0</v>
       </c>
@@ -11048,49 +11052,49 @@
         <v>0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.449</v>
+        <v>0.132</v>
       </c>
       <c r="CR18" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="CS18" t="n">
         <v>-5</v>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 45% — LOW</t>
+          <t>🧠 Sniper Bayes 13% — LOW</t>
         </is>
       </c>
       <c r="CU18" t="n">
         <v>55</v>
       </c>
       <c r="CV18" t="n">
-        <v>3499.45</v>
+        <v>175.64</v>
       </c>
       <c r="CW18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX18" t="b">
         <v>0</v>
       </c>
       <c r="CY18" t="n">
-        <v>3366.1</v>
+        <v>158.71</v>
       </c>
       <c r="CZ18" t="n">
-        <v>3366.1</v>
+        <v>158.71</v>
       </c>
       <c r="DA18" t="n">
-        <v>4239.81</v>
+        <v>208.49</v>
       </c>
       <c r="DB18" t="n">
-        <v>5218.22</v>
+        <v>256.61</v>
       </c>
       <c r="DC18" t="n">
-        <v>6522.78</v>
+        <v>320.76</v>
       </c>
       <c r="DD18" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹3261.39</t>
+          <t>Sell 30% | Move stop to T1 ₹160.38</t>
         </is>
       </c>
       <c r="DE18" t="inlineStr">
@@ -11104,11 +11108,11 @@
         </is>
       </c>
       <c r="DG18" t="n">
-        <v>9.6</v>
+        <v>3.7</v>
       </c>
       <c r="DH18" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 55/100 · +9.6% vs T1</t>
+          <t>👁️ WATCHING — score 55/100 · +3.7% vs T1</t>
         </is>
       </c>
       <c r="DI18" t="inlineStr">
@@ -11150,7 +11154,7 @@
         <v>0</v>
       </c>
       <c r="DU18" t="n">
-        <v>238.06</v>
+        <v>15.26</v>
       </c>
       <c r="DV18" t="inlineStr">
         <is>
@@ -11170,7 +11174,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11179,10 +11183,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>418.4</v>
+        <v>3574.4</v>
       </c>
       <c r="D19" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E19" t="n">
         <v>200</v>
@@ -11198,7 +11202,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I19" t="n">
         <v>14</v>
@@ -11213,37 +11217,37 @@
         <v>20</v>
       </c>
       <c r="M19" t="n">
-        <v>388.33</v>
+        <v>3261.39</v>
       </c>
       <c r="N19" t="n">
-        <v>433.58</v>
+        <v>3752.94</v>
       </c>
       <c r="O19" t="n">
-        <v>404.23</v>
+        <v>3366.1</v>
       </c>
       <c r="P19" t="n">
-        <v>504.83</v>
+        <v>4239.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>621.33</v>
+        <v>5218.22</v>
       </c>
       <c r="R19" t="n">
-        <v>776.66</v>
+        <v>6522.78</v>
       </c>
       <c r="S19" t="n">
-        <v>3.39</v>
+        <v>5.83</v>
       </c>
       <c r="T19" t="n">
-        <v>4.43</v>
+        <v>2.57</v>
       </c>
       <c r="U19" t="n">
-        <v>45.4</v>
+        <v>37.6</v>
       </c>
       <c r="V19" t="n">
-        <v>27.5</v>
+        <v>29.6</v>
       </c>
       <c r="W19" t="n">
-        <v>26.2</v>
+        <v>43.3</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -11257,7 +11261,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>NEUTRAL ↔</t>
+          <t>ACCUMULATION 🟢</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -11267,19 +11271,19 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>₹380.81–₹396.91</t>
+          <t>₹3174.51–₹3348.31</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ATR-1.40× stop</t>
+          <t>ATR-1.75× stop</t>
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AE19" t="n">
-        <v>7.28</v>
+        <v>11.47</v>
       </c>
       <c r="AF19" t="b">
         <v>0</v>
@@ -11291,7 +11295,7 @@
         <v>1</v>
       </c>
       <c r="AI19" t="n">
-        <v>288.38</v>
+        <v>138.75</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -11336,22 +11340,22 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>52W: 10.0% from ₹465 [APPROACHING HIGH] +3pts</t>
+          <t>52W: 9.0% from ₹3930 [NEAR 52W HIGH] +5pts</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>ATR-V: 4% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: -11% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX19" t="inlineStr"/>
       <c r="AY19" t="n">
@@ -11372,25 +11376,25 @@
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>404.23</v>
+        <v>3366.1</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>Initial stop ₹404.23</t>
+          <t>Initial stop ₹3366.10</t>
         </is>
       </c>
       <c r="BF19" t="b">
         <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>529</v>
+        <v>36</v>
       </c>
       <c r="BH19" t="n">
-        <v>221333.6</v>
+        <v>128678.4</v>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>529 shares · ₹221,334  (risk ₹7,500)</t>
+          <t>36 shares · ₹128,678  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ19" t="n">
@@ -11405,11 +11409,11 @@
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>54.2</v>
+        <v>64</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 54.2%</t>
+          <t>⚠️ MC survival 64.0%</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
@@ -11442,16 +11446,16 @@
         <v>0</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.16</v>
+        <v>6.91</v>
       </c>
       <c r="CA19" t="n">
-        <v>10.12</v>
+        <v>119.03</v>
       </c>
       <c r="CB19" t="n">
-        <v>8219980</v>
+        <v>589924</v>
       </c>
       <c r="CC19" t="n">
-        <v>388.33</v>
+        <v>3261.39</v>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
@@ -11464,13 +11468,9 @@
         </is>
       </c>
       <c r="CF19" t="b">
-        <v>1</v>
-      </c>
-      <c r="CG19" t="inlineStr">
-        <is>
-          <t>⚠️ ROUND_TRIP_RISK — close 418 &lt; 90% of 465</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="CG19" t="inlineStr"/>
       <c r="CH19" t="b">
         <v>0</v>
       </c>
@@ -11499,24 +11499,24 @@
         <v>0</v>
       </c>
       <c r="CQ19" t="n">
-        <v>0.132</v>
+        <v>0.449</v>
       </c>
       <c r="CR19" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="CS19" t="n">
         <v>-5</v>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 13% — LOW</t>
+          <t>🧠 Sniper Bayes 45% — LOW</t>
         </is>
       </c>
       <c r="CU19" t="n">
         <v>55</v>
       </c>
       <c r="CV19" t="n">
-        <v>408.57</v>
+        <v>3499.45</v>
       </c>
       <c r="CW19" t="b">
         <v>1</v>
@@ -11525,23 +11525,23 @@
         <v>0</v>
       </c>
       <c r="CY19" t="n">
-        <v>404.23</v>
+        <v>3366.1</v>
       </c>
       <c r="CZ19" t="n">
-        <v>404.23</v>
+        <v>3366.1</v>
       </c>
       <c r="DA19" t="n">
-        <v>504.83</v>
+        <v>4239.81</v>
       </c>
       <c r="DB19" t="n">
-        <v>621.33</v>
+        <v>5218.22</v>
       </c>
       <c r="DC19" t="n">
-        <v>776.66</v>
+        <v>6522.78</v>
       </c>
       <c r="DD19" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹388.33</t>
+          <t>Sell 30% | Move stop to T1 ₹3261.39</t>
         </is>
       </c>
       <c r="DE19" t="inlineStr">
@@ -11555,11 +11555,11 @@
         </is>
       </c>
       <c r="DG19" t="n">
-        <v>7.7</v>
+        <v>9.6</v>
       </c>
       <c r="DH19" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 55/100 · +7.7% vs T1</t>
+          <t>👁️ WATCHING — score 55/100 · +9.6% vs T1</t>
         </is>
       </c>
       <c r="DI19" t="inlineStr">
@@ -11601,7 +11601,7 @@
         <v>0</v>
       </c>
       <c r="DU19" t="n">
-        <v>20.24</v>
+        <v>238.06</v>
       </c>
       <c r="DV19" t="inlineStr">
         <is>
@@ -11633,19 +11633,19 @@
         <v>1597.6</v>
       </c>
       <c r="D20" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E20" t="n">
         <v>200</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟠 MODERATE</t>
+          <t>🔵 PROBE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>QTR 25%</t>
+          <t>PROBE 10%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -11661,7 +11661,7 @@
         <v>15</v>
       </c>
       <c r="L20" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="M20" t="n">
         <v>1335.54</v>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>Results just 1td ago — fresh data</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -11856,11 +11856,11 @@
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>66.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 66.4%</t>
+          <t>✅ MC survival 72.0% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
@@ -12307,11 +12307,11 @@
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>60.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 60.2%</t>
+          <t>⚠️ MC survival 65.4%</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
@@ -12519,19 +12519,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1626.7</v>
+        <v>86.62</v>
       </c>
       <c r="D22" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E22" t="n">
         <v>200</v>
@@ -12547,7 +12547,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I22" t="n">
         <v>14</v>
@@ -12559,40 +12559,40 @@
         <v>15</v>
       </c>
       <c r="L22" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M22" t="n">
-        <v>1518.05</v>
+        <v>78.36</v>
       </c>
       <c r="N22" t="n">
-        <v>1704.31</v>
+        <v>89.78</v>
       </c>
       <c r="O22" t="n">
-        <v>1536.15</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>1973.46</v>
+        <v>101.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>2428.88</v>
+        <v>125.38</v>
       </c>
       <c r="R22" t="n">
-        <v>3036.1</v>
+        <v>156.72</v>
       </c>
       <c r="S22" t="n">
-        <v>5.57</v>
+        <v>1.82</v>
       </c>
       <c r="T22" t="n">
-        <v>2.69</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>35.4</v>
+        <v>57.7</v>
       </c>
       <c r="V22" t="n">
-        <v>36.5</v>
+        <v>35.8</v>
       </c>
       <c r="W22" t="n">
-        <v>20.3</v>
+        <v>22.8</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>ACCUMULATION 🟢</t>
+          <t>NEUTRAL ↔</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -12616,19 +12616,19 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>₹1479.42–₹1557.37</t>
+          <t>₹76.83–₹80.10</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ATR-1.75× stop</t>
+          <t>ATR-0.75× stop</t>
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.1</v>
+        <v>10.57</v>
       </c>
       <c r="AF22" t="b">
         <v>0</v>
@@ -12640,7 +12640,7 @@
         <v>1</v>
       </c>
       <c r="AI22" t="n">
-        <v>142.5</v>
+        <v>125.51</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>Results in 48td — safe runway ✓</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -12685,22 +12685,22 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>52W: 18.9% from ₹2005 [19% from 52W high] +0pts</t>
+          <t>52W: 6.6% from ₹93 [NEAR 52W HIGH] +5pts</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>ATR-V: -20% compressed [EXPANDING]</t>
+          <t>ATR-V: 14% compressed [🌀 COILING (+4pts)]</t>
         </is>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AX22" t="inlineStr"/>
       <c r="AY22" t="n">
@@ -12721,25 +12721,25 @@
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>1536.15</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>Initial stop ₹1536.15</t>
+          <t>Initial stop ₹85.04</t>
         </is>
       </c>
       <c r="BF22" t="b">
         <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>82</v>
+        <v>4739</v>
       </c>
       <c r="BH22" t="n">
-        <v>133389.4</v>
+        <v>410492.18</v>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>82 shares · ₹133,389  (risk ₹7,500)</t>
+          <t>4739 shares · ₹410,492  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ22" t="n">
@@ -12754,11 +12754,11 @@
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>61.4</v>
+        <v>32.6</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 61.4%</t>
+          <t>⚠️ MC survival 32.6%</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
@@ -12791,25 +12791,25 @@
         <v>1</v>
       </c>
       <c r="BZ22" t="n">
-        <v>-2.69</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CA22" t="n">
-        <v>51.74</v>
+        <v>2.11</v>
       </c>
       <c r="CB22" t="n">
-        <v>564006</v>
+        <v>23051741</v>
       </c>
       <c r="CC22" t="n">
-        <v>1518.05</v>
+        <v>78.36</v>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>N/A (large-cap)</t>
+          <t>Smallcap circuit breaker: data unavailable (pass)</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; clear of earnings risk</t>
+          <t>Recent filing: no recent filing</t>
         </is>
       </c>
       <c r="CF22" t="b">
@@ -12844,24 +12844,24 @@
         <v>0</v>
       </c>
       <c r="CQ22" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="CR22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="CS22" t="n">
         <v>-5</v>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 12% — LOW</t>
+          <t>🧠 Sniper Bayes 7% — LOW</t>
         </is>
       </c>
       <c r="CU22" t="n">
         <v>50</v>
       </c>
       <c r="CV22" t="n">
-        <v>1621.53</v>
+        <v>82.58</v>
       </c>
       <c r="CW22" t="b">
         <v>1</v>
@@ -12870,23 +12870,23 @@
         <v>0</v>
       </c>
       <c r="CY22" t="n">
-        <v>1536.15</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="CZ22" t="n">
-        <v>1536.15</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="DA22" t="n">
-        <v>1973.46</v>
+        <v>101.87</v>
       </c>
       <c r="DB22" t="n">
-        <v>2428.88</v>
+        <v>125.38</v>
       </c>
       <c r="DC22" t="n">
-        <v>3036.1</v>
+        <v>156.72</v>
       </c>
       <c r="DD22" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹1518.05</t>
+          <t>Sell 30% | Move stop to T1 ₹78.36</t>
         </is>
       </c>
       <c r="DE22" t="inlineStr">
@@ -12900,11 +12900,11 @@
         </is>
       </c>
       <c r="DG22" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="DH22" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 50/100 · +7.2% vs T1</t>
+          <t>👁️ WATCHING — score 50/100 · +10.5% vs T1</t>
         </is>
       </c>
       <c r="DI22" t="inlineStr">
@@ -12946,7 +12946,7 @@
         <v>0</v>
       </c>
       <c r="DU22" t="n">
-        <v>103.48</v>
+        <v>4.22</v>
       </c>
       <c r="DV22" t="inlineStr">
         <is>
@@ -12966,19 +12966,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>86.62</v>
+        <v>1626.7</v>
       </c>
       <c r="D23" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E23" t="n">
         <v>200</v>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I23" t="n">
         <v>14</v>
@@ -13009,37 +13009,37 @@
         <v>20</v>
       </c>
       <c r="M23" t="n">
-        <v>78.36</v>
+        <v>1518.05</v>
       </c>
       <c r="N23" t="n">
-        <v>89.78</v>
+        <v>1704.31</v>
       </c>
       <c r="O23" t="n">
-        <v>85.04000000000001</v>
+        <v>1536.15</v>
       </c>
       <c r="P23" t="n">
-        <v>101.87</v>
+        <v>1973.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>125.38</v>
+        <v>2428.88</v>
       </c>
       <c r="R23" t="n">
-        <v>156.72</v>
+        <v>3036.1</v>
       </c>
       <c r="S23" t="n">
-        <v>1.82</v>
+        <v>5.57</v>
       </c>
       <c r="T23" t="n">
-        <v>8.220000000000001</v>
+        <v>2.69</v>
       </c>
       <c r="U23" t="n">
-        <v>57.7</v>
+        <v>35.4</v>
       </c>
       <c r="V23" t="n">
-        <v>35.8</v>
+        <v>36.5</v>
       </c>
       <c r="W23" t="n">
-        <v>22.8</v>
+        <v>20.3</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>NEUTRAL ↔</t>
+          <t>ACCUMULATION 🟢</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -13063,40 +13063,40 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>₹76.83–₹80.10</t>
+          <t>₹1479.42–₹1557.37</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ATR-0.75× stop</t>
+          <t>ATR-1.75× stop</t>
         </is>
       </c>
       <c r="AD23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>MA200</t>
+        </is>
+      </c>
+      <c r="AK23" t="n">
         <v>0.75</v>
       </c>
-      <c r="AE23" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="AF23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>125.51</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>MA200</t>
-        </is>
-      </c>
-      <c r="AK23" t="n">
-        <v>0.85</v>
-      </c>
       <c r="AL23" t="inlineStr">
         <is>
           <t>↔ VIX stable (neutral flow)</t>
@@ -13132,22 +13132,22 @@
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>52W: 6.6% from ₹93 [NEAR 52W HIGH] +5pts</t>
+          <t>52W: 18.9% from ₹2005 [19% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>ATR-V: 14% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: -20% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="inlineStr"/>
       <c r="AY23" t="n">
@@ -13168,25 +13168,25 @@
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>85.04000000000001</v>
+        <v>1536.15</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>Initial stop ₹85.04</t>
+          <t>Initial stop ₹1536.15</t>
         </is>
       </c>
       <c r="BF23" t="b">
         <v>0</v>
       </c>
       <c r="BG23" t="n">
-        <v>4739</v>
+        <v>82</v>
       </c>
       <c r="BH23" t="n">
-        <v>410492.18</v>
+        <v>133389.4</v>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>4739 shares · ₹410,492  (risk ₹7,500)</t>
+          <t>82 shares · ₹133,389  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ23" t="n">
@@ -13201,11 +13201,11 @@
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>33.2</v>
+        <v>60.2</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 33.2%</t>
+          <t>⚠️ MC survival 60.2%</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
@@ -13238,20 +13238,20 @@
         <v>1</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0.9399999999999999</v>
+        <v>-2.69</v>
       </c>
       <c r="CA23" t="n">
-        <v>2.11</v>
+        <v>51.74</v>
       </c>
       <c r="CB23" t="n">
-        <v>23051741</v>
+        <v>564006</v>
       </c>
       <c r="CC23" t="n">
-        <v>78.36</v>
+        <v>1518.05</v>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>Smallcap circuit breaker: data unavailable (pass)</t>
+          <t>N/A (large-cap)</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -13291,24 +13291,24 @@
         <v>0</v>
       </c>
       <c r="CQ23" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="CR23" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CS23" t="n">
         <v>-5</v>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 7% — LOW</t>
+          <t>🧠 Sniper Bayes 12% — LOW</t>
         </is>
       </c>
       <c r="CU23" t="n">
         <v>50</v>
       </c>
       <c r="CV23" t="n">
-        <v>82.58</v>
+        <v>1621.53</v>
       </c>
       <c r="CW23" t="b">
         <v>1</v>
@@ -13317,23 +13317,23 @@
         <v>0</v>
       </c>
       <c r="CY23" t="n">
-        <v>85.04000000000001</v>
+        <v>1536.15</v>
       </c>
       <c r="CZ23" t="n">
-        <v>85.04000000000001</v>
+        <v>1536.15</v>
       </c>
       <c r="DA23" t="n">
-        <v>101.87</v>
+        <v>1973.46</v>
       </c>
       <c r="DB23" t="n">
-        <v>125.38</v>
+        <v>2428.88</v>
       </c>
       <c r="DC23" t="n">
-        <v>156.72</v>
+        <v>3036.1</v>
       </c>
       <c r="DD23" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹78.36</t>
+          <t>Sell 30% | Move stop to T1 ₹1518.05</t>
         </is>
       </c>
       <c r="DE23" t="inlineStr">
@@ -13347,11 +13347,11 @@
         </is>
       </c>
       <c r="DG23" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="DH23" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 50/100 · +10.5% vs T1</t>
+          <t>👁️ WATCHING — score 50/100 · +7.2% vs T1</t>
         </is>
       </c>
       <c r="DI23" t="inlineStr">
@@ -13393,7 +13393,7 @@
         <v>0</v>
       </c>
       <c r="DU23" t="n">
-        <v>4.22</v>
+        <v>103.48</v>
       </c>
       <c r="DV23" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -13422,10 +13422,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6851.5</v>
+        <v>124.26</v>
       </c>
       <c r="D24" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E24" t="n">
         <v>200</v>
@@ -13441,7 +13441,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I24" t="n">
         <v>14</v>
@@ -13453,40 +13453,40 @@
         <v>15</v>
       </c>
       <c r="L24" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M24" t="n">
-        <v>6328.62</v>
+        <v>117.49</v>
       </c>
       <c r="N24" t="n">
-        <v>7120.66</v>
+        <v>130.77</v>
       </c>
       <c r="O24" t="n">
-        <v>6537.48</v>
+        <v>119.92</v>
       </c>
       <c r="P24" t="n">
-        <v>8227.209999999999</v>
+        <v>152.74</v>
       </c>
       <c r="Q24" t="n">
-        <v>10125.79</v>
+        <v>187.98</v>
       </c>
       <c r="R24" t="n">
-        <v>12657.24</v>
+        <v>234.98</v>
       </c>
       <c r="S24" t="n">
-        <v>4.58</v>
+        <v>3.49</v>
       </c>
       <c r="T24" t="n">
-        <v>3.27</v>
+        <v>4.29</v>
       </c>
       <c r="U24" t="n">
-        <v>79.40000000000001</v>
+        <v>40.8</v>
       </c>
       <c r="V24" t="n">
-        <v>49.4</v>
+        <v>46.7</v>
       </c>
       <c r="W24" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>DISTRIBUTION 🔴</t>
+          <t>NEUTRAL ↔</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -13510,19 +13510,19 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>₹6196.02–₹6474.78</t>
+          <t>₹114.21–₹120.72</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ATR-1.75× stop</t>
+          <t>ATR-1.00× stop</t>
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
-        <v>9.4</v>
+        <v>10.55</v>
       </c>
       <c r="AF24" t="b">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>1</v>
       </c>
       <c r="AI24" t="n">
-        <v>39.6</v>
+        <v>258.71</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>Results in 47td — safe runway ✓</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -13579,22 +13579,22 @@
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>52W: 12.0% from ₹7788 [APPROACHING HIGH] +3pts</t>
+          <t>52W: 8.7% from ₹136 [NEAR 52W HIGH] +5pts</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>ATR-V: 12% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: -2% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX24" t="inlineStr"/>
       <c r="AY24" t="n">
@@ -13615,25 +13615,25 @@
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>6537.48</v>
+        <v>119.92</v>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>Initial stop ₹6537.48</t>
+          <t>Initial stop ₹119.92</t>
         </is>
       </c>
       <c r="BF24" t="b">
         <v>0</v>
       </c>
       <c r="BG24" t="n">
-        <v>23</v>
+        <v>1728</v>
       </c>
       <c r="BH24" t="n">
-        <v>157584.5</v>
+        <v>214721.28</v>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>23 shares · ₹157,584  (risk ₹7,500)</t>
+          <t>1728 shares · ₹214,721  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ24" t="n">
@@ -13648,19 +13648,23 @@
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>55.2</v>
+        <v>47.4</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 55.2%</t>
+          <t>⚠️ MC survival 47.4%</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="BP24" t="inlineStr"/>
+          <t>ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="BP24" t="inlineStr">
+        <is>
+          <t>🟢 CVD Accum — smart money</t>
+        </is>
+      </c>
       <c r="BQ24" t="b">
         <v>0</v>
       </c>
@@ -13682,28 +13686,28 @@
       </c>
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ24" t="n">
-        <v>8.609999999999999</v>
+        <v>4.32</v>
       </c>
       <c r="CA24" t="n">
-        <v>179.44</v>
+        <v>4.34</v>
       </c>
       <c r="CB24" t="n">
-        <v>48498</v>
+        <v>18810744</v>
       </c>
       <c r="CC24" t="n">
-        <v>6328.62</v>
+        <v>117.49</v>
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>N/A (large-cap)</t>
+          <t>Smallcap circuit breaker: data unavailable (pass)</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; clear of earnings risk</t>
+          <t>Recent filing: no recent filing</t>
         </is>
       </c>
       <c r="CF24" t="b">
@@ -13738,49 +13742,49 @@
         <v>0</v>
       </c>
       <c r="CQ24" t="n">
-        <v>0.241</v>
+        <v>0.525</v>
       </c>
       <c r="CR24" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="CS24" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 24% — LOW</t>
+          <t>🧠 Sniper Bayes 52% — neutral</t>
         </is>
       </c>
       <c r="CU24" t="n">
         <v>49</v>
       </c>
       <c r="CV24" t="n">
-        <v>6687.5</v>
+        <v>126.17</v>
       </c>
       <c r="CW24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX24" t="b">
         <v>0</v>
       </c>
       <c r="CY24" t="n">
-        <v>6537.48</v>
+        <v>119.92</v>
       </c>
       <c r="CZ24" t="n">
-        <v>6537.48</v>
+        <v>119.92</v>
       </c>
       <c r="DA24" t="n">
-        <v>8227.209999999999</v>
+        <v>152.74</v>
       </c>
       <c r="DB24" t="n">
-        <v>10125.79</v>
+        <v>187.98</v>
       </c>
       <c r="DC24" t="n">
-        <v>12657.24</v>
+        <v>234.98</v>
       </c>
       <c r="DD24" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹6328.62</t>
+          <t>Sell 30% | Move stop to T1 ₹117.49</t>
         </is>
       </c>
       <c r="DE24" t="inlineStr">
@@ -13794,11 +13798,11 @@
         </is>
       </c>
       <c r="DG24" t="n">
-        <v>8.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="DH24" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 49/100 · +8.3% vs T1</t>
+          <t>👁️ WATCHING — score 49/100 · +5.8% vs T1</t>
         </is>
       </c>
       <c r="DI24" t="inlineStr">
@@ -13840,7 +13844,7 @@
         <v>0</v>
       </c>
       <c r="DU24" t="n">
-        <v>358.88</v>
+        <v>8.68</v>
       </c>
       <c r="DV24" t="inlineStr">
         <is>
@@ -13860,7 +13864,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -13869,7 +13873,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>124.26</v>
+        <v>6851.5</v>
       </c>
       <c r="D25" t="n">
         <v>86</v>
@@ -13888,7 +13892,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I25" t="n">
         <v>14</v>
@@ -13900,40 +13904,40 @@
         <v>15</v>
       </c>
       <c r="L25" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="M25" t="n">
-        <v>117.49</v>
+        <v>6328.62</v>
       </c>
       <c r="N25" t="n">
-        <v>130.77</v>
+        <v>7120.66</v>
       </c>
       <c r="O25" t="n">
-        <v>119.92</v>
+        <v>6537.48</v>
       </c>
       <c r="P25" t="n">
-        <v>152.74</v>
+        <v>8227.209999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>187.98</v>
+        <v>10125.79</v>
       </c>
       <c r="R25" t="n">
-        <v>234.98</v>
+        <v>12657.24</v>
       </c>
       <c r="S25" t="n">
-        <v>3.49</v>
+        <v>4.58</v>
       </c>
       <c r="T25" t="n">
-        <v>4.29</v>
+        <v>3.27</v>
       </c>
       <c r="U25" t="n">
-        <v>40.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>46.7</v>
+        <v>49.4</v>
       </c>
       <c r="W25" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -13947,7 +13951,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>NEUTRAL ↔</t>
+          <t>DISTRIBUTION 🔴</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -13957,19 +13961,19 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>₹114.21–₹120.72</t>
+          <t>₹6196.02–₹6474.78</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ATR-1.00× stop</t>
+          <t>ATR-1.75× stop</t>
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AE25" t="n">
-        <v>10.55</v>
+        <v>9.4</v>
       </c>
       <c r="AF25" t="b">
         <v>0</v>
@@ -13981,7 +13985,7 @@
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>258.71</v>
+        <v>39.6</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -14013,7 +14017,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>Results in 7td — caution</t>
+          <t>Results in 47td — safe runway ✓</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -14026,22 +14030,22 @@
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>52W: 8.7% from ₹136 [NEAR 52W HIGH] +5pts</t>
+          <t>52W: 12.0% from ₹7788 [APPROACHING HIGH] +3pts</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>ATR-V: -2% compressed [EXPANDING]</t>
+          <t>ATR-V: 12% compressed [🌀 COILING (+4pts)]</t>
         </is>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX25" t="inlineStr"/>
       <c r="AY25" t="n">
@@ -14062,25 +14066,25 @@
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>119.92</v>
+        <v>6537.48</v>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>Initial stop ₹119.92</t>
+          <t>Initial stop ₹6537.48</t>
         </is>
       </c>
       <c r="BF25" t="b">
         <v>0</v>
       </c>
       <c r="BG25" t="n">
-        <v>1728</v>
+        <v>23</v>
       </c>
       <c r="BH25" t="n">
-        <v>214721.28</v>
+        <v>157584.5</v>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1728 shares · ₹214,721  (risk ₹7,500)</t>
+          <t>23 shares · ₹157,584  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ25" t="n">
@@ -14095,23 +14099,19 @@
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>43.8</v>
+        <v>56</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 43.8%</t>
+          <t>⚠️ MC survival 56.0%</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>ACCUMULATION</t>
-        </is>
-      </c>
-      <c r="BP25" t="inlineStr">
-        <is>
-          <t>🟢 CVD Accum — smart money</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="BP25" t="inlineStr"/>
       <c r="BQ25" t="b">
         <v>0</v>
       </c>
@@ -14133,28 +14133,28 @@
       </c>
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ25" t="n">
-        <v>4.32</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="CA25" t="n">
-        <v>4.34</v>
+        <v>179.44</v>
       </c>
       <c r="CB25" t="n">
-        <v>18810744</v>
+        <v>48498</v>
       </c>
       <c r="CC25" t="n">
-        <v>117.49</v>
+        <v>6328.62</v>
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>Smallcap circuit breaker: data unavailable (pass)</t>
+          <t>N/A (large-cap)</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing</t>
+          <t>Recent filing: no recent filing; clear of earnings risk</t>
         </is>
       </c>
       <c r="CF25" t="b">
@@ -14189,49 +14189,49 @@
         <v>0</v>
       </c>
       <c r="CQ25" t="n">
-        <v>0.525</v>
+        <v>0.241</v>
       </c>
       <c r="CR25" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="CS25" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 52% — neutral</t>
+          <t>🧠 Sniper Bayes 24% — LOW</t>
         </is>
       </c>
       <c r="CU25" t="n">
         <v>49</v>
       </c>
       <c r="CV25" t="n">
-        <v>126.17</v>
+        <v>6687.5</v>
       </c>
       <c r="CW25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX25" t="b">
         <v>0</v>
       </c>
       <c r="CY25" t="n">
-        <v>119.92</v>
+        <v>6537.48</v>
       </c>
       <c r="CZ25" t="n">
-        <v>119.92</v>
+        <v>6537.48</v>
       </c>
       <c r="DA25" t="n">
-        <v>152.74</v>
+        <v>8227.209999999999</v>
       </c>
       <c r="DB25" t="n">
-        <v>187.98</v>
+        <v>10125.79</v>
       </c>
       <c r="DC25" t="n">
-        <v>234.98</v>
+        <v>12657.24</v>
       </c>
       <c r="DD25" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹117.49</t>
+          <t>Sell 30% | Move stop to T1 ₹6328.62</t>
         </is>
       </c>
       <c r="DE25" t="inlineStr">
@@ -14245,11 +14245,11 @@
         </is>
       </c>
       <c r="DG25" t="n">
-        <v>5.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DH25" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 49/100 · +5.8% vs T1</t>
+          <t>👁️ WATCHING — score 49/100 · +8.3% vs T1</t>
         </is>
       </c>
       <c r="DI25" t="inlineStr">
@@ -14291,7 +14291,7 @@
         <v>0</v>
       </c>
       <c r="DU25" t="n">
-        <v>8.68</v>
+        <v>358.88</v>
       </c>
       <c r="DV25" t="inlineStr">
         <is>
@@ -14546,11 +14546,11 @@
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>60.2</v>
+        <v>56.4</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 60.2%</t>
+          <t>⚠️ MC survival 56.4%</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
@@ -14774,19 +14774,19 @@
         <v>5160</v>
       </c>
       <c r="D27" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E27" t="n">
         <v>200</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>🟠 MODERATE</t>
+          <t>🔵 PROBE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>QTR 25%</t>
+          <t>PROBE 10%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -14802,7 +14802,7 @@
         <v>15</v>
       </c>
       <c r="L27" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M27" t="n">
         <v>4578.42</v>
@@ -14915,7 +14915,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>Results in 12td — acceptable window</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -14997,11 +14997,11 @@
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>72.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>✅ MC survival 72.4% (500 sims, 20d)</t>
+          <t>✅ MC survival 74.8% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
@@ -15444,11 +15444,11 @@
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>37.6</v>
+        <v>31.8</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 37.6%</t>
+          <t>⚠️ MC survival 31.8%</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
@@ -15660,19 +15660,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2125.2</v>
+        <v>1252.3</v>
       </c>
       <c r="D29" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E29" t="n">
         <v>200</v>
@@ -15688,7 +15688,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I29" t="n">
         <v>14</v>
@@ -15703,41 +15703,41 @@
         <v>20</v>
       </c>
       <c r="M29" t="n">
-        <v>2169.06</v>
+        <v>1203.19</v>
       </c>
       <c r="N29" t="n">
-        <v>2200.89</v>
+        <v>1289.91</v>
       </c>
       <c r="O29" t="n">
-        <v>2036.89</v>
+        <v>1208.42</v>
       </c>
       <c r="P29" t="n">
-        <v>2819.78</v>
+        <v>1564.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>3470.5</v>
+        <v>1925.1</v>
       </c>
       <c r="R29" t="n">
-        <v>4338.12</v>
+        <v>2406.38</v>
       </c>
       <c r="S29" t="n">
-        <v>4.16</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>3.61</v>
+        <v>4.28</v>
       </c>
       <c r="U29" t="n">
-        <v>54.3</v>
+        <v>41.4</v>
       </c>
       <c r="V29" t="n">
-        <v>48.8</v>
+        <v>44.1</v>
       </c>
       <c r="W29" t="n">
-        <v>37.5</v>
+        <v>24.2</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>TRANSITION</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -15752,12 +15752,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>BELOW</t>
+          <t>ABOVE</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>₹2127.86–₹2216.50</t>
+          <t>₹1183.92–₹1227.27</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -15769,7 +15769,7 @@
         <v>1.75</v>
       </c>
       <c r="AE29" t="n">
-        <v>-1.92</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="AF29" t="b">
         <v>0</v>
@@ -15781,7 +15781,7 @@
         <v>1</v>
       </c>
       <c r="AI29" t="n">
-        <v>63.9</v>
+        <v>185.3</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         </is>
       </c>
       <c r="AK29" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
@@ -15826,22 +15826,22 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>52W: 15.6% from ₹2519 [16% from 52W high] +0pts</t>
+          <t>52W: 4.2% from ₹1307 [AT 52W HIGH] +9pts</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>ATR-V: 7% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: 19% compressed [🌀 COILING (+4pts)]</t>
         </is>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AX29" t="inlineStr"/>
       <c r="AY29" t="n">
@@ -15862,25 +15862,25 @@
         </is>
       </c>
       <c r="BD29" t="n">
-        <v>2036.89</v>
+        <v>1208.42</v>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>Initial stop ₹2036.89</t>
+          <t>Initial stop ₹1208.42</t>
         </is>
       </c>
       <c r="BF29" t="b">
         <v>0</v>
       </c>
       <c r="BG29" t="n">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="BH29" t="n">
-        <v>178516.8</v>
+        <v>212891</v>
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>84 shares · ₹178,517  (risk ₹7,500)</t>
+          <t>170 shares · ₹212,891  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ29" t="n">
@@ -15895,11 +15895,11 @@
         </is>
       </c>
       <c r="BM29" t="n">
-        <v>50.8</v>
+        <v>56.6</v>
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 50.8%</t>
+          <t>⚠️ MC survival 56.6%</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
@@ -15932,16 +15932,16 @@
         <v>0</v>
       </c>
       <c r="BZ29" t="n">
-        <v>10.92</v>
+        <v>3.99</v>
       </c>
       <c r="CA29" t="n">
-        <v>50.46</v>
+        <v>25.07</v>
       </c>
       <c r="CB29" t="n">
-        <v>478838</v>
+        <v>1815683</v>
       </c>
       <c r="CC29" t="n">
-        <v>2169.06</v>
+        <v>1203.19</v>
       </c>
       <c r="CD29" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="CL29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM29" t="b">
         <v>1</v>
@@ -15979,30 +15979,30 @@
         <v>0</v>
       </c>
       <c r="CO29" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="CP29" t="n">
         <v>0</v>
       </c>
       <c r="CQ29" t="n">
-        <v>0.241</v>
+        <v>0.12</v>
       </c>
       <c r="CR29" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="CS29" t="n">
         <v>-5</v>
       </c>
       <c r="CT29" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 24% — LOW</t>
+          <t>🧠 Sniper Bayes 12% — LOW</t>
         </is>
       </c>
       <c r="CU29" t="n">
         <v>44</v>
       </c>
       <c r="CV29" t="n">
-        <v>2269.98</v>
+        <v>1253.33</v>
       </c>
       <c r="CW29" t="b">
         <v>0</v>
@@ -16011,23 +16011,23 @@
         <v>0</v>
       </c>
       <c r="CY29" t="n">
-        <v>2036.89</v>
+        <v>1208.42</v>
       </c>
       <c r="CZ29" t="n">
-        <v>2036.89</v>
+        <v>1208.42</v>
       </c>
       <c r="DA29" t="n">
-        <v>2819.78</v>
+        <v>1564.15</v>
       </c>
       <c r="DB29" t="n">
-        <v>3470.5</v>
+        <v>1925.1</v>
       </c>
       <c r="DC29" t="n">
-        <v>4338.12</v>
+        <v>2406.38</v>
       </c>
       <c r="DD29" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹2169.06</t>
+          <t>Sell 30% | Move stop to T1 ₹1203.19</t>
         </is>
       </c>
       <c r="DE29" t="inlineStr">
@@ -16041,11 +16041,11 @@
         </is>
       </c>
       <c r="DG29" t="n">
-        <v>-2</v>
+        <v>4.1</v>
       </c>
       <c r="DH29" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 44/100 · -2.0% vs T1</t>
+          <t>👁️ WATCHING — score 44/100 · +4.1% vs T1</t>
         </is>
       </c>
       <c r="DI29" t="inlineStr">
@@ -16087,7 +16087,7 @@
         <v>0</v>
       </c>
       <c r="DU29" t="n">
-        <v>100.92</v>
+        <v>50.14</v>
       </c>
       <c r="DV29" t="inlineStr">
         <is>
@@ -16107,19 +16107,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1252.3</v>
+        <v>2125.2</v>
       </c>
       <c r="D30" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E30" t="n">
         <v>200</v>
@@ -16135,7 +16135,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I30" t="n">
         <v>14</v>
@@ -16147,44 +16147,44 @@
         <v>15</v>
       </c>
       <c r="L30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M30" t="n">
-        <v>1203.19</v>
+        <v>2169.06</v>
       </c>
       <c r="N30" t="n">
-        <v>1289.91</v>
+        <v>2200.89</v>
       </c>
       <c r="O30" t="n">
-        <v>1208.42</v>
+        <v>2036.89</v>
       </c>
       <c r="P30" t="n">
-        <v>1564.15</v>
+        <v>2819.78</v>
       </c>
       <c r="Q30" t="n">
-        <v>1925.1</v>
+        <v>3470.5</v>
       </c>
       <c r="R30" t="n">
-        <v>2406.38</v>
+        <v>4338.12</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>4.16</v>
       </c>
       <c r="T30" t="n">
-        <v>4.28</v>
+        <v>3.61</v>
       </c>
       <c r="U30" t="n">
-        <v>41.4</v>
+        <v>54.3</v>
       </c>
       <c r="V30" t="n">
-        <v>44.1</v>
+        <v>48.8</v>
       </c>
       <c r="W30" t="n">
-        <v>24.2</v>
+        <v>37.5</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>TRANSITION</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -16199,12 +16199,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>ABOVE</t>
+          <t>BELOW</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>₹1183.92–₹1227.27</t>
+          <t>₹2127.86–₹2216.50</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -16216,7 +16216,7 @@
         <v>1.75</v>
       </c>
       <c r="AE30" t="n">
-        <v>8.210000000000001</v>
+        <v>-1.92</v>
       </c>
       <c r="AF30" t="b">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>1</v>
       </c>
       <c r="AI30" t="n">
-        <v>185.3</v>
+        <v>63.9</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         </is>
       </c>
       <c r="AK30" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>⚠️ Results in 3td — risky, size to PROBE</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -16273,22 +16273,22 @@
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>52W: 4.2% from ₹1307 [AT 52W HIGH] +9pts</t>
+          <t>52W: 15.6% from ₹2519 [16% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>ATR-V: 19% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: 7% compressed [🌀 COILING (+4pts)]</t>
         </is>
       </c>
       <c r="AV30" t="n">
         <v>4</v>
       </c>
       <c r="AW30" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AX30" t="inlineStr"/>
       <c r="AY30" t="n">
@@ -16309,25 +16309,25 @@
         </is>
       </c>
       <c r="BD30" t="n">
-        <v>1208.42</v>
+        <v>2036.89</v>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>Initial stop ₹1208.42</t>
+          <t>Initial stop ₹2036.89</t>
         </is>
       </c>
       <c r="BF30" t="b">
         <v>0</v>
       </c>
       <c r="BG30" t="n">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="BH30" t="n">
-        <v>212891</v>
+        <v>178516.8</v>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>170 shares · ₹212,891  (risk ₹7,500)</t>
+          <t>84 shares · ₹178,517  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ30" t="n">
@@ -16342,11 +16342,11 @@
         </is>
       </c>
       <c r="BM30" t="n">
-        <v>62</v>
+        <v>48.8</v>
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 62.0%</t>
+          <t>⚠️ MC survival 48.8%</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
@@ -16379,16 +16379,16 @@
         <v>0</v>
       </c>
       <c r="BZ30" t="n">
-        <v>3.99</v>
+        <v>10.92</v>
       </c>
       <c r="CA30" t="n">
-        <v>25.07</v>
+        <v>50.46</v>
       </c>
       <c r="CB30" t="n">
-        <v>1815683</v>
+        <v>478838</v>
       </c>
       <c r="CC30" t="n">
-        <v>1203.19</v>
+        <v>2169.06</v>
       </c>
       <c r="CD30" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>0</v>
       </c>
       <c r="CL30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM30" t="b">
         <v>1</v>
@@ -16426,30 +16426,30 @@
         <v>0</v>
       </c>
       <c r="CO30" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="CP30" t="n">
         <v>0</v>
       </c>
       <c r="CQ30" t="n">
-        <v>0.12</v>
+        <v>0.241</v>
       </c>
       <c r="CR30" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="CS30" t="n">
         <v>-5</v>
       </c>
       <c r="CT30" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 12% — LOW</t>
+          <t>🧠 Sniper Bayes 24% — LOW</t>
         </is>
       </c>
       <c r="CU30" t="n">
         <v>44</v>
       </c>
       <c r="CV30" t="n">
-        <v>1253.33</v>
+        <v>2269.98</v>
       </c>
       <c r="CW30" t="b">
         <v>0</v>
@@ -16458,23 +16458,23 @@
         <v>0</v>
       </c>
       <c r="CY30" t="n">
-        <v>1208.42</v>
+        <v>2036.89</v>
       </c>
       <c r="CZ30" t="n">
-        <v>1208.42</v>
+        <v>2036.89</v>
       </c>
       <c r="DA30" t="n">
-        <v>1564.15</v>
+        <v>2819.78</v>
       </c>
       <c r="DB30" t="n">
-        <v>1925.1</v>
+        <v>3470.5</v>
       </c>
       <c r="DC30" t="n">
-        <v>2406.38</v>
+        <v>4338.12</v>
       </c>
       <c r="DD30" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹1203.19</t>
+          <t>Sell 30% | Move stop to T1 ₹2169.06</t>
         </is>
       </c>
       <c r="DE30" t="inlineStr">
@@ -16488,11 +16488,11 @@
         </is>
       </c>
       <c r="DG30" t="n">
-        <v>4.1</v>
+        <v>-2</v>
       </c>
       <c r="DH30" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 44/100 · +4.1% vs T1</t>
+          <t>👁️ WATCHING — score 44/100 · -2.0% vs T1</t>
         </is>
       </c>
       <c r="DI30" t="inlineStr">
@@ -16534,7 +16534,7 @@
         <v>0</v>
       </c>
       <c r="DU30" t="n">
-        <v>50.14</v>
+        <v>100.92</v>
       </c>
       <c r="DV30" t="inlineStr">
         <is>
@@ -16789,11 +16789,11 @@
         </is>
       </c>
       <c r="BM31" t="n">
-        <v>33.6</v>
+        <v>36</v>
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 33.6%</t>
+          <t>⚠️ MC survival 36.0%</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr">
@@ -17236,11 +17236,11 @@
         </is>
       </c>
       <c r="BM32" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="BN32" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 49.0%</t>
+          <t>⚠️ MC survival 53.0%</t>
         </is>
       </c>
       <c r="BO32" t="inlineStr">
@@ -17464,7 +17464,7 @@
         <v>2505.5</v>
       </c>
       <c r="D33" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E33" t="n">
         <v>200</v>
@@ -17492,7 +17492,7 @@
         <v>15</v>
       </c>
       <c r="L33" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M33" t="n">
         <v>2428.4</v>
@@ -17605,7 +17605,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>Results in 13td — acceptable window</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -17687,11 +17687,11 @@
         </is>
       </c>
       <c r="BM33" t="n">
-        <v>58.2</v>
+        <v>64.2</v>
       </c>
       <c r="BN33" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 58.2%</t>
+          <t>⚠️ MC survival 64.2%</t>
         </is>
       </c>
       <c r="BO33" t="inlineStr">
@@ -17911,19 +17911,19 @@
         <v>4381.9</v>
       </c>
       <c r="D34" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E34" t="n">
         <v>200</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>🔵 PROBE</t>
+          <t>🟠 MODERATE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PROBE 10%</t>
+          <t>QTR 25%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -17939,7 +17939,7 @@
         <v>15</v>
       </c>
       <c r="L34" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M34" t="n">
         <v>4070.89</v>
@@ -18052,7 +18052,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>Results in 9td — caution</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -18134,11 +18134,11 @@
         </is>
       </c>
       <c r="BM34" t="n">
-        <v>75</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="BN34" t="inlineStr">
         <is>
-          <t>✅ MC survival 75.0% (500 sims, 20d)</t>
+          <t>✅ MC survival 75.4% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO34" t="inlineStr">
@@ -18581,11 +18581,11 @@
         </is>
       </c>
       <c r="BM35" t="n">
-        <v>57.2</v>
+        <v>54</v>
       </c>
       <c r="BN35" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 57.2%</t>
+          <t>⚠️ MC survival 54.0%</t>
         </is>
       </c>
       <c r="BO35" t="inlineStr">
@@ -18805,7 +18805,7 @@
         <v>2257.1</v>
       </c>
       <c r="D36" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E36" t="n">
         <v>200</v>
@@ -18833,7 +18833,7 @@
         <v>15</v>
       </c>
       <c r="L36" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M36" t="n">
         <v>1996.23</v>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>Results in 6td — caution</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -19028,11 +19028,11 @@
         </is>
       </c>
       <c r="BM36" t="n">
-        <v>71.8</v>
+        <v>73</v>
       </c>
       <c r="BN36" t="inlineStr">
         <is>
-          <t>✅ MC survival 71.8% (500 sims, 20d)</t>
+          <t>✅ MC survival 73.0% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO36" t="inlineStr">
@@ -19475,11 +19475,11 @@
         </is>
       </c>
       <c r="BM37" t="n">
-        <v>61</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="BN37" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 61.0%</t>
+          <t>⚠️ MC survival 66.6%</t>
         </is>
       </c>
       <c r="BO37" t="inlineStr">
@@ -19687,7 +19687,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>ENDURANCE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -19696,10 +19696,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1253</v>
+        <v>2578.8</v>
       </c>
       <c r="D38" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E38" t="n">
         <v>200</v>
@@ -19715,7 +19715,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="I38" t="n">
         <v>14</v>
@@ -19727,40 +19727,40 @@
         <v>15</v>
       </c>
       <c r="L38" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M38" t="n">
-        <v>1161.48</v>
+        <v>2498.17</v>
       </c>
       <c r="N38" t="n">
-        <v>1308.06</v>
+        <v>2729.42</v>
       </c>
       <c r="O38" t="n">
-        <v>1188.76</v>
+        <v>2403.08</v>
       </c>
       <c r="P38" t="n">
-        <v>1509.92</v>
+        <v>3247.62</v>
       </c>
       <c r="Q38" t="n">
-        <v>1858.37</v>
+        <v>3997.07</v>
       </c>
       <c r="R38" t="n">
-        <v>2322.96</v>
+        <v>4996.34</v>
       </c>
       <c r="S38" t="n">
-        <v>5.13</v>
+        <v>6.81</v>
       </c>
       <c r="T38" t="n">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>77.5</v>
+        <v>71.7</v>
       </c>
       <c r="V38" t="n">
-        <v>76.3</v>
+        <v>71.2</v>
       </c>
       <c r="W38" t="n">
-        <v>51</v>
+        <v>44.4</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>₹1134.26–₹1190.11</t>
+          <t>₹2420.35–₹2571.79</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -19796,7 +19796,7 @@
         <v>1.75</v>
       </c>
       <c r="AE38" t="n">
-        <v>10.78</v>
+        <v>-1.44</v>
       </c>
       <c r="AF38" t="b">
         <v>0</v>
@@ -19808,7 +19808,7 @@
         <v>1</v>
       </c>
       <c r="AI38" t="n">
-        <v>424.59</v>
+        <v>53.42</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>Results in 51td — safe runway ✓</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -19853,22 +19853,22 @@
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>52W: 2.3% from ₹1283 [AT 52W HIGH] +9pts</t>
+          <t>52W: 16.3% from ₹3080 [16% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>ATR-V: -45% compressed [EXPANDING]</t>
+          <t>ATR-V: -32% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV38" t="n">
         <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="inlineStr"/>
       <c r="AY38" t="n">
@@ -19889,25 +19889,25 @@
         </is>
       </c>
       <c r="BD38" t="n">
-        <v>1188.76</v>
+        <v>2403.08</v>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>Initial stop ₹1188.76</t>
+          <t>Initial stop ₹2403.08</t>
         </is>
       </c>
       <c r="BF38" t="b">
         <v>0</v>
       </c>
       <c r="BG38" t="n">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="BH38" t="n">
-        <v>145348</v>
+        <v>108309.6</v>
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>116 shares · ₹145,348  (risk ₹7,500)</t>
+          <t>42 shares · ₹108,310  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ38" t="n">
@@ -19922,11 +19922,11 @@
         </is>
       </c>
       <c r="BM38" t="n">
-        <v>71.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="BN38" t="inlineStr">
         <is>
-          <t>✅ MC survival 71.4% (500 sims, 20d)</t>
+          <t>⚠️ MC survival 59.8%</t>
         </is>
       </c>
       <c r="BO38" t="inlineStr">
@@ -19959,16 +19959,16 @@
         <v>1</v>
       </c>
       <c r="BZ38" t="n">
-        <v>14.92</v>
+        <v>7.82</v>
       </c>
       <c r="CA38" t="n">
-        <v>36.71</v>
+        <v>100.41</v>
       </c>
       <c r="CB38" t="n">
-        <v>2525362</v>
+        <v>135794</v>
       </c>
       <c r="CC38" t="n">
-        <v>1161.48</v>
+        <v>2498.17</v>
       </c>
       <c r="CD38" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="CE38" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; clear of earnings risk; 2/3 fortress layers at vpoc floor</t>
+          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CF38" t="b">
@@ -20029,32 +20029,32 @@
         <v>39</v>
       </c>
       <c r="CV38" t="n">
-        <v>1234.9</v>
+        <v>2698.99</v>
       </c>
       <c r="CW38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX38" t="b">
         <v>0</v>
       </c>
       <c r="CY38" t="n">
-        <v>1188.76</v>
+        <v>2403.08</v>
       </c>
       <c r="CZ38" t="n">
-        <v>1188.76</v>
+        <v>2403.08</v>
       </c>
       <c r="DA38" t="n">
-        <v>1509.92</v>
+        <v>3247.62</v>
       </c>
       <c r="DB38" t="n">
-        <v>1858.37</v>
+        <v>3997.07</v>
       </c>
       <c r="DC38" t="n">
-        <v>2322.96</v>
+        <v>4996.34</v>
       </c>
       <c r="DD38" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹1161.48</t>
+          <t>Sell 30% | Move stop to T1 ₹2498.17</t>
         </is>
       </c>
       <c r="DE38" t="inlineStr">
@@ -20068,11 +20068,11 @@
         </is>
       </c>
       <c r="DG38" t="n">
-        <v>7.9</v>
+        <v>3.2</v>
       </c>
       <c r="DH38" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +7.9% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +3.2% vs T1</t>
         </is>
       </c>
       <c r="DI38" t="inlineStr">
@@ -20114,7 +20114,7 @@
         <v>0</v>
       </c>
       <c r="DU38" t="n">
-        <v>73.42</v>
+        <v>200.82</v>
       </c>
       <c r="DV38" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ENDURANCE</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -20143,7 +20143,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2578.8</v>
+        <v>1786.7</v>
       </c>
       <c r="D39" t="n">
         <v>104</v>
@@ -20162,7 +20162,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I39" t="n">
         <v>14</v>
@@ -20174,40 +20174,40 @@
         <v>15</v>
       </c>
       <c r="L39" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M39" t="n">
-        <v>2498.17</v>
+        <v>1612.84</v>
       </c>
       <c r="N39" t="n">
-        <v>2729.42</v>
+        <v>1895.51</v>
       </c>
       <c r="O39" t="n">
-        <v>2403.08</v>
+        <v>1659.75</v>
       </c>
       <c r="P39" t="n">
-        <v>3247.62</v>
+        <v>2096.69</v>
       </c>
       <c r="Q39" t="n">
-        <v>3997.07</v>
+        <v>2580.54</v>
       </c>
       <c r="R39" t="n">
-        <v>4996.34</v>
+        <v>3225.68</v>
       </c>
       <c r="S39" t="n">
-        <v>6.81</v>
+        <v>7.11</v>
       </c>
       <c r="T39" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="U39" t="n">
-        <v>71.7</v>
+        <v>64.5</v>
       </c>
       <c r="V39" t="n">
-        <v>71.2</v>
+        <v>78.8</v>
       </c>
       <c r="W39" t="n">
-        <v>44.4</v>
+        <v>50.8</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>₹2420.35–₹2571.79</t>
+          <t>₹1560.45–₹1661.71</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -20243,7 +20243,7 @@
         <v>1.75</v>
       </c>
       <c r="AE39" t="n">
-        <v>-1.44</v>
+        <v>12.73</v>
       </c>
       <c r="AF39" t="b">
         <v>0</v>
@@ -20255,7 +20255,7 @@
         <v>1</v>
       </c>
       <c r="AI39" t="n">
-        <v>53.42</v>
+        <v>43.75</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>Results in 51td — safe runway ✓</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -20300,22 +20300,22 @@
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>52W: 16.3% from ₹3080 [16% from 52W high] +0pts</t>
+          <t>52W: 5.2% from ₹1884 [NEAR 52W HIGH] +5pts</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>ATR-V: -32% compressed [EXPANDING]</t>
+          <t>ATR-V: -51% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV39" t="n">
         <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX39" t="inlineStr"/>
       <c r="AY39" t="n">
@@ -20336,25 +20336,25 @@
         </is>
       </c>
       <c r="BD39" t="n">
-        <v>2403.08</v>
+        <v>1659.75</v>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
-          <t>Initial stop ₹2403.08</t>
+          <t>Initial stop ₹1659.75</t>
         </is>
       </c>
       <c r="BF39" t="b">
         <v>0</v>
       </c>
       <c r="BG39" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="BH39" t="n">
-        <v>108309.6</v>
+        <v>105415.3</v>
       </c>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>42 shares · ₹108,310  (risk ₹7,500)</t>
+          <t>59 shares · ₹105,415  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ39" t="n">
@@ -20369,11 +20369,11 @@
         </is>
       </c>
       <c r="BM39" t="n">
-        <v>62.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="BN39" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 62.2%</t>
+          <t>✅ MC survival 70.4% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO39" t="inlineStr">
@@ -20403,19 +20403,19 @@
       </c>
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BZ39" t="n">
-        <v>7.82</v>
+        <v>16.28</v>
       </c>
       <c r="CA39" t="n">
-        <v>100.41</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="CB39" t="n">
-        <v>135794</v>
+        <v>149048</v>
       </c>
       <c r="CC39" t="n">
-        <v>2498.17</v>
+        <v>1612.84</v>
       </c>
       <c r="CD39" t="inlineStr">
         <is>
@@ -20424,7 +20424,7 @@
       </c>
       <c r="CE39" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor</t>
+          <t>Recent filing: no recent filing; clear of earnings risk; 2/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CF39" t="b">
@@ -20476,32 +20476,32 @@
         <v>39</v>
       </c>
       <c r="CV39" t="n">
-        <v>2698.99</v>
+        <v>1757.92</v>
       </c>
       <c r="CW39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX39" t="b">
         <v>0</v>
       </c>
       <c r="CY39" t="n">
-        <v>2403.08</v>
+        <v>1659.75</v>
       </c>
       <c r="CZ39" t="n">
-        <v>2403.08</v>
+        <v>1659.75</v>
       </c>
       <c r="DA39" t="n">
-        <v>3247.62</v>
+        <v>2096.69</v>
       </c>
       <c r="DB39" t="n">
-        <v>3997.07</v>
+        <v>2580.54</v>
       </c>
       <c r="DC39" t="n">
-        <v>4996.34</v>
+        <v>3225.68</v>
       </c>
       <c r="DD39" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹2498.17</t>
+          <t>Sell 30% | Move stop to T1 ₹1612.84</t>
         </is>
       </c>
       <c r="DE39" t="inlineStr">
@@ -20515,11 +20515,11 @@
         </is>
       </c>
       <c r="DG39" t="n">
-        <v>3.2</v>
+        <v>10.8</v>
       </c>
       <c r="DH39" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +3.2% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +10.8% vs T1</t>
         </is>
       </c>
       <c r="DI39" t="inlineStr">
@@ -20561,7 +20561,7 @@
         <v>0</v>
       </c>
       <c r="DU39" t="n">
-        <v>200.82</v>
+        <v>145.08</v>
       </c>
       <c r="DV39" t="inlineStr">
         <is>
@@ -20816,11 +20816,11 @@
         </is>
       </c>
       <c r="BM40" t="n">
-        <v>63.6</v>
+        <v>61.8</v>
       </c>
       <c r="BN40" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 63.6%</t>
+          <t>⚠️ MC survival 61.8%</t>
         </is>
       </c>
       <c r="BO40" t="inlineStr">
@@ -21267,11 +21267,11 @@
         </is>
       </c>
       <c r="BM41" t="n">
-        <v>78.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="BN41" t="inlineStr">
         <is>
-          <t>✅ MC survival 78.6% (500 sims, 20d)</t>
+          <t>✅ MC survival 77.8% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO41" t="inlineStr">
@@ -21714,11 +21714,11 @@
         </is>
       </c>
       <c r="BM42" t="n">
-        <v>64.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="BN42" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 64.6%</t>
+          <t>⚠️ MC survival 68.2%</t>
         </is>
       </c>
       <c r="BO42" t="inlineStr">
@@ -22161,11 +22161,11 @@
         </is>
       </c>
       <c r="BM43" t="n">
-        <v>58.8</v>
+        <v>59.8</v>
       </c>
       <c r="BN43" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 58.8%</t>
+          <t>⚠️ MC survival 59.8%</t>
         </is>
       </c>
       <c r="BO43" t="inlineStr">
@@ -22608,11 +22608,11 @@
         </is>
       </c>
       <c r="BM44" t="n">
-        <v>72.8</v>
+        <v>67.8</v>
       </c>
       <c r="BN44" t="inlineStr">
         <is>
-          <t>✅ MC survival 72.8% (500 sims, 20d)</t>
+          <t>⚠️ MC survival 67.8%</t>
         </is>
       </c>
       <c r="BO44" t="inlineStr">
@@ -22820,7 +22820,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -22829,10 +22829,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1786.7</v>
+        <v>1253</v>
       </c>
       <c r="D45" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E45" t="n">
         <v>200</v>
@@ -22848,7 +22848,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I45" t="n">
         <v>14</v>
@@ -22863,37 +22863,37 @@
         <v>20</v>
       </c>
       <c r="M45" t="n">
-        <v>1612.84</v>
+        <v>1161.48</v>
       </c>
       <c r="N45" t="n">
-        <v>1895.51</v>
+        <v>1308.06</v>
       </c>
       <c r="O45" t="n">
-        <v>1659.75</v>
+        <v>1188.76</v>
       </c>
       <c r="P45" t="n">
-        <v>2096.69</v>
+        <v>1509.92</v>
       </c>
       <c r="Q45" t="n">
-        <v>2580.54</v>
+        <v>1858.37</v>
       </c>
       <c r="R45" t="n">
-        <v>3225.68</v>
+        <v>2322.96</v>
       </c>
       <c r="S45" t="n">
-        <v>7.11</v>
+        <v>5.13</v>
       </c>
       <c r="T45" t="n">
-        <v>2.11</v>
+        <v>2.93</v>
       </c>
       <c r="U45" t="n">
-        <v>64.5</v>
+        <v>77.5</v>
       </c>
       <c r="V45" t="n">
-        <v>78.8</v>
+        <v>76.3</v>
       </c>
       <c r="W45" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>₹1560.45–₹1661.71</t>
+          <t>₹1134.26–₹1190.11</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -22929,7 +22929,7 @@
         <v>1.75</v>
       </c>
       <c r="AE45" t="n">
-        <v>12.73</v>
+        <v>10.78</v>
       </c>
       <c r="AF45" t="b">
         <v>0</v>
@@ -22941,7 +22941,7 @@
         <v>1</v>
       </c>
       <c r="AI45" t="n">
-        <v>43.75</v>
+        <v>424.59</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -22986,22 +22986,22 @@
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>52W: 5.2% from ₹1884 [NEAR 52W HIGH] +5pts</t>
+          <t>52W: 2.3% from ₹1283 [AT 52W HIGH] +9pts</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>ATR-V: -51% compressed [EXPANDING]</t>
+          <t>ATR-V: -45% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV45" t="n">
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX45" t="inlineStr"/>
       <c r="AY45" t="n">
@@ -23022,25 +23022,25 @@
         </is>
       </c>
       <c r="BD45" t="n">
-        <v>1659.75</v>
+        <v>1188.76</v>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>Initial stop ₹1659.75</t>
+          <t>Initial stop ₹1188.76</t>
         </is>
       </c>
       <c r="BF45" t="b">
         <v>0</v>
       </c>
       <c r="BG45" t="n">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="BH45" t="n">
-        <v>105415.3</v>
+        <v>145348</v>
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>59 shares · ₹105,415  (risk ₹7,500)</t>
+          <t>116 shares · ₹145,348  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ45" t="n">
@@ -23055,11 +23055,11 @@
         </is>
       </c>
       <c r="BM45" t="n">
-        <v>69.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="BN45" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 69.4%</t>
+          <t>✅ MC survival 75.2% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO45" t="inlineStr">
@@ -23089,19 +23089,19 @@
       </c>
       <c r="BX45" t="inlineStr"/>
       <c r="BY45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BZ45" t="n">
-        <v>16.28</v>
+        <v>14.92</v>
       </c>
       <c r="CA45" t="n">
-        <v>72.54000000000001</v>
+        <v>36.71</v>
       </c>
       <c r="CB45" t="n">
-        <v>149048</v>
+        <v>2525362</v>
       </c>
       <c r="CC45" t="n">
-        <v>1612.84</v>
+        <v>1161.48</v>
       </c>
       <c r="CD45" t="inlineStr">
         <is>
@@ -23162,7 +23162,7 @@
         <v>39</v>
       </c>
       <c r="CV45" t="n">
-        <v>1757.92</v>
+        <v>1234.9</v>
       </c>
       <c r="CW45" t="b">
         <v>1</v>
@@ -23171,23 +23171,23 @@
         <v>0</v>
       </c>
       <c r="CY45" t="n">
-        <v>1659.75</v>
+        <v>1188.76</v>
       </c>
       <c r="CZ45" t="n">
-        <v>1659.75</v>
+        <v>1188.76</v>
       </c>
       <c r="DA45" t="n">
-        <v>2096.69</v>
+        <v>1509.92</v>
       </c>
       <c r="DB45" t="n">
-        <v>2580.54</v>
+        <v>1858.37</v>
       </c>
       <c r="DC45" t="n">
-        <v>3225.68</v>
+        <v>2322.96</v>
       </c>
       <c r="DD45" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹1612.84</t>
+          <t>Sell 30% | Move stop to T1 ₹1161.48</t>
         </is>
       </c>
       <c r="DE45" t="inlineStr">
@@ -23201,11 +23201,11 @@
         </is>
       </c>
       <c r="DG45" t="n">
-        <v>10.8</v>
+        <v>7.9</v>
       </c>
       <c r="DH45" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +10.8% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +7.9% vs T1</t>
         </is>
       </c>
       <c r="DI45" t="inlineStr">
@@ -23247,7 +23247,7 @@
         <v>0</v>
       </c>
       <c r="DU45" t="n">
-        <v>145.08</v>
+        <v>73.42</v>
       </c>
       <c r="DV45" t="inlineStr">
         <is>
@@ -23502,11 +23502,11 @@
         </is>
       </c>
       <c r="BM46" t="n">
-        <v>81</v>
+        <v>79.8</v>
       </c>
       <c r="BN46" t="inlineStr">
         <is>
-          <t>✅ MC survival 81.0% (500 sims, 20d)</t>
+          <t>✅ MC survival 79.8% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO46" t="inlineStr">
@@ -23718,7 +23718,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -23727,10 +23727,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>198.4</v>
+        <v>2859.8</v>
       </c>
       <c r="D47" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E47" t="n">
         <v>200</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I47" t="n">
         <v>14</v>
@@ -23761,37 +23761,37 @@
         <v>20</v>
       </c>
       <c r="M47" t="n">
-        <v>182.85</v>
+        <v>2344.97</v>
       </c>
       <c r="N47" t="n">
-        <v>212.27</v>
+        <v>3124.89</v>
       </c>
       <c r="O47" t="n">
-        <v>189.16</v>
+        <v>2550.52</v>
       </c>
       <c r="P47" t="n">
-        <v>237.71</v>
+        <v>3048.46</v>
       </c>
       <c r="Q47" t="n">
-        <v>292.56</v>
+        <v>3751.95</v>
       </c>
       <c r="R47" t="n">
-        <v>365.7</v>
+        <v>4689.94</v>
       </c>
       <c r="S47" t="n">
-        <v>4.66</v>
+        <v>10.81</v>
       </c>
       <c r="T47" t="n">
-        <v>3.22</v>
+        <v>1.39</v>
       </c>
       <c r="U47" t="n">
-        <v>79.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="V47" t="n">
-        <v>60</v>
+        <v>62.8</v>
       </c>
       <c r="W47" t="n">
-        <v>37</v>
+        <v>67.5</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -23815,19 +23815,19 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>₹176.03–₹188.94</t>
+          <t>₹2229.04–₹2438.77</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>ATR-1.00× stop</t>
+          <t>ATR-1.75× stop</t>
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AE47" t="n">
-        <v>8.74</v>
+        <v>20.02</v>
       </c>
       <c r="AF47" t="b">
         <v>0</v>
@@ -23839,7 +23839,7 @@
         <v>1</v>
       </c>
       <c r="AI47" t="n">
-        <v>39.57</v>
+        <v>15</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -23884,22 +23884,22 @@
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>52W: 26.7% from ₹271 [27% from 52W high] +0pts</t>
+          <t>52W: 14.5% from ₹3345 [APPROACHING HIGH] +3pts</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>ATR-V: -36% compressed [EXPANDING]</t>
+          <t>ATR-V: -79% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV47" t="n">
         <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX47" t="inlineStr"/>
       <c r="AY47" t="n">
@@ -23920,25 +23920,25 @@
         </is>
       </c>
       <c r="BD47" t="n">
-        <v>189.16</v>
+        <v>2550.52</v>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
-          <t>Initial stop ₹189.16</t>
+          <t>Initial stop ₹2550.52</t>
         </is>
       </c>
       <c r="BF47" t="b">
         <v>0</v>
       </c>
       <c r="BG47" t="n">
-        <v>811</v>
+        <v>24</v>
       </c>
       <c r="BH47" t="n">
-        <v>160902.4</v>
+        <v>68635.2</v>
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>811 shares · ₹160,902  (risk ₹7,500)</t>
+          <t>24 shares · ₹68,635  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ47" t="n">
@@ -23953,11 +23953,11 @@
         </is>
       </c>
       <c r="BM47" t="n">
-        <v>37.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="BN47" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 37.2%</t>
+          <t>✅ MC survival 75.4% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO47" t="inlineStr">
@@ -23990,20 +23990,20 @@
         <v>0</v>
       </c>
       <c r="BZ47" t="n">
-        <v>12.64</v>
+        <v>22.51</v>
       </c>
       <c r="CA47" t="n">
-        <v>9.24</v>
+        <v>176.73</v>
       </c>
       <c r="CB47" t="n">
-        <v>1633128</v>
+        <v>68918</v>
       </c>
       <c r="CC47" t="n">
-        <v>182.85</v>
+        <v>2344.97</v>
       </c>
       <c r="CD47" t="inlineStr">
         <is>
-          <t>Smallcap circuit breaker: data unavailable (pass)</t>
+          <t>N/A (large-cap)</t>
         </is>
       </c>
       <c r="CE47" t="inlineStr">
@@ -24012,9 +24012,13 @@
         </is>
       </c>
       <c r="CF47" t="b">
-        <v>0</v>
-      </c>
-      <c r="CG47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="CG47" t="inlineStr">
+        <is>
+          <t>⚠️ ROUND_TRIP_RISK — close 2860 &lt; 90% of 3345</t>
+        </is>
+      </c>
       <c r="CH47" t="b">
         <v>0</v>
       </c>
@@ -24060,32 +24064,32 @@
         <v>39</v>
       </c>
       <c r="CV47" t="n">
-        <v>201.33</v>
+        <v>2698.43</v>
       </c>
       <c r="CW47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY47" t="n">
-        <v>189.16</v>
+        <v>2550.52</v>
       </c>
       <c r="CZ47" t="n">
-        <v>189.16</v>
+        <v>2550.52</v>
       </c>
       <c r="DA47" t="n">
-        <v>237.71</v>
+        <v>3048.46</v>
       </c>
       <c r="DB47" t="n">
-        <v>292.56</v>
+        <v>3751.95</v>
       </c>
       <c r="DC47" t="n">
-        <v>365.7</v>
+        <v>4689.94</v>
       </c>
       <c r="DD47" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹182.85</t>
+          <t>Sell 30% | Move stop to T1 ₹2344.97</t>
         </is>
       </c>
       <c r="DE47" t="inlineStr">
@@ -24099,11 +24103,11 @@
         </is>
       </c>
       <c r="DG47" t="n">
-        <v>8.5</v>
+        <v>22</v>
       </c>
       <c r="DH47" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +8.5% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +22.0% vs T1</t>
         </is>
       </c>
       <c r="DI47" t="inlineStr">
@@ -24145,7 +24149,7 @@
         <v>0</v>
       </c>
       <c r="DU47" t="n">
-        <v>18.48</v>
+        <v>353.46</v>
       </c>
       <c r="DV47" t="inlineStr">
         <is>
@@ -24165,7 +24169,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -24174,7 +24178,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1075.2</v>
+        <v>198.4</v>
       </c>
       <c r="D48" t="n">
         <v>89</v>
@@ -24193,7 +24197,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I48" t="n">
         <v>14</v>
@@ -24208,37 +24212,37 @@
         <v>20</v>
       </c>
       <c r="M48" t="n">
-        <v>867.9</v>
+        <v>182.85</v>
       </c>
       <c r="N48" t="n">
-        <v>1157.29</v>
+        <v>212.27</v>
       </c>
       <c r="O48" t="n">
-        <v>979.42</v>
+        <v>189.16</v>
       </c>
       <c r="P48" t="n">
-        <v>1128.27</v>
+        <v>237.71</v>
       </c>
       <c r="Q48" t="n">
-        <v>1388.64</v>
+        <v>292.56</v>
       </c>
       <c r="R48" t="n">
-        <v>1735.8</v>
+        <v>365.7</v>
       </c>
       <c r="S48" t="n">
-        <v>8.91</v>
+        <v>4.66</v>
       </c>
       <c r="T48" t="n">
-        <v>1.68</v>
+        <v>3.22</v>
       </c>
       <c r="U48" t="n">
-        <v>42.1</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="V48" t="n">
-        <v>66.3</v>
+        <v>60</v>
       </c>
       <c r="W48" t="n">
-        <v>61.5</v>
+        <v>37</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -24252,7 +24256,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>NEUTRAL ↔</t>
+          <t>DISTRIBUTION 🔴</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -24262,19 +24266,19 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>₹832.56–₹898.67</t>
+          <t>₹176.03–₹188.94</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ATR-1.75× stop</t>
+          <t>ATR-1.00× stop</t>
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="AE48" t="n">
-        <v>33.84</v>
+        <v>8.74</v>
       </c>
       <c r="AF48" t="b">
         <v>0</v>
@@ -24286,7 +24290,7 @@
         <v>1</v>
       </c>
       <c r="AI48" t="n">
-        <v>1260.03</v>
+        <v>39.57</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -24331,22 +24335,22 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>52W: 9.5% from ₹1188 [NEAR 52W HIGH] +5pts</t>
+          <t>52W: 26.7% from ₹271 [27% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>ATR-V: -60% compressed [EXPANDING]</t>
+          <t>ATR-V: -36% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV48" t="n">
         <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="inlineStr"/>
       <c r="AY48" t="n">
@@ -24367,25 +24371,25 @@
         </is>
       </c>
       <c r="BD48" t="n">
-        <v>979.42</v>
+        <v>189.16</v>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>Initial stop ₹979.42</t>
+          <t>Initial stop ₹189.16</t>
         </is>
       </c>
       <c r="BF48" t="b">
         <v>0</v>
       </c>
       <c r="BG48" t="n">
-        <v>78</v>
+        <v>811</v>
       </c>
       <c r="BH48" t="n">
-        <v>83865.60000000001</v>
+        <v>160902.4</v>
       </c>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>78 shares · ₹83,866  (risk ₹7,500)</t>
+          <t>811 shares · ₹160,902  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ48" t="n">
@@ -24400,23 +24404,19 @@
         </is>
       </c>
       <c r="BM48" t="n">
-        <v>82.8</v>
+        <v>41.2</v>
       </c>
       <c r="BN48" t="inlineStr">
         <is>
-          <t>✅ MC survival 82.8% (500 sims, 20d)</t>
+          <t>⚠️ MC survival 41.2%</t>
         </is>
       </c>
       <c r="BO48" t="inlineStr">
         <is>
-          <t>DISTRIBUTION</t>
-        </is>
-      </c>
-      <c r="BP48" t="inlineStr">
-        <is>
-          <t>🔴 CVD Diverge — distribution</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="BP48" t="inlineStr"/>
       <c r="BQ48" t="b">
         <v>0</v>
       </c>
@@ -24434,31 +24434,27 @@
       </c>
       <c r="BV48" t="inlineStr"/>
       <c r="BW48" t="b">
-        <v>1</v>
-      </c>
-      <c r="BX48" t="inlineStr">
-        <is>
-          <t>🚨 EXIT_LIQUIDITY (3/5) — vol spike on red · close&lt;open high vol · close&gt;VPOC+3ATR</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BZ48" t="n">
-        <v>24.81</v>
+        <v>12.64</v>
       </c>
       <c r="CA48" t="n">
-        <v>54.73</v>
+        <v>9.24</v>
       </c>
       <c r="CB48" t="n">
-        <v>2056803</v>
+        <v>1633128</v>
       </c>
       <c r="CC48" t="n">
-        <v>867.9</v>
+        <v>182.85</v>
       </c>
       <c r="CD48" t="inlineStr">
         <is>
-          <t>N/A (large-cap)</t>
+          <t>Smallcap circuit breaker: data unavailable (pass)</t>
         </is>
       </c>
       <c r="CE48" t="inlineStr">
@@ -24480,7 +24476,7 @@
         <v>1</v>
       </c>
       <c r="CK48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL48" t="b">
         <v>1</v>
@@ -24492,55 +24488,55 @@
         <v>0</v>
       </c>
       <c r="CO48" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="CP48" t="n">
         <v>0</v>
       </c>
       <c r="CQ48" t="n">
-        <v>0.285</v>
+        <v>0.241</v>
       </c>
       <c r="CR48" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="CS48" t="n">
         <v>-5</v>
       </c>
       <c r="CT48" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 28% — LOW</t>
+          <t>🧠 Sniper Bayes 24% — LOW</t>
         </is>
       </c>
       <c r="CU48" t="n">
         <v>39</v>
       </c>
       <c r="CV48" t="n">
-        <v>977.36</v>
+        <v>201.33</v>
       </c>
       <c r="CW48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY48" t="n">
-        <v>979.42</v>
+        <v>189.16</v>
       </c>
       <c r="CZ48" t="n">
-        <v>979.42</v>
+        <v>189.16</v>
       </c>
       <c r="DA48" t="n">
-        <v>1128.27</v>
+        <v>237.71</v>
       </c>
       <c r="DB48" t="n">
-        <v>1388.64</v>
+        <v>292.56</v>
       </c>
       <c r="DC48" t="n">
-        <v>1735.8</v>
+        <v>365.7</v>
       </c>
       <c r="DD48" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹867.90</t>
+          <t>Sell 30% | Move stop to T1 ₹182.85</t>
         </is>
       </c>
       <c r="DE48" t="inlineStr">
@@ -24554,11 +24550,11 @@
         </is>
       </c>
       <c r="DG48" t="n">
-        <v>23.9</v>
+        <v>8.5</v>
       </c>
       <c r="DH48" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +23.9% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +8.5% vs T1</t>
         </is>
       </c>
       <c r="DI48" t="inlineStr">
@@ -24600,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="DU48" t="n">
-        <v>109.46</v>
+        <v>18.48</v>
       </c>
       <c r="DV48" t="inlineStr">
         <is>
@@ -24620,7 +24616,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -24629,10 +24625,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1268</v>
+        <v>1075.2</v>
       </c>
       <c r="D49" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E49" t="n">
         <v>200</v>
@@ -24648,7 +24644,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I49" t="n">
         <v>14</v>
@@ -24660,40 +24656,40 @@
         <v>15</v>
       </c>
       <c r="L49" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M49" t="n">
-        <v>1018.24</v>
+        <v>867.9</v>
       </c>
       <c r="N49" t="n">
-        <v>1321.33</v>
+        <v>1157.29</v>
       </c>
       <c r="O49" t="n">
-        <v>1205.78</v>
+        <v>979.42</v>
       </c>
       <c r="P49" t="n">
-        <v>1323.71</v>
+        <v>1128.27</v>
       </c>
       <c r="Q49" t="n">
-        <v>1629.18</v>
+        <v>1388.64</v>
       </c>
       <c r="R49" t="n">
-        <v>2036.48</v>
+        <v>1735.8</v>
       </c>
       <c r="S49" t="n">
-        <v>4.91</v>
+        <v>8.91</v>
       </c>
       <c r="T49" t="n">
-        <v>3.06</v>
+        <v>1.68</v>
       </c>
       <c r="U49" t="n">
-        <v>83.2</v>
+        <v>42.1</v>
       </c>
       <c r="V49" t="n">
-        <v>85.8</v>
+        <v>66.3</v>
       </c>
       <c r="W49" t="n">
-        <v>52.2</v>
+        <v>61.5</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -24707,7 +24703,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>DISTRIBUTION 🔴</t>
+          <t>NEUTRAL ↔</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -24717,7 +24713,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>₹995.40–₹1042.70</t>
+          <t>₹832.56–₹898.67</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -24729,19 +24725,19 @@
         <v>1.75</v>
       </c>
       <c r="AE49" t="n">
-        <v>28.61</v>
+        <v>33.84</v>
       </c>
       <c r="AF49" t="b">
         <v>0</v>
       </c>
       <c r="AG49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH49" t="b">
         <v>1</v>
       </c>
       <c r="AI49" t="n">
-        <v>296.57</v>
+        <v>1260.03</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -24773,7 +24769,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>Results in 52td — safe runway ✓</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -24786,22 +24782,22 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>52W: 1.6% from ₹1289 [AT 52W HIGH] +9pts</t>
+          <t>52W: 9.5% from ₹1188 [NEAR 52W HIGH] +5pts</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>ATR-V: -10% compressed [EXPANDING]</t>
+          <t>ATR-V: -60% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV49" t="n">
         <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AX49" t="inlineStr"/>
       <c r="AY49" t="n">
@@ -24822,25 +24818,25 @@
         </is>
       </c>
       <c r="BD49" t="n">
-        <v>1205.78</v>
+        <v>979.42</v>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>Initial stop ₹1205.78</t>
+          <t>Initial stop ₹979.42</t>
         </is>
       </c>
       <c r="BF49" t="b">
         <v>0</v>
       </c>
       <c r="BG49" t="n">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="BH49" t="n">
-        <v>152160</v>
+        <v>83865.60000000001</v>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>120 shares · ₹152,160  (risk ₹7,500)</t>
+          <t>78 shares · ₹83,866  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ49" t="n">
@@ -24855,19 +24851,23 @@
         </is>
       </c>
       <c r="BM49" t="n">
-        <v>76</v>
+        <v>81.8</v>
       </c>
       <c r="BN49" t="inlineStr">
         <is>
-          <t>✅ MC survival 76.0% (500 sims, 20d)</t>
+          <t>✅ MC survival 81.8% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO49" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="BP49" t="inlineStr"/>
+          <t>DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="BP49" t="inlineStr">
+        <is>
+          <t>🔴 CVD Diverge — distribution</t>
+        </is>
+      </c>
       <c r="BQ49" t="b">
         <v>0</v>
       </c>
@@ -24889,23 +24889,23 @@
       </c>
       <c r="BX49" t="inlineStr">
         <is>
-          <t>🚨 EXIT_LIQUIDITY (3/5) — upper wick 2×body · RSI 86&gt;70 · close&gt;VPOC+3ATR</t>
+          <t>🚨 EXIT_LIQUIDITY (3/5) — vol spike on red · close&lt;open high vol · close&gt;VPOC+3ATR</t>
         </is>
       </c>
       <c r="BY49" t="n">
         <v>3</v>
       </c>
       <c r="BZ49" t="n">
-        <v>16.57</v>
+        <v>24.81</v>
       </c>
       <c r="CA49" t="n">
-        <v>35.55</v>
+        <v>54.73</v>
       </c>
       <c r="CB49" t="n">
-        <v>2164459</v>
+        <v>2056803</v>
       </c>
       <c r="CC49" t="n">
-        <v>1018.24</v>
+        <v>867.9</v>
       </c>
       <c r="CD49" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
       </c>
       <c r="CE49" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; clear of earnings risk</t>
+          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CF49" t="b">
@@ -24931,7 +24931,7 @@
         <v>1</v>
       </c>
       <c r="CK49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL49" t="b">
         <v>1</v>
@@ -24943,30 +24943,30 @@
         <v>0</v>
       </c>
       <c r="CO49" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="CP49" t="n">
         <v>0</v>
       </c>
       <c r="CQ49" t="n">
-        <v>0.241</v>
+        <v>0.285</v>
       </c>
       <c r="CR49" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="CS49" t="n">
         <v>-5</v>
       </c>
       <c r="CT49" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 24% — LOW</t>
+          <t>🧠 Sniper Bayes 28% — LOW</t>
         </is>
       </c>
       <c r="CU49" t="n">
         <v>39</v>
       </c>
       <c r="CV49" t="n">
-        <v>1089.34</v>
+        <v>977.36</v>
       </c>
       <c r="CW49" t="b">
         <v>1</v>
@@ -24975,23 +24975,23 @@
         <v>1</v>
       </c>
       <c r="CY49" t="n">
-        <v>1205.78</v>
+        <v>979.42</v>
       </c>
       <c r="CZ49" t="n">
-        <v>1205.78</v>
+        <v>979.42</v>
       </c>
       <c r="DA49" t="n">
-        <v>1323.71</v>
+        <v>1128.27</v>
       </c>
       <c r="DB49" t="n">
-        <v>1629.18</v>
+        <v>1388.64</v>
       </c>
       <c r="DC49" t="n">
-        <v>2036.48</v>
+        <v>1735.8</v>
       </c>
       <c r="DD49" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹1018.24</t>
+          <t>Sell 30% | Move stop to T1 ₹867.90</t>
         </is>
       </c>
       <c r="DE49" t="inlineStr">
@@ -25005,11 +25005,11 @@
         </is>
       </c>
       <c r="DG49" t="n">
-        <v>24.5</v>
+        <v>23.9</v>
       </c>
       <c r="DH49" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +24.5% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +23.9% vs T1</t>
         </is>
       </c>
       <c r="DI49" t="inlineStr">
@@ -25051,7 +25051,7 @@
         <v>0</v>
       </c>
       <c r="DU49" t="n">
-        <v>71.09999999999999</v>
+        <v>109.46</v>
       </c>
       <c r="DV49" t="inlineStr">
         <is>
@@ -25071,19 +25071,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1488.2</v>
+        <v>1268</v>
       </c>
       <c r="D50" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E50" t="n">
         <v>200</v>
@@ -25099,7 +25099,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I50" t="n">
         <v>14</v>
@@ -25111,40 +25111,40 @@
         <v>15</v>
       </c>
       <c r="L50" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M50" t="n">
-        <v>1230.24</v>
+        <v>1018.24</v>
       </c>
       <c r="N50" t="n">
-        <v>1539.69</v>
+        <v>1321.33</v>
       </c>
       <c r="O50" t="n">
-        <v>1428.12</v>
+        <v>1205.78</v>
       </c>
       <c r="P50" t="n">
-        <v>1599.31</v>
+        <v>1323.71</v>
       </c>
       <c r="Q50" t="n">
-        <v>1968.38</v>
+        <v>1629.18</v>
       </c>
       <c r="R50" t="n">
-        <v>2460.48</v>
+        <v>2036.48</v>
       </c>
       <c r="S50" t="n">
-        <v>4.04</v>
+        <v>4.91</v>
       </c>
       <c r="T50" t="n">
-        <v>3.72</v>
+        <v>3.06</v>
       </c>
       <c r="U50" t="n">
-        <v>65</v>
+        <v>83.2</v>
       </c>
       <c r="V50" t="n">
-        <v>75.40000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="W50" t="n">
-        <v>34.1</v>
+        <v>52.2</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>₹1207.54–₹1256.73</t>
+          <t>₹995.40–₹1042.70</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -25180,7 +25180,7 @@
         <v>1.75</v>
       </c>
       <c r="AE50" t="n">
-        <v>25.09</v>
+        <v>28.61</v>
       </c>
       <c r="AF50" t="b">
         <v>0</v>
@@ -25192,7 +25192,7 @@
         <v>1</v>
       </c>
       <c r="AI50" t="n">
-        <v>200.33</v>
+        <v>296.57</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         </is>
       </c>
       <c r="AK50" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>Results in 52td — safe runway ✓</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -25237,7 +25237,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>52W: 1.7% from ₹1513 [AT 52W HIGH] +9pts</t>
+          <t>52W: 1.6% from ₹1289 [AT 52W HIGH] +9pts</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -25245,14 +25245,14 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>ATR-V: 7% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: -10% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX50" t="inlineStr"/>
       <c r="AY50" t="n">
@@ -25273,25 +25273,25 @@
         </is>
       </c>
       <c r="BD50" t="n">
-        <v>1428.12</v>
+        <v>1205.78</v>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>Initial stop ₹1428.12</t>
+          <t>Initial stop ₹1205.78</t>
         </is>
       </c>
       <c r="BF50" t="b">
         <v>0</v>
       </c>
       <c r="BG50" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BH50" t="n">
-        <v>184536.8</v>
+        <v>152160</v>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>124 shares · ₹184,537  (risk ₹7,500)</t>
+          <t>120 shares · ₹152,160  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ50" t="n">
@@ -25306,11 +25306,11 @@
         </is>
       </c>
       <c r="BM50" t="n">
-        <v>60.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="BN50" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 60.2%</t>
+          <t>✅ MC survival 77.4% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO50" t="inlineStr">
@@ -25340,23 +25340,23 @@
       </c>
       <c r="BX50" t="inlineStr">
         <is>
-          <t>🚨 EXIT_LIQUIDITY (3/5) — upper wick 2×body · RSI 75&gt;70 · close&gt;VPOC+3ATR</t>
+          <t>🚨 EXIT_LIQUIDITY (3/5) — upper wick 2×body · RSI 86&gt;70 · close&gt;VPOC+3ATR</t>
         </is>
       </c>
       <c r="BY50" t="n">
         <v>3</v>
       </c>
       <c r="BZ50" t="n">
-        <v>11.08</v>
+        <v>16.57</v>
       </c>
       <c r="CA50" t="n">
-        <v>34.33</v>
+        <v>35.55</v>
       </c>
       <c r="CB50" t="n">
-        <v>1319593</v>
+        <v>2164459</v>
       </c>
       <c r="CC50" t="n">
-        <v>1230.24</v>
+        <v>1018.24</v>
       </c>
       <c r="CD50" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
       </c>
       <c r="CE50" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; sector truth boost (1.15x)</t>
+          <t>Recent filing: no recent filing; clear of earnings risk</t>
         </is>
       </c>
       <c r="CF50" t="b">
@@ -25400,24 +25400,24 @@
         <v>0</v>
       </c>
       <c r="CQ50" t="n">
-        <v>0.394</v>
+        <v>0.241</v>
       </c>
       <c r="CR50" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="CS50" t="n">
         <v>-5</v>
       </c>
       <c r="CT50" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 39% — LOW</t>
+          <t>🧠 Sniper Bayes 24% — LOW</t>
         </is>
       </c>
       <c r="CU50" t="n">
         <v>39</v>
       </c>
       <c r="CV50" t="n">
-        <v>1298.9</v>
+        <v>1089.34</v>
       </c>
       <c r="CW50" t="b">
         <v>1</v>
@@ -25426,23 +25426,23 @@
         <v>1</v>
       </c>
       <c r="CY50" t="n">
-        <v>1428.12</v>
+        <v>1205.78</v>
       </c>
       <c r="CZ50" t="n">
-        <v>1428.12</v>
+        <v>1205.78</v>
       </c>
       <c r="DA50" t="n">
-        <v>1599.31</v>
+        <v>1323.71</v>
       </c>
       <c r="DB50" t="n">
-        <v>1968.38</v>
+        <v>1629.18</v>
       </c>
       <c r="DC50" t="n">
-        <v>2460.48</v>
+        <v>2036.48</v>
       </c>
       <c r="DD50" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹1230.24</t>
+          <t>Sell 30% | Move stop to T1 ₹1018.24</t>
         </is>
       </c>
       <c r="DE50" t="inlineStr">
@@ -25456,11 +25456,11 @@
         </is>
       </c>
       <c r="DG50" t="n">
-        <v>21</v>
+        <v>24.5</v>
       </c>
       <c r="DH50" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +21.0% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +24.5% vs T1</t>
         </is>
       </c>
       <c r="DI50" t="inlineStr">
@@ -25502,7 +25502,7 @@
         <v>0</v>
       </c>
       <c r="DU50" t="n">
-        <v>68.66</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="DV50" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -25531,10 +25531,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1872.1</v>
+        <v>6950.5</v>
       </c>
       <c r="D51" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E51" t="n">
         <v>200</v>
@@ -25550,7 +25550,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="I51" t="n">
         <v>14</v>
@@ -25562,40 +25562,40 @@
         <v>15</v>
       </c>
       <c r="L51" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M51" t="n">
-        <v>1769.43</v>
+        <v>6199.08</v>
       </c>
       <c r="N51" t="n">
-        <v>1960.67</v>
+        <v>7216.66</v>
       </c>
       <c r="O51" t="n">
-        <v>1768.77</v>
+        <v>6639.98</v>
       </c>
       <c r="P51" t="n">
-        <v>2300.26</v>
+        <v>8058.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>2831.09</v>
+        <v>9918.530000000001</v>
       </c>
       <c r="R51" t="n">
-        <v>3538.86</v>
+        <v>12398.16</v>
       </c>
       <c r="S51" t="n">
-        <v>5.52</v>
+        <v>4.47</v>
       </c>
       <c r="T51" t="n">
-        <v>2.72</v>
+        <v>3.36</v>
       </c>
       <c r="U51" t="n">
-        <v>67.40000000000001</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="V51" t="n">
-        <v>61.2</v>
+        <v>62.9</v>
       </c>
       <c r="W51" t="n">
-        <v>43.4</v>
+        <v>60.5</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>₹1724.78–₹1815.03</t>
+          <t>₹6072.47–₹6340.20</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -25631,19 +25631,19 @@
         <v>1.75</v>
       </c>
       <c r="AE51" t="n">
-        <v>2.42</v>
+        <v>21.86</v>
       </c>
       <c r="AF51" t="b">
         <v>0</v>
       </c>
       <c r="AG51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="b">
         <v>1</v>
       </c>
       <c r="AI51" t="n">
-        <v>17.04</v>
+        <v>73.94</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>⚠️ Results in 4td — risky, size to PROBE</t>
+          <t>Results in 56td — safe runway ✓</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -25688,22 +25688,22 @@
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>52W: 12.1% from ₹2131 [APPROACHING HIGH] +3pts</t>
+          <t>52W: 3.5% from ₹7200 [AT 52W HIGH] +9pts</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>ATR-V: -13% compressed [EXPANDING]</t>
+          <t>ATR-V: 23% compressed [🌀 COILING (+4pts)]</t>
         </is>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW51" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AX51" t="inlineStr"/>
       <c r="AY51" t="n">
@@ -25724,25 +25724,25 @@
         </is>
       </c>
       <c r="BD51" t="n">
-        <v>1768.77</v>
+        <v>6639.98</v>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>Initial stop ₹1768.77</t>
+          <t>Initial stop ₹6639.98</t>
         </is>
       </c>
       <c r="BF51" t="b">
         <v>0</v>
       </c>
       <c r="BG51" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="BH51" t="n">
-        <v>134791.2</v>
+        <v>166812</v>
       </c>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>72 shares · ₹134,791  (risk ₹7,500)</t>
+          <t>24 shares · ₹166,812  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ51" t="n">
@@ -25757,19 +25757,23 @@
         </is>
       </c>
       <c r="BM51" t="n">
-        <v>71</v>
+        <v>61.6</v>
       </c>
       <c r="BN51" t="inlineStr">
         <is>
-          <t>✅ MC survival 71.0% (500 sims, 20d)</t>
+          <t>⚠️ MC survival 61.6%</t>
         </is>
       </c>
       <c r="BO51" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="BP51" t="inlineStr"/>
+          <t>DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="BP51" t="inlineStr">
+        <is>
+          <t>🔴 CVD Diverge — distribution</t>
+        </is>
+      </c>
       <c r="BQ51" t="b">
         <v>0</v>
       </c>
@@ -25791,19 +25795,19 @@
       </c>
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ51" t="n">
-        <v>8.57</v>
+        <v>11.42</v>
       </c>
       <c r="CA51" t="n">
-        <v>59.05</v>
+        <v>177.44</v>
       </c>
       <c r="CB51" t="n">
-        <v>145084</v>
+        <v>336000</v>
       </c>
       <c r="CC51" t="n">
-        <v>1769.43</v>
+        <v>6199.08</v>
       </c>
       <c r="CD51" t="inlineStr">
         <is>
@@ -25812,7 +25816,7 @@
       </c>
       <c r="CE51" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor</t>
+          <t>Recent filing: no recent filing; clear of earnings risk</t>
         </is>
       </c>
       <c r="CF51" t="b">
@@ -25864,32 +25868,32 @@
         <v>39</v>
       </c>
       <c r="CV51" t="n">
-        <v>1887.53</v>
+        <v>6553.96</v>
       </c>
       <c r="CW51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX51" t="b">
         <v>0</v>
       </c>
       <c r="CY51" t="n">
-        <v>1768.77</v>
+        <v>6639.98</v>
       </c>
       <c r="CZ51" t="n">
-        <v>1768.77</v>
+        <v>6639.98</v>
       </c>
       <c r="DA51" t="n">
-        <v>2300.26</v>
+        <v>8058.8</v>
       </c>
       <c r="DB51" t="n">
-        <v>2831.09</v>
+        <v>9918.530000000001</v>
       </c>
       <c r="DC51" t="n">
-        <v>3538.86</v>
+        <v>12398.16</v>
       </c>
       <c r="DD51" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹1769.43</t>
+          <t>Sell 30% | Move stop to T1 ₹6199.08</t>
         </is>
       </c>
       <c r="DE51" t="inlineStr">
@@ -25903,11 +25907,11 @@
         </is>
       </c>
       <c r="DG51" t="n">
-        <v>5.8</v>
+        <v>12.1</v>
       </c>
       <c r="DH51" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +5.8% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +12.1% vs T1</t>
         </is>
       </c>
       <c r="DI51" t="inlineStr">
@@ -25949,7 +25953,7 @@
         <v>0</v>
       </c>
       <c r="DU51" t="n">
-        <v>118.1</v>
+        <v>354.88</v>
       </c>
       <c r="DV51" t="inlineStr">
         <is>
@@ -25969,19 +25973,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2859.8</v>
+        <v>1488.2</v>
       </c>
       <c r="D52" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E52" t="n">
         <v>200</v>
@@ -25997,7 +26001,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I52" t="n">
         <v>14</v>
@@ -26009,40 +26013,40 @@
         <v>15</v>
       </c>
       <c r="L52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M52" t="n">
-        <v>2344.97</v>
+        <v>1230.24</v>
       </c>
       <c r="N52" t="n">
-        <v>3124.89</v>
+        <v>1539.69</v>
       </c>
       <c r="O52" t="n">
-        <v>2550.52</v>
+        <v>1428.12</v>
       </c>
       <c r="P52" t="n">
-        <v>3048.46</v>
+        <v>1599.31</v>
       </c>
       <c r="Q52" t="n">
-        <v>3751.95</v>
+        <v>1968.38</v>
       </c>
       <c r="R52" t="n">
-        <v>4689.94</v>
+        <v>2460.48</v>
       </c>
       <c r="S52" t="n">
-        <v>10.81</v>
+        <v>4.04</v>
       </c>
       <c r="T52" t="n">
-        <v>1.39</v>
+        <v>3.72</v>
       </c>
       <c r="U52" t="n">
-        <v>86.2</v>
+        <v>65</v>
       </c>
       <c r="V52" t="n">
-        <v>62.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="W52" t="n">
-        <v>67.5</v>
+        <v>34.1</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -26066,7 +26070,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>₹2229.04–₹2438.77</t>
+          <t>₹1207.54–₹1256.73</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -26078,19 +26082,19 @@
         <v>1.75</v>
       </c>
       <c r="AE52" t="n">
-        <v>20.02</v>
+        <v>25.09</v>
       </c>
       <c r="AF52" t="b">
         <v>0</v>
       </c>
       <c r="AG52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="b">
         <v>1</v>
       </c>
       <c r="AI52" t="n">
-        <v>15</v>
+        <v>200.33</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -26098,7 +26102,7 @@
         </is>
       </c>
       <c r="AK52" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
@@ -26122,7 +26126,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>⚠️ Results in 4td — risky, size to PROBE</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -26135,22 +26139,22 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>52W: 14.5% from ₹3345 [APPROACHING HIGH] +3pts</t>
+          <t>52W: 1.7% from ₹1513 [AT 52W HIGH] +9pts</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>ATR-V: -79% compressed [EXPANDING]</t>
+          <t>ATR-V: 7% compressed [🌀 COILING (+4pts)]</t>
         </is>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW52" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AX52" t="inlineStr"/>
       <c r="AY52" t="n">
@@ -26171,25 +26175,25 @@
         </is>
       </c>
       <c r="BD52" t="n">
-        <v>2550.52</v>
+        <v>1428.12</v>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
-          <t>Initial stop ₹2550.52</t>
+          <t>Initial stop ₹1428.12</t>
         </is>
       </c>
       <c r="BF52" t="b">
         <v>0</v>
       </c>
       <c r="BG52" t="n">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="BH52" t="n">
-        <v>68635.2</v>
+        <v>184536.8</v>
       </c>
       <c r="BI52" t="inlineStr">
         <is>
-          <t>24 shares · ₹68,635  (risk ₹7,500)</t>
+          <t>124 shares · ₹184,537  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ52" t="n">
@@ -26204,11 +26208,11 @@
         </is>
       </c>
       <c r="BM52" t="n">
-        <v>73.40000000000001</v>
+        <v>58</v>
       </c>
       <c r="BN52" t="inlineStr">
         <is>
-          <t>✅ MC survival 73.4% (500 sims, 20d)</t>
+          <t>⚠️ MC survival 58.0%</t>
         </is>
       </c>
       <c r="BO52" t="inlineStr">
@@ -26234,23 +26238,27 @@
       </c>
       <c r="BV52" t="inlineStr"/>
       <c r="BW52" t="b">
-        <v>0</v>
-      </c>
-      <c r="BX52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="BX52" t="inlineStr">
+        <is>
+          <t>🚨 EXIT_LIQUIDITY (3/5) — upper wick 2×body · RSI 75&gt;70 · close&gt;VPOC+3ATR</t>
+        </is>
+      </c>
       <c r="BY52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BZ52" t="n">
-        <v>22.51</v>
+        <v>11.08</v>
       </c>
       <c r="CA52" t="n">
-        <v>176.73</v>
+        <v>34.33</v>
       </c>
       <c r="CB52" t="n">
-        <v>68918</v>
+        <v>1319593</v>
       </c>
       <c r="CC52" t="n">
-        <v>2344.97</v>
+        <v>1230.24</v>
       </c>
       <c r="CD52" t="inlineStr">
         <is>
@@ -26259,17 +26267,13 @@
       </c>
       <c r="CE52" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor</t>
+          <t>Recent filing: no recent filing; sector truth boost (1.15x)</t>
         </is>
       </c>
       <c r="CF52" t="b">
-        <v>1</v>
-      </c>
-      <c r="CG52" t="inlineStr">
-        <is>
-          <t>⚠️ ROUND_TRIP_RISK — close 2860 &lt; 90% of 3345</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="CG52" t="inlineStr"/>
       <c r="CH52" t="b">
         <v>0</v>
       </c>
@@ -26298,24 +26302,24 @@
         <v>0</v>
       </c>
       <c r="CQ52" t="n">
-        <v>0.241</v>
+        <v>0.394</v>
       </c>
       <c r="CR52" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="CS52" t="n">
         <v>-5</v>
       </c>
       <c r="CT52" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 24% — LOW</t>
+          <t>🧠 Sniper Bayes 39% — LOW</t>
         </is>
       </c>
       <c r="CU52" t="n">
         <v>39</v>
       </c>
       <c r="CV52" t="n">
-        <v>2698.43</v>
+        <v>1298.9</v>
       </c>
       <c r="CW52" t="b">
         <v>1</v>
@@ -26324,23 +26328,23 @@
         <v>1</v>
       </c>
       <c r="CY52" t="n">
-        <v>2550.52</v>
+        <v>1428.12</v>
       </c>
       <c r="CZ52" t="n">
-        <v>2550.52</v>
+        <v>1428.12</v>
       </c>
       <c r="DA52" t="n">
-        <v>3048.46</v>
+        <v>1599.31</v>
       </c>
       <c r="DB52" t="n">
-        <v>3751.95</v>
+        <v>1968.38</v>
       </c>
       <c r="DC52" t="n">
-        <v>4689.94</v>
+        <v>2460.48</v>
       </c>
       <c r="DD52" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹2344.97</t>
+          <t>Sell 30% | Move stop to T1 ₹1230.24</t>
         </is>
       </c>
       <c r="DE52" t="inlineStr">
@@ -26354,11 +26358,11 @@
         </is>
       </c>
       <c r="DG52" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="DH52" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +22.0% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +21.0% vs T1</t>
         </is>
       </c>
       <c r="DI52" t="inlineStr">
@@ -26400,7 +26404,7 @@
         <v>0</v>
       </c>
       <c r="DU52" t="n">
-        <v>353.46</v>
+        <v>68.66</v>
       </c>
       <c r="DV52" t="inlineStr">
         <is>
@@ -26420,19 +26424,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6644</v>
+        <v>1587</v>
       </c>
       <c r="D53" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E53" t="n">
         <v>200</v>
@@ -26448,7 +26452,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I53" t="n">
         <v>14</v>
@@ -26460,40 +26464,40 @@
         <v>15</v>
       </c>
       <c r="L53" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M53" t="n">
-        <v>6289.62</v>
+        <v>1407.76</v>
       </c>
       <c r="N53" t="n">
-        <v>6826.46</v>
+        <v>1696.53</v>
       </c>
       <c r="O53" t="n">
-        <v>6431.13</v>
+        <v>1459.22</v>
       </c>
       <c r="P53" t="n">
-        <v>8176.51</v>
+        <v>1830.09</v>
       </c>
       <c r="Q53" t="n">
-        <v>10063.39</v>
+        <v>2252.42</v>
       </c>
       <c r="R53" t="n">
-        <v>12579.24</v>
+        <v>2815.52</v>
       </c>
       <c r="S53" t="n">
-        <v>3.2</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="T53" t="n">
-        <v>4.68</v>
+        <v>1.86</v>
       </c>
       <c r="U53" t="n">
-        <v>82.3</v>
+        <v>85</v>
       </c>
       <c r="V53" t="n">
-        <v>65.7</v>
+        <v>61.1</v>
       </c>
       <c r="W53" t="n">
-        <v>65.7</v>
+        <v>54.9</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -26517,7 +26521,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>₹6197.50–₹6410.09</t>
+          <t>₹1355.94–₹1454.22</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -26529,7 +26533,7 @@
         <v>1.75</v>
       </c>
       <c r="AE53" t="n">
-        <v>5.52</v>
+        <v>5.89</v>
       </c>
       <c r="AF53" t="b">
         <v>0</v>
@@ -26541,7 +26545,7 @@
         <v>1</v>
       </c>
       <c r="AI53" t="n">
-        <v>104.29</v>
+        <v>44.63</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -26549,7 +26553,7 @@
         </is>
       </c>
       <c r="AK53" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
@@ -26573,7 +26577,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>Results 8td ago — clear runway</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -26586,26 +26590,30 @@
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>52W: 6.0% from ₹7072 [NEAR 52W HIGH] +5pts</t>
+          <t>52W: 10.3% from ₹1770 [APPROACHING HIGH] +3pts</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>ATR-V: 17% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: -47% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW53" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX53" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>📈 PEAD DRIFT — 16.1% over 8td (+7pts)</t>
+        </is>
+      </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
@@ -26622,25 +26630,25 @@
         </is>
       </c>
       <c r="BD53" t="n">
-        <v>6431.13</v>
+        <v>1459.22</v>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>Initial stop ₹6431.13</t>
+          <t>Initial stop ₹1459.22</t>
         </is>
       </c>
       <c r="BF53" t="b">
         <v>0</v>
       </c>
       <c r="BG53" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="BH53" t="n">
-        <v>232540</v>
+        <v>92046</v>
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>35 shares · ₹232,540  (risk ₹7,500)</t>
+          <t>58 shares · ₹92,046  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ53" t="n">
@@ -26655,11 +26663,11 @@
         </is>
       </c>
       <c r="BM53" t="n">
-        <v>51.4</v>
+        <v>76</v>
       </c>
       <c r="BN53" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 51.4%</t>
+          <t>✅ MC survival 76.0% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO53" t="inlineStr">
@@ -26692,16 +26700,16 @@
         <v>0</v>
       </c>
       <c r="BZ53" t="n">
-        <v>8.619999999999999</v>
+        <v>15.02</v>
       </c>
       <c r="CA53" t="n">
-        <v>121.64</v>
+        <v>73.02</v>
       </c>
       <c r="CB53" t="n">
-        <v>268391</v>
+        <v>833199</v>
       </c>
       <c r="CC53" t="n">
-        <v>6289.62</v>
+        <v>1407.76</v>
       </c>
       <c r="CD53" t="inlineStr">
         <is>
@@ -26710,7 +26718,7 @@
       </c>
       <c r="CE53" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; sector truth boost (1.15x)</t>
+          <t>Recent filing: no recent filing</t>
         </is>
       </c>
       <c r="CF53" t="b">
@@ -26745,24 +26753,24 @@
         <v>0</v>
       </c>
       <c r="CQ53" t="n">
-        <v>0.394</v>
+        <v>0.241</v>
       </c>
       <c r="CR53" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="CS53" t="n">
         <v>-5</v>
       </c>
       <c r="CT53" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 39% — LOW</t>
+          <t>🧠 Sniper Bayes 24% — LOW</t>
         </is>
       </c>
       <c r="CU53" t="n">
         <v>39</v>
       </c>
       <c r="CV53" t="n">
-        <v>6532.9</v>
+        <v>1553.8</v>
       </c>
       <c r="CW53" t="b">
         <v>1</v>
@@ -26771,23 +26779,23 @@
         <v>0</v>
       </c>
       <c r="CY53" t="n">
-        <v>6431.13</v>
+        <v>1459.22</v>
       </c>
       <c r="CZ53" t="n">
-        <v>6431.13</v>
+        <v>1459.22</v>
       </c>
       <c r="DA53" t="n">
-        <v>8176.51</v>
+        <v>1830.09</v>
       </c>
       <c r="DB53" t="n">
-        <v>10063.39</v>
+        <v>2252.42</v>
       </c>
       <c r="DC53" t="n">
-        <v>12579.24</v>
+        <v>2815.52</v>
       </c>
       <c r="DD53" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹6289.62</t>
+          <t>Sell 30% | Move stop to T1 ₹1407.76</t>
         </is>
       </c>
       <c r="DE53" t="inlineStr">
@@ -26801,11 +26809,11 @@
         </is>
       </c>
       <c r="DG53" t="n">
-        <v>5.6</v>
+        <v>12.7</v>
       </c>
       <c r="DH53" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +5.6% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +12.7% vs T1</t>
         </is>
       </c>
       <c r="DI53" t="inlineStr">
@@ -26847,7 +26855,7 @@
         <v>0</v>
       </c>
       <c r="DU53" t="n">
-        <v>243.28</v>
+        <v>146.04</v>
       </c>
       <c r="DV53" t="inlineStr">
         <is>
@@ -26867,35 +26875,35 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1845.7</v>
+        <v>1872.1</v>
       </c>
       <c r="D54" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E54" t="n">
         <v>200</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>🔵 PROBE</t>
+          <t>🟠 MODERATE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>PROBE 10%</t>
+          <t>QTR 25%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I54" t="n">
         <v>14</v>
@@ -26907,40 +26915,40 @@
         <v>15</v>
       </c>
       <c r="L54" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M54" t="n">
-        <v>1729.8</v>
+        <v>1769.43</v>
       </c>
       <c r="N54" t="n">
-        <v>1910.07</v>
+        <v>1960.67</v>
       </c>
       <c r="O54" t="n">
-        <v>1770.6</v>
+        <v>1768.77</v>
       </c>
       <c r="P54" t="n">
-        <v>2248.74</v>
+        <v>2300.26</v>
       </c>
       <c r="Q54" t="n">
-        <v>2767.68</v>
+        <v>2831.09</v>
       </c>
       <c r="R54" t="n">
-        <v>3459.6</v>
+        <v>3538.86</v>
       </c>
       <c r="S54" t="n">
-        <v>4.07</v>
+        <v>5.52</v>
       </c>
       <c r="T54" t="n">
-        <v>3.69</v>
+        <v>2.72</v>
       </c>
       <c r="U54" t="n">
-        <v>80.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="V54" t="n">
-        <v>64.5</v>
+        <v>61.2</v>
       </c>
       <c r="W54" t="n">
-        <v>43.1</v>
+        <v>43.4</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -26964,7 +26972,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>₹1697.62–₹1767.21</t>
+          <t>₹1724.78–₹1815.03</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -26976,19 +26984,19 @@
         <v>1.75</v>
       </c>
       <c r="AE54" t="n">
-        <v>8.23</v>
+        <v>2.42</v>
       </c>
       <c r="AF54" t="b">
         <v>0</v>
       </c>
       <c r="AG54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH54" t="b">
         <v>1</v>
       </c>
       <c r="AI54" t="n">
-        <v>607.8099999999999</v>
+        <v>17.04</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -26996,7 +27004,7 @@
         </is>
       </c>
       <c r="AK54" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
@@ -27020,7 +27028,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>Results in 9td — caution</t>
+          <t>⚠️ Results in 4td — risky, size to PROBE</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
@@ -27033,22 +27041,22 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>52W: 2.1% from ₹1886 [AT 52W HIGH] +9pts</t>
+          <t>52W: 12.1% from ₹2131 [APPROACHING HIGH] +3pts</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>ATR-V: -0% compressed [EXPANDING]</t>
+          <t>ATR-V: -13% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV54" t="n">
         <v>0</v>
       </c>
       <c r="AW54" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AX54" t="inlineStr"/>
       <c r="AY54" t="n">
@@ -27069,25 +27077,25 @@
         </is>
       </c>
       <c r="BD54" t="n">
-        <v>1770.6</v>
+        <v>1768.77</v>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
-          <t>Initial stop ₹1770.60</t>
+          <t>Initial stop ₹1768.77</t>
         </is>
       </c>
       <c r="BF54" t="b">
         <v>0</v>
       </c>
       <c r="BG54" t="n">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="BH54" t="n">
-        <v>182724.3</v>
+        <v>134791.2</v>
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>99 shares · ₹182,724  (risk ₹7,500)</t>
+          <t>72 shares · ₹134,791  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ54" t="n">
@@ -27102,11 +27110,11 @@
         </is>
       </c>
       <c r="BM54" t="n">
-        <v>68.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="BN54" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 68.4%</t>
+          <t>✅ MC survival 72.0% (500 sims, 20d)</t>
         </is>
       </c>
       <c r="BO54" t="inlineStr">
@@ -27139,16 +27147,16 @@
         <v>0</v>
       </c>
       <c r="BZ54" t="n">
-        <v>11.71</v>
+        <v>8.57</v>
       </c>
       <c r="CA54" t="n">
-        <v>42.91</v>
+        <v>59.05</v>
       </c>
       <c r="CB54" t="n">
-        <v>5569614</v>
+        <v>145084</v>
       </c>
       <c r="CC54" t="n">
-        <v>1729.8</v>
+        <v>1769.43</v>
       </c>
       <c r="CD54" t="inlineStr">
         <is>
@@ -27157,7 +27165,7 @@
       </c>
       <c r="CE54" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; sector truth boost (1.15x)</t>
+          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CF54" t="b">
@@ -27192,49 +27200,49 @@
         <v>0</v>
       </c>
       <c r="CQ54" t="n">
-        <v>0.394</v>
+        <v>0.241</v>
       </c>
       <c r="CR54" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="CS54" t="n">
         <v>-5</v>
       </c>
       <c r="CT54" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 39% — LOW</t>
+          <t>🧠 Sniper Bayes 24% — LOW</t>
         </is>
       </c>
       <c r="CU54" t="n">
         <v>39</v>
       </c>
       <c r="CV54" t="n">
-        <v>1815.62</v>
+        <v>1887.53</v>
       </c>
       <c r="CW54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX54" t="b">
         <v>0</v>
       </c>
       <c r="CY54" t="n">
-        <v>1770.6</v>
+        <v>1768.77</v>
       </c>
       <c r="CZ54" t="n">
-        <v>1770.6</v>
+        <v>1768.77</v>
       </c>
       <c r="DA54" t="n">
-        <v>2248.74</v>
+        <v>2300.26</v>
       </c>
       <c r="DB54" t="n">
-        <v>2767.68</v>
+        <v>2831.09</v>
       </c>
       <c r="DC54" t="n">
-        <v>3459.6</v>
+        <v>3538.86</v>
       </c>
       <c r="DD54" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹1729.80</t>
+          <t>Sell 30% | Move stop to T1 ₹1769.43</t>
         </is>
       </c>
       <c r="DE54" t="inlineStr">
@@ -27248,11 +27256,11 @@
         </is>
       </c>
       <c r="DG54" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="DH54" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +6.7% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +5.8% vs T1</t>
         </is>
       </c>
       <c r="DI54" t="inlineStr">
@@ -27294,7 +27302,7 @@
         <v>0</v>
       </c>
       <c r="DU54" t="n">
-        <v>85.81999999999999</v>
+        <v>118.1</v>
       </c>
       <c r="DV54" t="inlineStr">
         <is>
@@ -27314,7 +27322,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -27323,22 +27331,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6950.5</v>
+        <v>3611.1</v>
       </c>
       <c r="D55" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E55" t="n">
         <v>200</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>🔵 PROBE</t>
+          <t>🟠 MODERATE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>PROBE 10%</t>
+          <t>QTR 25%</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -27357,37 +27365,37 @@
         <v>20</v>
       </c>
       <c r="M55" t="n">
-        <v>6199.08</v>
+        <v>3123.35</v>
       </c>
       <c r="N55" t="n">
-        <v>7216.66</v>
+        <v>3776.33</v>
       </c>
       <c r="O55" t="n">
-        <v>6639.98</v>
+        <v>3418.33</v>
       </c>
       <c r="P55" t="n">
-        <v>8058.8</v>
+        <v>4060.36</v>
       </c>
       <c r="Q55" t="n">
-        <v>9918.530000000001</v>
+        <v>4997.36</v>
       </c>
       <c r="R55" t="n">
-        <v>12398.16</v>
+        <v>6246.7</v>
       </c>
       <c r="S55" t="n">
-        <v>4.47</v>
+        <v>5.34</v>
       </c>
       <c r="T55" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="U55" t="n">
-        <v>93.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="V55" t="n">
-        <v>62.9</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="W55" t="n">
-        <v>60.5</v>
+        <v>36.6</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -27411,7 +27419,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>₹6072.47–₹6340.20</t>
+          <t>₹3047.13–₹3202.22</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -27423,7 +27431,7 @@
         <v>1.75</v>
       </c>
       <c r="AE55" t="n">
-        <v>21.86</v>
+        <v>14.71</v>
       </c>
       <c r="AF55" t="b">
         <v>0</v>
@@ -27435,7 +27443,7 @@
         <v>1</v>
       </c>
       <c r="AI55" t="n">
-        <v>73.94</v>
+        <v>38.55</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -27480,7 +27488,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>52W: 3.5% from ₹7200 [AT 52W HIGH] +9pts</t>
+          <t>52W: 1.9% from ₹3680 [AT 52W HIGH] +9pts</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -27488,7 +27496,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>ATR-V: 23% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: 6% compressed [🌀 COILING (+4pts)]</t>
         </is>
       </c>
       <c r="AV55" t="n">
@@ -27516,25 +27524,25 @@
         </is>
       </c>
       <c r="BD55" t="n">
-        <v>6639.98</v>
+        <v>3418.33</v>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>Initial stop ₹6639.98</t>
+          <t>Initial stop ₹3418.33</t>
         </is>
       </c>
       <c r="BF55" t="b">
         <v>0</v>
       </c>
       <c r="BG55" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="BH55" t="n">
-        <v>166812</v>
+        <v>137221.8</v>
       </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>24 shares · ₹166,812  (risk ₹7,500)</t>
+          <t>38 shares · ₹137,222  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ55" t="n">
@@ -27558,14 +27566,10 @@
       </c>
       <c r="BO55" t="inlineStr">
         <is>
-          <t>DISTRIBUTION</t>
-        </is>
-      </c>
-      <c r="BP55" t="inlineStr">
-        <is>
-          <t>🔴 CVD Diverge — distribution</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="BP55" t="inlineStr"/>
       <c r="BQ55" t="b">
         <v>0</v>
       </c>
@@ -27587,19 +27591,19 @@
       </c>
       <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BZ55" t="n">
-        <v>11.42</v>
+        <v>4.04</v>
       </c>
       <c r="CA55" t="n">
-        <v>177.44</v>
+        <v>110.15</v>
       </c>
       <c r="CB55" t="n">
-        <v>336000</v>
+        <v>61124</v>
       </c>
       <c r="CC55" t="n">
-        <v>6199.08</v>
+        <v>3123.35</v>
       </c>
       <c r="CD55" t="inlineStr">
         <is>
@@ -27643,49 +27647,49 @@
         <v>0</v>
       </c>
       <c r="CQ55" t="n">
-        <v>0.241</v>
+        <v>0.132</v>
       </c>
       <c r="CR55" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="CS55" t="n">
         <v>-5</v>
       </c>
       <c r="CT55" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 24% — LOW</t>
+          <t>🧠 Sniper Bayes 13% — LOW</t>
         </is>
       </c>
       <c r="CU55" t="n">
         <v>39</v>
       </c>
       <c r="CV55" t="n">
-        <v>6553.96</v>
+        <v>3343.65</v>
       </c>
       <c r="CW55" t="b">
         <v>1</v>
       </c>
       <c r="CX55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY55" t="n">
-        <v>6639.98</v>
+        <v>3418.33</v>
       </c>
       <c r="CZ55" t="n">
-        <v>6639.98</v>
+        <v>3418.33</v>
       </c>
       <c r="DA55" t="n">
-        <v>8058.8</v>
+        <v>4060.36</v>
       </c>
       <c r="DB55" t="n">
-        <v>9918.530000000001</v>
+        <v>4997.36</v>
       </c>
       <c r="DC55" t="n">
-        <v>12398.16</v>
+        <v>6246.7</v>
       </c>
       <c r="DD55" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹6199.08</t>
+          <t>Sell 30% | Move stop to T1 ₹3123.35</t>
         </is>
       </c>
       <c r="DE55" t="inlineStr">
@@ -27699,11 +27703,11 @@
         </is>
       </c>
       <c r="DG55" t="n">
-        <v>12.1</v>
+        <v>15.6</v>
       </c>
       <c r="DH55" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +12.1% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +15.6% vs T1</t>
         </is>
       </c>
       <c r="DI55" t="inlineStr">
@@ -27745,7 +27749,7 @@
         <v>0</v>
       </c>
       <c r="DU55" t="n">
-        <v>354.88</v>
+        <v>220.3</v>
       </c>
       <c r="DV55" t="inlineStr">
         <is>
@@ -27765,35 +27769,35 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1587</v>
+        <v>1845.7</v>
       </c>
       <c r="D56" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E56" t="n">
         <v>200</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>🔵 PROBE</t>
+          <t>🟠 MODERATE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PROBE 10%</t>
+          <t>QTR 25%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="I56" t="n">
         <v>14</v>
@@ -27808,37 +27812,37 @@
         <v>20</v>
       </c>
       <c r="M56" t="n">
-        <v>1407.76</v>
+        <v>1729.8</v>
       </c>
       <c r="N56" t="n">
-        <v>1696.53</v>
+        <v>1910.07</v>
       </c>
       <c r="O56" t="n">
-        <v>1459.22</v>
+        <v>1770.6</v>
       </c>
       <c r="P56" t="n">
-        <v>1830.09</v>
+        <v>2248.74</v>
       </c>
       <c r="Q56" t="n">
-        <v>2252.42</v>
+        <v>2767.68</v>
       </c>
       <c r="R56" t="n">
-        <v>2815.52</v>
+        <v>3459.6</v>
       </c>
       <c r="S56" t="n">
-        <v>8.050000000000001</v>
+        <v>4.07</v>
       </c>
       <c r="T56" t="n">
-        <v>1.86</v>
+        <v>3.69</v>
       </c>
       <c r="U56" t="n">
-        <v>85</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="V56" t="n">
-        <v>61.1</v>
+        <v>64.5</v>
       </c>
       <c r="W56" t="n">
-        <v>54.9</v>
+        <v>43.1</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -27862,7 +27866,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>₹1355.94–₹1454.22</t>
+          <t>₹1697.62–₹1767.21</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -27874,7 +27878,7 @@
         <v>1.75</v>
       </c>
       <c r="AE56" t="n">
-        <v>5.89</v>
+        <v>8.23</v>
       </c>
       <c r="AF56" t="b">
         <v>0</v>
@@ -27886,7 +27890,7 @@
         <v>1</v>
       </c>
       <c r="AI56" t="n">
-        <v>44.63</v>
+        <v>607.8099999999999</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
@@ -27894,7 +27898,7 @@
         </is>
       </c>
       <c r="AK56" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
@@ -27931,22 +27935,22 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>52W: 10.3% from ₹1770 [APPROACHING HIGH] +3pts</t>
+          <t>52W: 2.1% from ₹1886 [AT 52W HIGH] +9pts</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>ATR-V: -47% compressed [EXPANDING]</t>
+          <t>ATR-V: -0% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV56" t="n">
         <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AX56" t="inlineStr"/>
       <c r="AY56" t="n">
@@ -27967,25 +27971,25 @@
         </is>
       </c>
       <c r="BD56" t="n">
-        <v>1459.22</v>
+        <v>1770.6</v>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>Initial stop ₹1459.22</t>
+          <t>Initial stop ₹1770.60</t>
         </is>
       </c>
       <c r="BF56" t="b">
         <v>0</v>
       </c>
       <c r="BG56" t="n">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="BH56" t="n">
-        <v>92046</v>
+        <v>182724.3</v>
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>58 shares · ₹92,046  (risk ₹7,500)</t>
+          <t>99 shares · ₹182,724  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ56" t="n">
@@ -28000,11 +28004,11 @@
         </is>
       </c>
       <c r="BM56" t="n">
-        <v>79.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="BN56" t="inlineStr">
         <is>
-          <t>✅ MC survival 79.8% (500 sims, 20d)</t>
+          <t>⚠️ MC survival 66.4%</t>
         </is>
       </c>
       <c r="BO56" t="inlineStr">
@@ -28037,16 +28041,16 @@
         <v>0</v>
       </c>
       <c r="BZ56" t="n">
-        <v>15.02</v>
+        <v>11.71</v>
       </c>
       <c r="CA56" t="n">
-        <v>73.02</v>
+        <v>42.91</v>
       </c>
       <c r="CB56" t="n">
-        <v>833199</v>
+        <v>5569614</v>
       </c>
       <c r="CC56" t="n">
-        <v>1407.76</v>
+        <v>1729.8</v>
       </c>
       <c r="CD56" t="inlineStr">
         <is>
@@ -28055,7 +28059,7 @@
       </c>
       <c r="CE56" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing</t>
+          <t>Recent filing: no recent filing; sector truth boost (1.15x)</t>
         </is>
       </c>
       <c r="CF56" t="b">
@@ -28090,24 +28094,24 @@
         <v>0</v>
       </c>
       <c r="CQ56" t="n">
-        <v>0.241</v>
+        <v>0.394</v>
       </c>
       <c r="CR56" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="CS56" t="n">
         <v>-5</v>
       </c>
       <c r="CT56" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 24% — LOW</t>
+          <t>🧠 Sniper Bayes 39% — LOW</t>
         </is>
       </c>
       <c r="CU56" t="n">
         <v>39</v>
       </c>
       <c r="CV56" t="n">
-        <v>1553.8</v>
+        <v>1815.62</v>
       </c>
       <c r="CW56" t="b">
         <v>1</v>
@@ -28116,23 +28120,23 @@
         <v>0</v>
       </c>
       <c r="CY56" t="n">
-        <v>1459.22</v>
+        <v>1770.6</v>
       </c>
       <c r="CZ56" t="n">
-        <v>1459.22</v>
+        <v>1770.6</v>
       </c>
       <c r="DA56" t="n">
-        <v>1830.09</v>
+        <v>2248.74</v>
       </c>
       <c r="DB56" t="n">
-        <v>2252.42</v>
+        <v>2767.68</v>
       </c>
       <c r="DC56" t="n">
-        <v>2815.52</v>
+        <v>3459.6</v>
       </c>
       <c r="DD56" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹1407.76</t>
+          <t>Sell 30% | Move stop to T1 ₹1729.80</t>
         </is>
       </c>
       <c r="DE56" t="inlineStr">
@@ -28146,11 +28150,11 @@
         </is>
       </c>
       <c r="DG56" t="n">
-        <v>12.7</v>
+        <v>6.7</v>
       </c>
       <c r="DH56" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +12.7% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +6.7% vs T1</t>
         </is>
       </c>
       <c r="DI56" t="inlineStr">
@@ -28192,7 +28196,7 @@
         <v>0</v>
       </c>
       <c r="DU56" t="n">
-        <v>146.04</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="DV56" t="inlineStr">
         <is>
@@ -28212,19 +28216,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3611.1</v>
+        <v>6644</v>
       </c>
       <c r="D57" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E57" t="n">
         <v>200</v>
@@ -28240,7 +28244,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I57" t="n">
         <v>14</v>
@@ -28252,40 +28256,40 @@
         <v>15</v>
       </c>
       <c r="L57" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="M57" t="n">
-        <v>3123.35</v>
+        <v>6289.62</v>
       </c>
       <c r="N57" t="n">
-        <v>3776.33</v>
+        <v>6826.46</v>
       </c>
       <c r="O57" t="n">
-        <v>3418.33</v>
+        <v>6431.13</v>
       </c>
       <c r="P57" t="n">
-        <v>4060.36</v>
+        <v>8176.51</v>
       </c>
       <c r="Q57" t="n">
-        <v>4997.36</v>
+        <v>10063.39</v>
       </c>
       <c r="R57" t="n">
-        <v>6246.7</v>
+        <v>12579.24</v>
       </c>
       <c r="S57" t="n">
-        <v>5.34</v>
+        <v>3.2</v>
       </c>
       <c r="T57" t="n">
-        <v>2.81</v>
+        <v>4.68</v>
       </c>
       <c r="U57" t="n">
-        <v>76.3</v>
+        <v>82.3</v>
       </c>
       <c r="V57" t="n">
-        <v>66.90000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="W57" t="n">
-        <v>36.6</v>
+        <v>65.7</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -28309,7 +28313,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>₹3047.13–₹3202.22</t>
+          <t>₹6197.50–₹6410.09</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -28321,7 +28325,7 @@
         <v>1.75</v>
       </c>
       <c r="AE57" t="n">
-        <v>14.71</v>
+        <v>5.52</v>
       </c>
       <c r="AF57" t="b">
         <v>0</v>
@@ -28333,7 +28337,7 @@
         <v>1</v>
       </c>
       <c r="AI57" t="n">
-        <v>38.55</v>
+        <v>104.29</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
@@ -28341,7 +28345,7 @@
         </is>
       </c>
       <c r="AK57" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
@@ -28365,7 +28369,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>⚠️ Results in 5td — risky, size to PROBE</t>
+          <t>Results in 9td — caution</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -28378,22 +28382,22 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>52W: 1.9% from ₹3680 [AT 52W HIGH] +9pts</t>
+          <t>52W: 6.0% from ₹7072 [NEAR 52W HIGH] +5pts</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>ATR-V: 6% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: 17% compressed [🌀 COILING (+4pts)]</t>
         </is>
       </c>
       <c r="AV57" t="n">
         <v>4</v>
       </c>
       <c r="AW57" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX57" t="inlineStr"/>
       <c r="AY57" t="n">
@@ -28414,25 +28418,25 @@
         </is>
       </c>
       <c r="BD57" t="n">
-        <v>3418.33</v>
+        <v>6431.13</v>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>Initial stop ₹3418.33</t>
+          <t>Initial stop ₹6431.13</t>
         </is>
       </c>
       <c r="BF57" t="b">
         <v>0</v>
       </c>
       <c r="BG57" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="BH57" t="n">
-        <v>137221.8</v>
+        <v>232540</v>
       </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>38 shares · ₹137,222  (risk ₹7,500)</t>
+          <t>35 shares · ₹232,540  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BJ57" t="n">
@@ -28447,11 +28451,11 @@
         </is>
       </c>
       <c r="BM57" t="n">
-        <v>65.2</v>
+        <v>46</v>
       </c>
       <c r="BN57" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 65.2%</t>
+          <t>⚠️ MC survival 46.0%</t>
         </is>
       </c>
       <c r="BO57" t="inlineStr">
@@ -28481,19 +28485,19 @@
       </c>
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BZ57" t="n">
-        <v>4.04</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="CA57" t="n">
-        <v>110.15</v>
+        <v>121.64</v>
       </c>
       <c r="CB57" t="n">
-        <v>61124</v>
+        <v>268391</v>
       </c>
       <c r="CC57" t="n">
-        <v>3123.35</v>
+        <v>6289.62</v>
       </c>
       <c r="CD57" t="inlineStr">
         <is>
@@ -28502,7 +28506,7 @@
       </c>
       <c r="CE57" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing</t>
+          <t>Recent filing: no recent filing; sector truth boost (1.15x)</t>
         </is>
       </c>
       <c r="CF57" t="b">
@@ -28537,49 +28541,49 @@
         <v>0</v>
       </c>
       <c r="CQ57" t="n">
-        <v>0.132</v>
+        <v>0.394</v>
       </c>
       <c r="CR57" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="CS57" t="n">
         <v>-5</v>
       </c>
       <c r="CT57" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 13% — LOW</t>
+          <t>🧠 Sniper Bayes 39% — LOW</t>
         </is>
       </c>
       <c r="CU57" t="n">
         <v>39</v>
       </c>
       <c r="CV57" t="n">
-        <v>3343.65</v>
+        <v>6532.9</v>
       </c>
       <c r="CW57" t="b">
         <v>1</v>
       </c>
       <c r="CX57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY57" t="n">
-        <v>3418.33</v>
+        <v>6431.13</v>
       </c>
       <c r="CZ57" t="n">
-        <v>3418.33</v>
+        <v>6431.13</v>
       </c>
       <c r="DA57" t="n">
-        <v>4060.36</v>
+        <v>8176.51</v>
       </c>
       <c r="DB57" t="n">
-        <v>4997.36</v>
+        <v>10063.39</v>
       </c>
       <c r="DC57" t="n">
-        <v>6246.7</v>
+        <v>12579.24</v>
       </c>
       <c r="DD57" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹3123.35</t>
+          <t>Sell 30% | Move stop to T1 ₹6289.62</t>
         </is>
       </c>
       <c r="DE57" t="inlineStr">
@@ -28593,11 +28597,11 @@
         </is>
       </c>
       <c r="DG57" t="n">
-        <v>15.6</v>
+        <v>5.6</v>
       </c>
       <c r="DH57" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 39/100 · +15.6% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +5.6% vs T1</t>
         </is>
       </c>
       <c r="DI57" t="inlineStr">
@@ -28639,7 +28643,7 @@
         <v>0</v>
       </c>
       <c r="DU57" t="n">
-        <v>220.3</v>
+        <v>243.28</v>
       </c>
       <c r="DV57" t="inlineStr">
         <is>
@@ -28894,11 +28898,11 @@
         </is>
       </c>
       <c r="BM58" t="n">
-        <v>54.2</v>
+        <v>57.6</v>
       </c>
       <c r="BN58" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 54.2%</t>
+          <t>⚠️ MC survival 57.6%</t>
         </is>
       </c>
       <c r="BO58" t="inlineStr">
@@ -29118,7 +29122,7 @@
         <v>1041.4</v>
       </c>
       <c r="D59" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E59" t="n">
         <v>200</v>
@@ -29146,7 +29150,7 @@
         <v>15</v>
       </c>
       <c r="L59" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M59" t="n">
         <v>935.38</v>
@@ -29259,7 +29263,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>Results in 9td — caution</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
@@ -29341,11 +29345,11 @@
         </is>
       </c>
       <c r="BM59" t="n">
-        <v>69</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="BN59" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 69.0%</t>
+          <t>⚠️ MC survival 69.4%</t>
         </is>
       </c>
       <c r="BO59" t="inlineStr">
@@ -29788,11 +29792,11 @@
         </is>
       </c>
       <c r="BM60" t="n">
-        <v>63.8</v>
+        <v>59.4</v>
       </c>
       <c r="BN60" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 63.8%</t>
+          <t>⚠️ MC survival 59.4%</t>
         </is>
       </c>
       <c r="BO60" t="inlineStr">
@@ -30016,19 +30020,19 @@
         <v>830</v>
       </c>
       <c r="D61" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E61" t="n">
         <v>200</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>🟠 MODERATE</t>
+          <t>🟡 HIGH</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>QTR 25%</t>
+          <t>HALF 50%</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -30044,7 +30048,7 @@
         <v>15</v>
       </c>
       <c r="L61" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M61" t="n">
         <v>744.8099999999999</v>
@@ -30157,7 +30161,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>Results in 59td — safe runway ✓</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -30298,7 +30302,7 @@
       </c>
       <c r="CE61" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor</t>
+          <t>Recent filing: no recent filing; clear of earnings risk; 2/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CF61" t="b">
@@ -30690,11 +30694,11 @@
         </is>
       </c>
       <c r="BM62" t="n">
-        <v>66.8</v>
+        <v>63.8</v>
       </c>
       <c r="BN62" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 66.8%</t>
+          <t>⚠️ MC survival 63.8%</t>
         </is>
       </c>
       <c r="BO62" t="inlineStr">
@@ -30918,7 +30922,7 @@
         <v>473.25</v>
       </c>
       <c r="D63" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E63" t="n">
         <v>200</v>
@@ -30946,7 +30950,7 @@
         <v>15</v>
       </c>
       <c r="L63" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M63" t="n">
         <v>499.86</v>
@@ -31059,7 +31063,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>Results in 56td — safe runway ✓</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
@@ -31141,11 +31145,11 @@
         </is>
       </c>
       <c r="BM63" t="n">
-        <v>49</v>
+        <v>49.8</v>
       </c>
       <c r="BN63" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 49.0%</t>
+          <t>⚠️ MC survival 49.8%</t>
         </is>
       </c>
       <c r="BO63" t="inlineStr">
@@ -31196,7 +31200,7 @@
       </c>
       <c r="CE63" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; clear of earnings risk; 2/3 fortress layers at vpoc floor</t>
+          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CF63" t="b">
@@ -31365,7 +31369,7 @@
         <v>1468.6</v>
       </c>
       <c r="D64" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E64" t="n">
         <v>200</v>
@@ -31393,7 +31397,7 @@
         <v>15</v>
       </c>
       <c r="L64" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="M64" t="n">
         <v>1325.93</v>
@@ -31506,7 +31510,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>Results 15td ago — clear runway</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -31536,13 +31540,9 @@
       <c r="AW64" t="n">
         <v>13</v>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>PEAD window 15td, drift 6.4% (+4pts)</t>
-        </is>
-      </c>
+      <c r="AX64" t="inlineStr"/>
       <c r="AY64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
@@ -31592,11 +31592,11 @@
         </is>
       </c>
       <c r="BM64" t="n">
-        <v>61</v>
+        <v>60.4</v>
       </c>
       <c r="BN64" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 61.0%</t>
+          <t>⚠️ MC survival 60.4%</t>
         </is>
       </c>
       <c r="BO64" t="inlineStr">
@@ -32039,11 +32039,11 @@
         </is>
       </c>
       <c r="BM65" t="n">
-        <v>65.2</v>
+        <v>61.8</v>
       </c>
       <c r="BN65" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 65.2%</t>
+          <t>⚠️ MC survival 61.8%</t>
         </is>
       </c>
       <c r="BO65" t="inlineStr">

--- a/outputs/fortress_screener.xlsx
+++ b/outputs/fortress_screener.xlsx
@@ -1083,7 +1083,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1092,29 +1092,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>519.85</v>
+        <v>471.1</v>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="E2" t="n">
         <v>200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>🟡 HIGH</t>
+          <t>🟢 PRISTINE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HALF 50%</t>
+          <t>FULL 100%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -1123,40 +1123,40 @@
         <v>15</v>
       </c>
       <c r="L2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M2" t="n">
-        <v>513.27</v>
+        <v>464.11</v>
       </c>
       <c r="N2" t="n">
-        <v>536.45</v>
+        <v>510.25</v>
       </c>
       <c r="O2" t="n">
-        <v>504.35</v>
+        <v>434.56</v>
       </c>
       <c r="P2" t="n">
-        <v>667.25</v>
+        <v>603.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>821.23</v>
+        <v>742.58</v>
       </c>
       <c r="R2" t="n">
-        <v>1026.54</v>
+        <v>928.22</v>
       </c>
       <c r="S2" t="n">
-        <v>2.98</v>
+        <v>7.76</v>
       </c>
       <c r="T2" t="n">
-        <v>5.03</v>
+        <v>1.93</v>
       </c>
       <c r="U2" t="n">
-        <v>45.5</v>
+        <v>70.5</v>
       </c>
       <c r="V2" t="n">
-        <v>50.3</v>
+        <v>48.1</v>
       </c>
       <c r="W2" t="n">
-        <v>56.8</v>
+        <v>35.7</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>NEUTRAL ↔</t>
+          <t>DISTRIBUTION 🔴</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>₹504.53–₹523.87</t>
+          <t>₹443.54–₹481.61</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1192,7 +1192,7 @@
         <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.31</v>
+        <v>-4.66</v>
       </c>
       <c r="AF2" t="b">
         <v>1</v>
@@ -1204,7 +1204,7 @@
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>100.29</v>
+        <v>1.65</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>No recent filing</t>
+          <t>Analysts/institutional investor meet/con. call updates [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Results in 9td — caution</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>52W: 20.3% from ₹652 [20% from 52W high] +0pts</t>
+          <t>52W: 39.9% from ₹784 [40% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -1257,21 +1257,25 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>ATR-V: 9% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: -17% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>🌀 VDU 5-bar deep coil (+7pts)</t>
+        </is>
+      </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
@@ -1292,25 +1296,25 @@
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>504.35</v>
+        <v>434.56</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>Initial stop ₹504.35</t>
+          <t>Initial stop ₹434.56</t>
         </is>
       </c>
       <c r="BI2" t="b">
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>483</v>
+        <v>205</v>
       </c>
       <c r="BK2" t="n">
-        <v>251087.55</v>
+        <v>96575.5</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>483 shares · ₹251,088  (risk ₹7,500)</t>
+          <t>205 shares · ₹96,576  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -1325,23 +1329,19 @@
         </is>
       </c>
       <c r="BP2" t="n">
-        <v>26.2</v>
+        <v>46.6</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 26.2%</t>
+          <t>⚠️ MC survival 46.6%</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>DISTRIBUTION</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>🔴 CVD Diverge — distribution</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr"/>
       <c r="BT2" t="b">
         <v>0</v>
       </c>
@@ -1363,19 +1363,19 @@
       </c>
       <c r="CA2" t="inlineStr"/>
       <c r="CB2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>7.95</v>
+        <v>12.14</v>
       </c>
       <c r="CD2" t="n">
-        <v>11.07</v>
+        <v>26.1</v>
       </c>
       <c r="CE2" t="n">
-        <v>1304032</v>
+        <v>1035447</v>
       </c>
       <c r="CF2" t="n">
-        <v>513.27</v>
+        <v>464.11</v>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
@@ -1384,13 +1384,17 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; 3/3 fortress layers at vpoc floor</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: analysts/institutional investor meet/con. call upd; 3/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CJ2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>⚠️ ROUND_TRIP_RISK — close 471 &lt; 90% of 544</t>
+        </is>
+      </c>
       <c r="CK2" t="b">
         <v>1</v>
       </c>
@@ -1401,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="CN2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO2" t="b">
         <v>1</v>
@@ -1413,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="CR2" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
@@ -1433,10 +1437,10 @@
         </is>
       </c>
       <c r="CX2" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="CY2" t="n">
-        <v>535.41</v>
+        <v>516.3099999999999</v>
       </c>
       <c r="CZ2" t="b">
         <v>0</v>
@@ -1445,23 +1449,23 @@
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>504.35</v>
+        <v>434.56</v>
       </c>
       <c r="DC2" t="n">
-        <v>504.35</v>
+        <v>434.56</v>
       </c>
       <c r="DD2" t="n">
-        <v>667.25</v>
+        <v>603.34</v>
       </c>
       <c r="DE2" t="n">
-        <v>821.23</v>
+        <v>742.58</v>
       </c>
       <c r="DF2" t="n">
-        <v>1026.54</v>
+        <v>928.22</v>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹513.27</t>
+          <t>Sell 30% | Move stop to T1 ₹464.11</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
@@ -1475,11 +1479,11 @@
         </is>
       </c>
       <c r="DJ2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>🔵 PROBE — SMALL BUY ₹508.14</t>
+          <t>🟡 MARGINAL — BUY LIMIT ₹461.79</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
@@ -1488,10 +1492,10 @@
         </is>
       </c>
       <c r="DM2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DN2" t="n">
-        <v>508.1373</v>
+        <v>461.78945</v>
       </c>
       <c r="DO2" t="b">
         <v>0</v>
@@ -1500,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="DQ2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR2" t="b">
         <v>1</v>
@@ -1509,21 +1513,21 @@
         <v>1</v>
       </c>
       <c r="DT2" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="DU2" t="n">
-        <v>37949</v>
+        <v>29679</v>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>73 sh | ₹37,949 | 25% deploy | Risk ₹1,616</t>
+          <t>63 sh | ₹29,679 | 50% deploy | Risk ₹3,289</t>
         </is>
       </c>
       <c r="DW2" t="n">
-        <v>0.32</v>
+        <v>0.66</v>
       </c>
       <c r="DX2" t="n">
-        <v>22.14</v>
+        <v>52.2</v>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
@@ -1534,16 +1538,16 @@
         <v>1</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.28</v>
+        <v>18.73</v>
       </c>
       <c r="EB2" t="n">
-        <v>-1.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ELGIEQUIP</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1552,71 +1556,71 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>518.5</v>
+        <v>407.85</v>
       </c>
       <c r="D3" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E3" t="n">
         <v>200</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>🟠 MODERATE</t>
+          <t>🟡 HIGH</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>QTR 25%</t>
+          <t>HALF 50%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M3" t="n">
-        <v>505.17</v>
+        <v>388.33</v>
       </c>
       <c r="N3" t="n">
-        <v>543.13</v>
+        <v>426.53</v>
       </c>
       <c r="O3" t="n">
-        <v>495.51</v>
+        <v>390.42</v>
       </c>
       <c r="P3" t="n">
-        <v>656.72</v>
+        <v>504.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>808.27</v>
+        <v>621.33</v>
       </c>
       <c r="R3" t="n">
-        <v>1010.34</v>
+        <v>776.66</v>
       </c>
       <c r="S3" t="n">
-        <v>4.43</v>
+        <v>4.27</v>
       </c>
       <c r="T3" t="n">
-        <v>3.38</v>
+        <v>3.51</v>
       </c>
       <c r="U3" t="n">
-        <v>58.8</v>
+        <v>40.7</v>
       </c>
       <c r="V3" t="n">
-        <v>33.2</v>
+        <v>19.9</v>
       </c>
       <c r="W3" t="n">
-        <v>30.7</v>
+        <v>32.1</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1640,7 +1644,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>₹492.37–₹518.22</t>
+          <t>₹378.84–₹398.14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1652,7 +1656,7 @@
         <v>1.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>4.31</v>
+        <v>4.57</v>
       </c>
       <c r="AF3" t="b">
         <v>0</v>
@@ -1664,7 +1668,7 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>8.140000000000001</v>
+        <v>28.85</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1676,12 +1680,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1691,17 +1695,17 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>No recent filing</t>
+          <t>Record date [SHEETS Tab 4] | ✅ ROE(proxy) 11.3% [ACCEPTABLE] | D/E:160.1</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Results in 11td — acceptable window</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>ROE(proxy) 11.3% [ACCEPTABLE] | D/E:160.1</t>
         </is>
       </c>
       <c r="AR3" t="b">
@@ -1709,7 +1713,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>52W: 14.8% from ₹608 [APPROACHING HIGH] +3pts</t>
+          <t>52W: 12.3% from ₹465 [APPROACHING HIGH] +3pts</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1717,7 +1721,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>ATR-V: -2% compressed [EXPANDING]</t>
+          <t>ATR-V: -28% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV3" t="n">
@@ -1752,25 +1756,25 @@
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>495.51</v>
+        <v>390.42</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>Initial stop ₹495.51</t>
+          <t>Initial stop ₹390.42</t>
         </is>
       </c>
       <c r="BI3" t="b">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>326</v>
+        <v>430</v>
       </c>
       <c r="BK3" t="n">
-        <v>169031</v>
+        <v>175375.5</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>326 shares · ₹169,031  (risk ₹7,500)</t>
+          <t>430 shares · ₹175,376  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -1785,23 +1789,19 @@
         </is>
       </c>
       <c r="BP3" t="n">
-        <v>51</v>
+        <v>54.6</v>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 51.0%</t>
+          <t>⚠️ MC survival 54.6%</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>ACCUMULATION</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>🟢 CVD Accum — smart money</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr"/>
       <c r="BT3" t="b">
         <v>0</v>
       </c>
@@ -1826,16 +1826,16 @@
         <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.55</v>
+        <v>-3.32</v>
       </c>
       <c r="CD3" t="n">
-        <v>16.42</v>
+        <v>12.45</v>
       </c>
       <c r="CE3" t="n">
-        <v>380227</v>
+        <v>8387416</v>
       </c>
       <c r="CF3" t="n">
-        <v>505.17</v>
+        <v>388.33</v>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
@@ -1844,13 +1844,17 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: record date [sheets tab 4] | ✅ roe(proxy) 11.3% [a</t>
         </is>
       </c>
       <c r="CI3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CJ3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>⚠️ ROUND_TRIP_RISK — close 408 &lt; 90% of 465</t>
+        </is>
+      </c>
       <c r="CK3" t="b">
         <v>0</v>
       </c>
@@ -1861,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="CN3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO3" t="b">
         <v>1</v>
@@ -1873,30 +1877,30 @@
         <v>0</v>
       </c>
       <c r="CR3" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.3</v>
+        <v>0.263</v>
       </c>
       <c r="CU3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="CV3" t="n">
         <v>-5</v>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 30% — LOW</t>
+          <t>🧠 Sniper Bayes 26% — LOW</t>
         </is>
       </c>
       <c r="CX3" t="n">
         <v>55</v>
       </c>
       <c r="CY3" t="n">
-        <v>538.01</v>
+        <v>413.23</v>
       </c>
       <c r="CZ3" t="b">
         <v>0</v>
@@ -1905,23 +1909,23 @@
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>495.51</v>
+        <v>390.42</v>
       </c>
       <c r="DC3" t="n">
-        <v>495.51</v>
+        <v>390.42</v>
       </c>
       <c r="DD3" t="n">
-        <v>656.72</v>
+        <v>504.83</v>
       </c>
       <c r="DE3" t="n">
-        <v>808.27</v>
+        <v>621.33</v>
       </c>
       <c r="DF3" t="n">
-        <v>1010.34</v>
+        <v>776.66</v>
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹505.17</t>
+          <t>Sell 30% | Move stop to T1 ₹388.33</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
@@ -1935,11 +1939,11 @@
         </is>
       </c>
       <c r="DJ3" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 55/100 · +2.6% vs T1</t>
+          <t>👁️ WATCHING — score 55/100 · +5.0% vs T1</t>
         </is>
       </c>
       <c r="DL3" t="inlineStr">
@@ -1981,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>32.84</v>
+        <v>24.9</v>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
@@ -1992,10 +1996,10 @@
         <v>1</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.28</v>
+        <v>18.73</v>
       </c>
       <c r="EB3" t="n">
-        <v>-1.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="4">
@@ -2010,29 +2014,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>91.11</v>
+        <v>92.94</v>
       </c>
       <c r="D4" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E4" t="n">
         <v>200</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>🔵 PROBE</t>
+          <t>🟠 MODERATE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>PROBE 10%</t>
+          <t>QTR 25%</t>
         </is>
       </c>
       <c r="H4" t="n">
+        <v>26</v>
+      </c>
+      <c r="I4" t="n">
         <v>30</v>
-      </c>
-      <c r="I4" t="n">
-        <v>12</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -2047,10 +2051,10 @@
         <v>78.36</v>
       </c>
       <c r="N4" t="n">
-        <v>94.27</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>89.53</v>
+        <v>91.03</v>
       </c>
       <c r="P4" t="n">
         <v>101.87</v>
@@ -2062,19 +2066,19 @@
         <v>156.72</v>
       </c>
       <c r="S4" t="n">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="T4" t="n">
-        <v>8.65</v>
+        <v>7.3</v>
       </c>
       <c r="U4" t="n">
-        <v>57.7</v>
+        <v>68.3</v>
       </c>
       <c r="V4" t="n">
-        <v>35.8</v>
+        <v>63.2</v>
       </c>
       <c r="W4" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -2088,7 +2092,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>NEUTRAL ↔</t>
+          <t>DISTRIBUTION 🔴</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -2098,7 +2102,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>₹76.91–₹80.05</t>
+          <t>₹76.64–₹80.22</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2110,7 +2114,7 @@
         <v>0.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>16.3</v>
+        <v>18.49</v>
       </c>
       <c r="AF4" t="b">
         <v>0</v>
@@ -2122,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="AI4" t="n">
-        <v>378.59</v>
+        <v>61.39</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -2134,12 +2138,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2149,7 +2153,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>No recent filing</t>
+          <t>Copy of newspaper publication [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -2167,7 +2171,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>52W: 1.8% from ₹93 [AT 52W HIGH] +9pts</t>
+          <t>52W: -0.2% from ₹93 [AT 52W HIGH] +9pts</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -2175,11 +2179,11 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>ATR-V: 14% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: -16% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
@@ -2189,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
@@ -2210,25 +2214,25 @@
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>89.53</v>
+        <v>91.03</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>Initial stop ₹89.53</t>
+          <t>Initial stop ₹91.03</t>
         </is>
       </c>
       <c r="BI4" t="b">
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>4739</v>
+        <v>3937</v>
       </c>
       <c r="BK4" t="n">
-        <v>431770.29</v>
+        <v>365904.78</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>4739 shares · ₹431,770  (risk ₹7,500)</t>
+          <t>3937 shares · ₹365,905  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -2243,11 +2247,11 @@
         </is>
       </c>
       <c r="BP4" t="n">
-        <v>0.8</v>
+        <v>17.2</v>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 0.8%</t>
+          <t>⚠️ MC survival 17.2%</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2280,13 +2284,13 @@
         <v>1</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.18</v>
+        <v>6.62</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.11</v>
+        <v>2.54</v>
       </c>
       <c r="CE4" t="n">
-        <v>23051911</v>
+        <v>24073621</v>
       </c>
       <c r="CF4" t="n">
         <v>78.36</v>
@@ -2298,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: copy of newspaper publication [sheets tab 4]</t>
         </is>
       </c>
       <c r="CI4" t="b">
@@ -2347,10 +2351,10 @@
         </is>
       </c>
       <c r="CX4" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="CY4" t="n">
-        <v>82.58</v>
+        <v>83.44</v>
       </c>
       <c r="CZ4" t="b">
         <v>1</v>
@@ -2359,10 +2363,10 @@
         <v>1</v>
       </c>
       <c r="DB4" t="n">
-        <v>89.53</v>
+        <v>91.03</v>
       </c>
       <c r="DC4" t="n">
-        <v>89.53</v>
+        <v>91.03</v>
       </c>
       <c r="DD4" t="n">
         <v>101.87</v>
@@ -2389,11 +2393,11 @@
         </is>
       </c>
       <c r="DJ4" t="n">
-        <v>16.3</v>
+        <v>18.6</v>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 50/100 · +16.3% vs T1</t>
+          <t>👁️ WATCHING — score 34/100 · +18.6% vs T1</t>
         </is>
       </c>
       <c r="DL4" t="inlineStr">
@@ -2435,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>4.22</v>
+        <v>5.08</v>
       </c>
       <c r="DY4" t="inlineStr">
         <is>
@@ -2446,10 +2450,10 @@
         <v>1</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.28</v>
+        <v>18.73</v>
       </c>
       <c r="EB4" t="n">
-        <v>-1.83</v>
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -2463,7 +2467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EB16"/>
+  <dimension ref="A1:EB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3131,7 +3135,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3140,29 +3144,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>519.85</v>
+        <v>471.1</v>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="E2" t="n">
         <v>200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>🟡 HIGH</t>
+          <t>🟢 PRISTINE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HALF 50%</t>
+          <t>FULL 100%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -3171,40 +3175,40 @@
         <v>15</v>
       </c>
       <c r="L2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M2" t="n">
-        <v>513.27</v>
+        <v>464.11</v>
       </c>
       <c r="N2" t="n">
-        <v>536.45</v>
+        <v>510.25</v>
       </c>
       <c r="O2" t="n">
-        <v>504.35</v>
+        <v>434.56</v>
       </c>
       <c r="P2" t="n">
-        <v>667.25</v>
+        <v>603.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>821.23</v>
+        <v>742.58</v>
       </c>
       <c r="R2" t="n">
-        <v>1026.54</v>
+        <v>928.22</v>
       </c>
       <c r="S2" t="n">
-        <v>2.98</v>
+        <v>7.76</v>
       </c>
       <c r="T2" t="n">
-        <v>5.03</v>
+        <v>1.93</v>
       </c>
       <c r="U2" t="n">
-        <v>45.5</v>
+        <v>70.5</v>
       </c>
       <c r="V2" t="n">
-        <v>50.3</v>
+        <v>48.1</v>
       </c>
       <c r="W2" t="n">
-        <v>56.8</v>
+        <v>35.7</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -3218,7 +3222,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>NEUTRAL ↔</t>
+          <t>DISTRIBUTION 🔴</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3228,7 +3232,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>₹504.53–₹523.87</t>
+          <t>₹443.54–₹481.61</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3240,7 +3244,7 @@
         <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.31</v>
+        <v>-4.66</v>
       </c>
       <c r="AF2" t="b">
         <v>1</v>
@@ -3252,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>100.29</v>
+        <v>1.65</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -3264,12 +3268,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -3279,12 +3283,12 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>No recent filing</t>
+          <t>Analysts/institutional investor meet/con. call updates [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Results in 9td — caution</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -3297,7 +3301,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>52W: 20.3% from ₹652 [20% from 52W high] +0pts</t>
+          <t>52W: 39.9% from ₹784 [40% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -3305,21 +3309,25 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>ATR-V: 9% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: -17% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>🌀 VDU 5-bar deep coil (+7pts)</t>
+        </is>
+      </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
@@ -3340,25 +3348,25 @@
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>504.35</v>
+        <v>434.56</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>Initial stop ₹504.35</t>
+          <t>Initial stop ₹434.56</t>
         </is>
       </c>
       <c r="BI2" t="b">
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>483</v>
+        <v>205</v>
       </c>
       <c r="BK2" t="n">
-        <v>251087.55</v>
+        <v>96575.5</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>483 shares · ₹251,088  (risk ₹7,500)</t>
+          <t>205 shares · ₹96,576  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BM2" t="n">
@@ -3373,23 +3381,19 @@
         </is>
       </c>
       <c r="BP2" t="n">
-        <v>26.2</v>
+        <v>46.6</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 26.2%</t>
+          <t>⚠️ MC survival 46.6%</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>DISTRIBUTION</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>🔴 CVD Diverge — distribution</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr"/>
       <c r="BT2" t="b">
         <v>0</v>
       </c>
@@ -3411,19 +3415,19 @@
       </c>
       <c r="CA2" t="inlineStr"/>
       <c r="CB2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>7.95</v>
+        <v>12.14</v>
       </c>
       <c r="CD2" t="n">
-        <v>11.07</v>
+        <v>26.1</v>
       </c>
       <c r="CE2" t="n">
-        <v>1304032</v>
+        <v>1035447</v>
       </c>
       <c r="CF2" t="n">
-        <v>513.27</v>
+        <v>464.11</v>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
@@ -3432,13 +3436,17 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; 3/3 fortress layers at vpoc floor</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: analysts/institutional investor meet/con. call upd; 3/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CJ2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>⚠️ ROUND_TRIP_RISK — close 471 &lt; 90% of 544</t>
+        </is>
+      </c>
       <c r="CK2" t="b">
         <v>1</v>
       </c>
@@ -3449,7 +3457,7 @@
         <v>1</v>
       </c>
       <c r="CN2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO2" t="b">
         <v>1</v>
@@ -3461,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="CR2" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
@@ -3481,10 +3489,10 @@
         </is>
       </c>
       <c r="CX2" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="CY2" t="n">
-        <v>535.41</v>
+        <v>516.3099999999999</v>
       </c>
       <c r="CZ2" t="b">
         <v>0</v>
@@ -3493,23 +3501,23 @@
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>504.35</v>
+        <v>434.56</v>
       </c>
       <c r="DC2" t="n">
-        <v>504.35</v>
+        <v>434.56</v>
       </c>
       <c r="DD2" t="n">
-        <v>667.25</v>
+        <v>603.34</v>
       </c>
       <c r="DE2" t="n">
-        <v>821.23</v>
+        <v>742.58</v>
       </c>
       <c r="DF2" t="n">
-        <v>1026.54</v>
+        <v>928.22</v>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹513.27</t>
+          <t>Sell 30% | Move stop to T1 ₹464.11</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
@@ -3523,11 +3531,11 @@
         </is>
       </c>
       <c r="DJ2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>🔵 PROBE — SMALL BUY ₹508.14</t>
+          <t>🟡 MARGINAL — BUY LIMIT ₹461.79</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
@@ -3536,10 +3544,10 @@
         </is>
       </c>
       <c r="DM2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DN2" t="n">
-        <v>508.1373</v>
+        <v>461.78945</v>
       </c>
       <c r="DO2" t="b">
         <v>0</v>
@@ -3548,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="DQ2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR2" t="b">
         <v>1</v>
@@ -3557,21 +3565,21 @@
         <v>1</v>
       </c>
       <c r="DT2" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="DU2" t="n">
-        <v>37949</v>
+        <v>29679</v>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>73 sh | ₹37,949 | 25% deploy | Risk ₹1,616</t>
+          <t>63 sh | ₹29,679 | 50% deploy | Risk ₹3,289</t>
         </is>
       </c>
       <c r="DW2" t="n">
-        <v>0.32</v>
+        <v>0.66</v>
       </c>
       <c r="DX2" t="n">
-        <v>22.14</v>
+        <v>52.2</v>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
@@ -3582,16 +3590,16 @@
         <v>1</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.28</v>
+        <v>18.73</v>
       </c>
       <c r="EB2" t="n">
-        <v>-1.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ELGIEQUIP</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3600,71 +3608,71 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>518.5</v>
+        <v>407.85</v>
       </c>
       <c r="D3" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E3" t="n">
         <v>200</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>🟠 MODERATE</t>
+          <t>🟡 HIGH</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>QTR 25%</t>
+          <t>HALF 50%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M3" t="n">
-        <v>505.17</v>
+        <v>388.33</v>
       </c>
       <c r="N3" t="n">
-        <v>543.13</v>
+        <v>426.53</v>
       </c>
       <c r="O3" t="n">
-        <v>495.51</v>
+        <v>390.42</v>
       </c>
       <c r="P3" t="n">
-        <v>656.72</v>
+        <v>504.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>808.27</v>
+        <v>621.33</v>
       </c>
       <c r="R3" t="n">
-        <v>1010.34</v>
+        <v>776.66</v>
       </c>
       <c r="S3" t="n">
-        <v>4.43</v>
+        <v>4.27</v>
       </c>
       <c r="T3" t="n">
-        <v>3.38</v>
+        <v>3.51</v>
       </c>
       <c r="U3" t="n">
-        <v>58.8</v>
+        <v>40.7</v>
       </c>
       <c r="V3" t="n">
-        <v>33.2</v>
+        <v>19.9</v>
       </c>
       <c r="W3" t="n">
-        <v>30.7</v>
+        <v>32.1</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -3688,7 +3696,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>₹492.37–₹518.22</t>
+          <t>₹378.84–₹398.14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3700,7 +3708,7 @@
         <v>1.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>4.31</v>
+        <v>4.57</v>
       </c>
       <c r="AF3" t="b">
         <v>0</v>
@@ -3712,7 +3720,7 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>8.140000000000001</v>
+        <v>28.85</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -3724,12 +3732,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -3739,17 +3747,17 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>No recent filing</t>
+          <t>Record date [SHEETS Tab 4] | ✅ ROE(proxy) 11.3% [ACCEPTABLE] | D/E:160.1</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Results in 11td — acceptable window</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>ROE(proxy) 11.3% [ACCEPTABLE] | D/E:160.1</t>
         </is>
       </c>
       <c r="AR3" t="b">
@@ -3757,7 +3765,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>52W: 14.8% from ₹608 [APPROACHING HIGH] +3pts</t>
+          <t>52W: 12.3% from ₹465 [APPROACHING HIGH] +3pts</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -3765,7 +3773,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>ATR-V: -2% compressed [EXPANDING]</t>
+          <t>ATR-V: -28% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV3" t="n">
@@ -3800,25 +3808,25 @@
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>495.51</v>
+        <v>390.42</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>Initial stop ₹495.51</t>
+          <t>Initial stop ₹390.42</t>
         </is>
       </c>
       <c r="BI3" t="b">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>326</v>
+        <v>430</v>
       </c>
       <c r="BK3" t="n">
-        <v>169031</v>
+        <v>175375.5</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>326 shares · ₹169,031  (risk ₹7,500)</t>
+          <t>430 shares · ₹175,376  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BM3" t="n">
@@ -3833,23 +3841,19 @@
         </is>
       </c>
       <c r="BP3" t="n">
-        <v>51</v>
+        <v>54.6</v>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 51.0%</t>
+          <t>⚠️ MC survival 54.6%</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>ACCUMULATION</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>🟢 CVD Accum — smart money</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr"/>
       <c r="BT3" t="b">
         <v>0</v>
       </c>
@@ -3874,16 +3878,16 @@
         <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.55</v>
+        <v>-3.32</v>
       </c>
       <c r="CD3" t="n">
-        <v>16.42</v>
+        <v>12.45</v>
       </c>
       <c r="CE3" t="n">
-        <v>380227</v>
+        <v>8387416</v>
       </c>
       <c r="CF3" t="n">
-        <v>505.17</v>
+        <v>388.33</v>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
@@ -3892,13 +3896,17 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: record date [sheets tab 4] | ✅ roe(proxy) 11.3% [a</t>
         </is>
       </c>
       <c r="CI3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CJ3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>⚠️ ROUND_TRIP_RISK — close 408 &lt; 90% of 465</t>
+        </is>
+      </c>
       <c r="CK3" t="b">
         <v>0</v>
       </c>
@@ -3909,7 +3917,7 @@
         <v>1</v>
       </c>
       <c r="CN3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO3" t="b">
         <v>1</v>
@@ -3921,30 +3929,30 @@
         <v>0</v>
       </c>
       <c r="CR3" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.3</v>
+        <v>0.263</v>
       </c>
       <c r="CU3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="CV3" t="n">
         <v>-5</v>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 30% — LOW</t>
+          <t>🧠 Sniper Bayes 26% — LOW</t>
         </is>
       </c>
       <c r="CX3" t="n">
         <v>55</v>
       </c>
       <c r="CY3" t="n">
-        <v>538.01</v>
+        <v>413.23</v>
       </c>
       <c r="CZ3" t="b">
         <v>0</v>
@@ -3953,23 +3961,23 @@
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>495.51</v>
+        <v>390.42</v>
       </c>
       <c r="DC3" t="n">
-        <v>495.51</v>
+        <v>390.42</v>
       </c>
       <c r="DD3" t="n">
-        <v>656.72</v>
+        <v>504.83</v>
       </c>
       <c r="DE3" t="n">
-        <v>808.27</v>
+        <v>621.33</v>
       </c>
       <c r="DF3" t="n">
-        <v>1010.34</v>
+        <v>776.66</v>
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹505.17</t>
+          <t>Sell 30% | Move stop to T1 ₹388.33</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
@@ -3983,11 +3991,11 @@
         </is>
       </c>
       <c r="DJ3" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 55/100 · +2.6% vs T1</t>
+          <t>👁️ WATCHING — score 55/100 · +5.0% vs T1</t>
         </is>
       </c>
       <c r="DL3" t="inlineStr">
@@ -4029,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>32.84</v>
+        <v>24.9</v>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
@@ -4040,16 +4048,16 @@
         <v>1</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.28</v>
+        <v>18.73</v>
       </c>
       <c r="EB3" t="n">
-        <v>-1.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4058,29 +4066,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>404.45</v>
+        <v>495.65</v>
       </c>
       <c r="D4" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="E4" t="n">
         <v>200</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>🟠 MODERATE</t>
+          <t>🟡 HIGH</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>QTR 25%</t>
+          <t>HALF 50%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4092,37 +4100,37 @@
         <v>20</v>
       </c>
       <c r="M4" t="n">
-        <v>388.33</v>
+        <v>482.44</v>
       </c>
       <c r="N4" t="n">
-        <v>419.63</v>
+        <v>516.29</v>
       </c>
       <c r="O4" t="n">
-        <v>390.28</v>
+        <v>476.39</v>
       </c>
       <c r="P4" t="n">
-        <v>504.83</v>
+        <v>627.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>621.33</v>
+        <v>771.9</v>
       </c>
       <c r="R4" t="n">
-        <v>776.66</v>
+        <v>964.88</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="T4" t="n">
-        <v>4.28</v>
+        <v>3.86</v>
       </c>
       <c r="U4" t="n">
-        <v>45.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>27.5</v>
+        <v>40.4</v>
       </c>
       <c r="W4" t="n">
-        <v>26.2</v>
+        <v>32.3</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -4136,7 +4144,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>NEUTRAL ↔</t>
+          <t>DISTRIBUTION 🔴</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4146,7 +4154,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>₹380.56–₹397.07</t>
+          <t>₹471.73–₹493.96</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4158,7 +4166,7 @@
         <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.7</v>
+        <v>5.72</v>
       </c>
       <c r="AF4" t="b">
         <v>0</v>
@@ -4170,7 +4178,7 @@
         <v>1</v>
       </c>
       <c r="AI4" t="n">
-        <v>849.34</v>
+        <v>9.75</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -4182,12 +4190,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -4197,7 +4205,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>No recent filing</t>
+          <t>Analysts/institutional investor meet/con. call updates [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -4215,15 +4223,15 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>52W: 13.0% from ₹465 [APPROACHING HIGH] +3pts</t>
+          <t>52W: 7.3% from ₹535 [NEAR 52W HIGH] +5pts</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>ATR-V: 4% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: 8% compressed [🌀 COILING (+4pts)]</t>
         </is>
       </c>
       <c r="AV4" t="n">
@@ -4237,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
@@ -4258,25 +4266,25 @@
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>390.28</v>
+        <v>476.39</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>Initial stop ₹390.28</t>
+          <t>Initial stop ₹476.39</t>
         </is>
       </c>
       <c r="BI4" t="b">
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>529</v>
+        <v>389</v>
       </c>
       <c r="BK4" t="n">
-        <v>213954.05</v>
+        <v>192807.85</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>529 shares · ₹213,954  (risk ₹7,500)</t>
+          <t>389 shares · ₹192,808  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BM4" t="n">
@@ -4291,11 +4299,11 @@
         </is>
       </c>
       <c r="BP4" t="n">
-        <v>83.8</v>
+        <v>33.8</v>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>✅ MC survival 83.8% (500 sims, 20d)</t>
+          <t>⚠️ MC survival 33.8%</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -4325,19 +4333,19 @@
       </c>
       <c r="CA4" t="inlineStr"/>
       <c r="CB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC4" t="n">
-        <v>-1.25</v>
+        <v>11.24</v>
       </c>
       <c r="CD4" t="n">
-        <v>10.12</v>
+        <v>13.76</v>
       </c>
       <c r="CE4" t="n">
-        <v>8220035</v>
+        <v>8333845</v>
       </c>
       <c r="CF4" t="n">
-        <v>388.33</v>
+        <v>482.44</v>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
@@ -4346,17 +4354,13 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: analysts/institutional investor meet/con. call upd</t>
         </is>
       </c>
       <c r="CI4" t="b">
-        <v>1</v>
-      </c>
-      <c r="CJ4" t="inlineStr">
-        <is>
-          <t>⚠️ ROUND_TRIP_RISK — close 404 &lt; 90% of 465</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="CJ4" t="inlineStr"/>
       <c r="CK4" t="b">
         <v>0</v>
       </c>
@@ -4385,24 +4389,24 @@
         <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.132</v>
+        <v>0.241</v>
       </c>
       <c r="CU4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="CV4" t="n">
         <v>-5</v>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 13% — LOW</t>
+          <t>🧠 Sniper Bayes 24% — LOW</t>
         </is>
       </c>
       <c r="CX4" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="CY4" t="n">
-        <v>408.57</v>
+        <v>509.96</v>
       </c>
       <c r="CZ4" t="b">
         <v>0</v>
@@ -4411,23 +4415,23 @@
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>390.28</v>
+        <v>476.39</v>
       </c>
       <c r="DC4" t="n">
-        <v>390.28</v>
+        <v>476.39</v>
       </c>
       <c r="DD4" t="n">
-        <v>504.83</v>
+        <v>627.17</v>
       </c>
       <c r="DE4" t="n">
-        <v>621.33</v>
+        <v>771.9</v>
       </c>
       <c r="DF4" t="n">
-        <v>776.66</v>
+        <v>964.88</v>
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹388.33</t>
+          <t>Sell 30% | Move stop to T1 ₹482.44</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
@@ -4441,11 +4445,11 @@
         </is>
       </c>
       <c r="DJ4" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 55/100 · +4.2% vs T1</t>
+          <t>👁️ WATCHING — score 49/100 · +2.7% vs T1</t>
         </is>
       </c>
       <c r="DL4" t="inlineStr">
@@ -4487,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>20.24</v>
+        <v>27.52</v>
       </c>
       <c r="DY4" t="inlineStr">
         <is>
@@ -4498,16 +4502,16 @@
         <v>1</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.28</v>
+        <v>18.73</v>
       </c>
       <c r="EB4" t="n">
-        <v>-1.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MARSONS</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4516,29 +4520,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>144.86</v>
+        <v>527.6</v>
       </c>
       <c r="D5" t="n">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="E5" t="n">
         <v>200</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🟠 MODERATE</t>
+          <t>🟡 HIGH</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>QTR 25%</t>
+          <t>HALF 50%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4547,40 +4551,40 @@
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M5" t="n">
-        <v>161.83</v>
+        <v>513.27</v>
       </c>
       <c r="N5" t="n">
-        <v>161.29</v>
+        <v>544.54</v>
       </c>
       <c r="O5" t="n">
-        <v>133.91</v>
+        <v>511.79</v>
       </c>
       <c r="P5" t="n">
-        <v>210.38</v>
+        <v>667.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>258.93</v>
+        <v>821.23</v>
       </c>
       <c r="R5" t="n">
-        <v>323.66</v>
+        <v>1026.54</v>
       </c>
       <c r="S5" t="n">
-        <v>7.56</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.98</v>
+        <v>5.01</v>
       </c>
       <c r="U5" t="n">
-        <v>43.9</v>
+        <v>53.9</v>
       </c>
       <c r="V5" t="n">
-        <v>37</v>
+        <v>54.5</v>
       </c>
       <c r="W5" t="n">
-        <v>26.1</v>
+        <v>51</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -4599,24 +4603,24 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>BELOW</t>
+          <t>ABOVE</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>₹153.74–₹168.30</t>
+          <t>₹504.48–₹523.90</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ATR-1.00× stop</t>
+          <t>ATR-1.40× stop</t>
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF5" t="b">
         <v>0</v>
@@ -4628,11 +4632,11 @@
         <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>36.85</v>
+        <v>3.69</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>MA50</t>
+          <t>MA200</t>
         </is>
       </c>
       <c r="AK5" t="n">
@@ -4640,12 +4644,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -4655,12 +4659,12 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>No recent filing</t>
+          <t>General updates [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>Results in 8td — caution</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -4673,7 +4677,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>52W: 17.4% from ₹175 [17% from 52W high] +0pts</t>
+          <t>52W: 19.1% from ₹652 [19% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -4681,11 +4685,11 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>ATR-V: insufficient data</t>
+          <t>ATR-V: 6% compressed [COMPRESSING (+2pts)]</t>
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
@@ -4695,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
@@ -4716,25 +4720,25 @@
         </is>
       </c>
       <c r="BG5" t="n">
-        <v>133.91</v>
+        <v>511.79</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>Initial stop ₹133.91</t>
+          <t>Initial stop ₹511.79</t>
         </is>
       </c>
       <c r="BI5" t="b">
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>684</v>
+        <v>474</v>
       </c>
       <c r="BK5" t="n">
-        <v>99084.24000000001</v>
+        <v>250082.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>684 shares · ₹99,084  (risk ₹7,500)</t>
+          <t>474 shares · ₹250,082  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BM5" t="n">
@@ -4749,19 +4753,23 @@
         </is>
       </c>
       <c r="BP5" t="n">
-        <v>39</v>
+        <v>24.8</v>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 39.0%</t>
+          <t>⚠️ MC survival 24.8%</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr"/>
+          <t>DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>🔴 CVD Diverge — distribution</t>
+        </is>
+      </c>
       <c r="BT5" t="b">
         <v>0</v>
       </c>
@@ -4786,16 +4794,16 @@
         <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-4.06</v>
+        <v>7.85</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.95</v>
+        <v>11.29</v>
       </c>
       <c r="CE5" t="n">
-        <v>1946762</v>
+        <v>1332993</v>
       </c>
       <c r="CF5" t="n">
-        <v>161.83</v>
+        <v>513.27</v>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
@@ -4804,7 +4812,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: general updates [sheets tab 4]; 2/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CI5" t="b">
@@ -4824,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="CO5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP5" t="b">
         <v>1</v>
@@ -4833,30 +4841,30 @@
         <v>0</v>
       </c>
       <c r="CR5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="CS5" t="n">
         <v>0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.263</v>
+        <v>0.241</v>
       </c>
       <c r="CU5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="CV5" t="n">
         <v>-5</v>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 26% — LOW</t>
+          <t>🧠 Sniper Bayes 24% — LOW</t>
         </is>
       </c>
       <c r="CX5" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="CY5" t="n">
-        <v>183.73</v>
+        <v>535.85</v>
       </c>
       <c r="CZ5" t="b">
         <v>0</v>
@@ -4865,23 +4873,23 @@
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>133.91</v>
+        <v>511.79</v>
       </c>
       <c r="DC5" t="n">
-        <v>133.91</v>
+        <v>511.79</v>
       </c>
       <c r="DD5" t="n">
-        <v>210.38</v>
+        <v>667.25</v>
       </c>
       <c r="DE5" t="n">
-        <v>258.93</v>
+        <v>821.23</v>
       </c>
       <c r="DF5" t="n">
-        <v>323.66</v>
+        <v>1026.54</v>
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹161.83</t>
+          <t>Sell 30% | Move stop to T1 ₹513.27</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
@@ -4895,11 +4903,11 @@
         </is>
       </c>
       <c r="DJ5" t="n">
-        <v>-10.5</v>
+        <v>2.8</v>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 55/100 · -10.5% vs T1</t>
+          <t>👁️ WATCHING — score 43/100 · +2.8% vs T1</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
@@ -4941,7 +4949,7 @@
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>21.9</v>
+        <v>22.58</v>
       </c>
       <c r="DY5" t="inlineStr">
         <is>
@@ -4952,16 +4960,16 @@
         <v>1</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.28</v>
+        <v>18.73</v>
       </c>
       <c r="EB5" t="n">
-        <v>-1.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4970,71 +4978,71 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>489.15</v>
+        <v>368.15</v>
       </c>
       <c r="D6" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="E6" t="n">
         <v>200</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>🟠 MODERATE</t>
+          <t>🟡 HIGH</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>QTR 25%</t>
+          <t>HALF 50%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
         <v>20</v>
       </c>
       <c r="M6" t="n">
-        <v>470.15</v>
+        <v>378.73</v>
       </c>
       <c r="N6" t="n">
-        <v>509.7</v>
+        <v>391.1</v>
       </c>
       <c r="O6" t="n">
-        <v>469.97</v>
+        <v>346.73</v>
       </c>
       <c r="P6" t="n">
-        <v>611.1900000000001</v>
+        <v>492.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>752.24</v>
+        <v>605.97</v>
       </c>
       <c r="R6" t="n">
-        <v>940.3</v>
+        <v>757.46</v>
       </c>
       <c r="S6" t="n">
-        <v>3.92</v>
+        <v>5.82</v>
       </c>
       <c r="T6" t="n">
-        <v>3.83</v>
+        <v>2.58</v>
       </c>
       <c r="U6" t="n">
-        <v>69.40000000000001</v>
+        <v>49.1</v>
       </c>
       <c r="V6" t="n">
-        <v>39.4</v>
+        <v>55.7</v>
       </c>
       <c r="W6" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -5048,17 +5056,17 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>DISTRIBUTION 🔴</t>
+          <t>NEUTRAL ↔</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>ABOVE</t>
+          <t>PRISTINE</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>₹459.62–₹481.44</t>
+          <t>₹366.14–₹390.39</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5070,7 +5078,7 @@
         <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>4.33</v>
+        <v>-2.22</v>
       </c>
       <c r="AF6" t="b">
         <v>0</v>
@@ -5082,7 +5090,7 @@
         <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>193.56</v>
+        <v>1.94</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -5094,12 +5102,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -5109,7 +5117,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Interim dividend - re 0.50 per share [SHEETS Tab 4] | ⚠️ ROCE unverifiable — filing capped</t>
+          <t>Updates [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -5119,7 +5127,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>ROE quality data unavailable</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="AR6" t="b">
@@ -5127,19 +5135,19 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>52W: 8.5% from ₹535 [NEAR 52W HIGH] +5pts</t>
+          <t>52W: 25.6% from ₹495 [26% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>ATR-V: 10% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: -12% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
@@ -5149,7 +5157,7 @@
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
@@ -5170,25 +5178,25 @@
         </is>
       </c>
       <c r="BG6" t="n">
-        <v>469.97</v>
+        <v>346.73</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>Initial stop ₹469.97</t>
+          <t>Initial stop ₹346.73</t>
         </is>
       </c>
       <c r="BI6" t="b">
         <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>391</v>
+        <v>350</v>
       </c>
       <c r="BK6" t="n">
-        <v>191257.65</v>
+        <v>128852.5</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>391 shares · ₹191,258  (risk ₹7,500)</t>
+          <t>350 shares · ₹128,852  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BM6" t="n">
@@ -5203,19 +5211,23 @@
         </is>
       </c>
       <c r="BP6" t="n">
-        <v>51</v>
+        <v>46.2</v>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 51.0%</t>
+          <t>⚠️ MC survival 46.2%</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr"/>
+          <t>ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>🟢 CVD Accum — smart money</t>
+        </is>
+      </c>
       <c r="BT6" t="b">
         <v>0</v>
       </c>
@@ -5240,16 +5252,16 @@
         <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>13.6</v>
+        <v>13.22</v>
       </c>
       <c r="CD6" t="n">
-        <v>13.7</v>
+        <v>15.3</v>
       </c>
       <c r="CE6" t="n">
-        <v>8527081</v>
+        <v>591987</v>
       </c>
       <c r="CF6" t="n">
-        <v>470.15</v>
+        <v>378.73</v>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
@@ -5258,7 +5270,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>Recent filing: interim dividend - re 0.50 per share [sheets tab 4</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: updates [sheets tab 4]</t>
         </is>
       </c>
       <c r="CI6" t="b">
@@ -5278,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="CO6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP6" t="b">
         <v>1</v>
@@ -5287,30 +5299,30 @@
         <v>0</v>
       </c>
       <c r="CR6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="CS6" t="n">
         <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.241</v>
+        <v>0.495</v>
       </c>
       <c r="CU6" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="CV6" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 24% — LOW</t>
+          <t>🧠 Sniper Bayes 50% — neutral</t>
         </is>
       </c>
       <c r="CX6" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="CY6" t="n">
-        <v>497.55</v>
+        <v>409.33</v>
       </c>
       <c r="CZ6" t="b">
         <v>0</v>
@@ -5319,23 +5331,23 @@
         <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>469.97</v>
+        <v>346.73</v>
       </c>
       <c r="DC6" t="n">
-        <v>469.97</v>
+        <v>346.73</v>
       </c>
       <c r="DD6" t="n">
-        <v>611.1900000000001</v>
+        <v>492.35</v>
       </c>
       <c r="DE6" t="n">
-        <v>752.24</v>
+        <v>605.97</v>
       </c>
       <c r="DF6" t="n">
-        <v>940.3</v>
+        <v>757.46</v>
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹470.15</t>
+          <t>Sell 30% | Move stop to T1 ₹378.73</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
@@ -5349,11 +5361,11 @@
         </is>
       </c>
       <c r="DJ6" t="n">
-        <v>4</v>
+        <v>-2.8</v>
       </c>
       <c r="DK6" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 55/100 · +4.0% vs T1</t>
+          <t>👁️ WATCHING — score 43/100 · -2.8% vs T1</t>
         </is>
       </c>
       <c r="DL6" t="inlineStr">
@@ -5395,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>27.4</v>
+        <v>30.6</v>
       </c>
       <c r="DY6" t="inlineStr">
         <is>
@@ -5406,16 +5418,16 @@
         <v>1</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.28</v>
+        <v>18.73</v>
       </c>
       <c r="EB6" t="n">
-        <v>-1.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NOCIL</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5424,29 +5436,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>168.77</v>
+        <v>743.8</v>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E7" t="n">
         <v>200</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🔵 PROBE</t>
+          <t>🟠 MODERATE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PROBE 10%</t>
+          <t>QTR 25%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -5458,37 +5470,37 @@
         <v>20</v>
       </c>
       <c r="M7" t="n">
-        <v>160.38</v>
+        <v>574.03</v>
       </c>
       <c r="N7" t="n">
-        <v>180.21</v>
+        <v>778.85</v>
       </c>
       <c r="O7" t="n">
-        <v>161.14</v>
+        <v>711.08</v>
       </c>
       <c r="P7" t="n">
-        <v>208.49</v>
+        <v>746.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>256.61</v>
+        <v>918.45</v>
       </c>
       <c r="R7" t="n">
-        <v>320.76</v>
+        <v>1148.06</v>
       </c>
       <c r="S7" t="n">
-        <v>4.52</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="U7" t="n">
-        <v>62.3</v>
+        <v>88.3</v>
       </c>
       <c r="V7" t="n">
-        <v>27.6</v>
+        <v>59.8</v>
       </c>
       <c r="W7" t="n">
-        <v>51.4</v>
+        <v>65.8</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -5512,19 +5524,19 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>₹154.58–₹165.61</t>
+          <t>₹559.60–₹588.79</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ATR-1.00× stop</t>
+          <t>ATR-1.40× stop</t>
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.69</v>
+        <v>30.66</v>
       </c>
       <c r="AF7" t="b">
         <v>0</v>
@@ -5536,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.7</v>
+        <v>3.69</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -5548,12 +5560,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -5563,7 +5575,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>No recent filing</t>
+          <t>Analysts/institutional investor meet/con. call updates [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -5581,15 +5593,15 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>52W: 20.0% from ₹211 [20% from 52W high] +0pts</t>
+          <t>52W: 2.3% from ₹761 [AT 52W HIGH] +9pts</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>ATR-V: -19% compressed [EXPANDING]</t>
+          <t>ATR-V: -8% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV7" t="n">
@@ -5607,7 +5619,7 @@
         <v>3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
@@ -5628,25 +5640,25 @@
         </is>
       </c>
       <c r="BG7" t="n">
-        <v>161.14</v>
+        <v>711.08</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>Initial stop ₹161.14</t>
+          <t>Initial stop ₹711.08</t>
         </is>
       </c>
       <c r="BI7" t="b">
         <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>982</v>
+        <v>229</v>
       </c>
       <c r="BK7" t="n">
-        <v>165732.14</v>
+        <v>170330.2</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>982 shares · ₹165,732  (risk ₹7,500)</t>
+          <t>229 shares · ₹170,330  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BM7" t="n">
@@ -5661,11 +5673,11 @@
         </is>
       </c>
       <c r="BP7" t="n">
-        <v>27.8</v>
+        <v>41.4</v>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 27.8%</t>
+          <t>⚠️ MC survival 41.4%</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -5695,19 +5707,19 @@
       </c>
       <c r="CA7" t="inlineStr"/>
       <c r="CB7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.86</v>
+        <v>13.97</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.63</v>
+        <v>23.37</v>
       </c>
       <c r="CE7" t="n">
-        <v>954628</v>
+        <v>1711708</v>
       </c>
       <c r="CF7" t="n">
-        <v>160.38</v>
+        <v>574.03</v>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
@@ -5716,17 +5728,13 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: analysts/institutional investor meet/con. call upd</t>
         </is>
       </c>
       <c r="CI7" t="b">
-        <v>1</v>
-      </c>
-      <c r="CJ7" t="inlineStr">
-        <is>
-          <t>⚠️ ROUND_TRIP_RISK — close 169 &lt; 90% of 192</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="inlineStr"/>
       <c r="CK7" t="b">
         <v>0</v>
       </c>
@@ -5755,49 +5763,49 @@
         <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.132</v>
+        <v>0.143</v>
       </c>
       <c r="CU7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CV7" t="n">
         <v>-5</v>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 13% — LOW</t>
+          <t>🧠 Sniper Bayes 14% — LOW</t>
         </is>
       </c>
       <c r="CX7" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="CY7" t="n">
-        <v>175.64</v>
+        <v>620.77</v>
       </c>
       <c r="CZ7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB7" t="n">
-        <v>161.14</v>
+        <v>711.08</v>
       </c>
       <c r="DC7" t="n">
-        <v>161.14</v>
+        <v>711.08</v>
       </c>
       <c r="DD7" t="n">
-        <v>208.49</v>
+        <v>746.24</v>
       </c>
       <c r="DE7" t="n">
-        <v>256.61</v>
+        <v>918.45</v>
       </c>
       <c r="DF7" t="n">
-        <v>320.76</v>
+        <v>1148.06</v>
       </c>
       <c r="DG7" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹160.38</t>
+          <t>Sell 30% | Move stop to T1 ₹574.03</t>
         </is>
       </c>
       <c r="DH7" t="inlineStr">
@@ -5811,11 +5819,11 @@
         </is>
       </c>
       <c r="DJ7" t="n">
-        <v>5.2</v>
+        <v>29.6</v>
       </c>
       <c r="DK7" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 55/100 · +5.2% vs T1</t>
+          <t>👁️ WATCHING — score 43/100 · +29.6% vs T1</t>
         </is>
       </c>
       <c r="DL7" t="inlineStr">
@@ -5857,7 +5865,7 @@
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.26</v>
+        <v>46.74</v>
       </c>
       <c r="DY7" t="inlineStr">
         <is>
@@ -5868,47 +5876,47 @@
         <v>1</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.28</v>
+        <v>18.73</v>
       </c>
       <c r="EB7" t="n">
-        <v>-1.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>91.11</v>
+        <v>127.61</v>
       </c>
       <c r="D8" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E8" t="n">
         <v>200</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🔵 PROBE</t>
+          <t>🟠 MODERATE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PROBE 10%</t>
+          <t>QTR 25%</t>
         </is>
       </c>
       <c r="H8" t="n">
+        <v>36</v>
+      </c>
+      <c r="I8" t="n">
         <v>30</v>
-      </c>
-      <c r="I8" t="n">
-        <v>12</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -5917,44 +5925,44 @@
         <v>15</v>
       </c>
       <c r="L8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>78.36</v>
+        <v>118.56</v>
       </c>
       <c r="N8" t="n">
-        <v>94.27</v>
+        <v>133.99</v>
       </c>
       <c r="O8" t="n">
-        <v>89.53</v>
+        <v>123.35</v>
       </c>
       <c r="P8" t="n">
-        <v>101.87</v>
+        <v>154.13</v>
       </c>
       <c r="Q8" t="n">
-        <v>125.38</v>
+        <v>189.7</v>
       </c>
       <c r="R8" t="n">
-        <v>156.72</v>
+        <v>237.12</v>
       </c>
       <c r="S8" t="n">
-        <v>1.73</v>
+        <v>3.34</v>
       </c>
       <c r="T8" t="n">
-        <v>8.65</v>
+        <v>4.49</v>
       </c>
       <c r="U8" t="n">
-        <v>57.7</v>
+        <v>42.4</v>
       </c>
       <c r="V8" t="n">
-        <v>35.8</v>
+        <v>52</v>
       </c>
       <c r="W8" t="n">
-        <v>22.8</v>
+        <v>27.2</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>TRANSITION</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -5974,19 +5982,19 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>₹76.91–₹80.05</t>
+          <t>₹115.40–₹121.72</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ATR-0.75× stop</t>
+          <t>ATR-1.00× stop</t>
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>16.3</v>
+        <v>13.4</v>
       </c>
       <c r="AF8" t="b">
         <v>0</v>
@@ -5998,7 +6006,7 @@
         <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>378.59</v>
+        <v>7.26</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -6006,16 +6014,16 @@
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -6025,12 +6033,12 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>No recent filing</t>
+          <t>General updates [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>⚠️ Results in 5td — risky, size to PROBE</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -6043,19 +6051,19 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>52W: 1.8% from ₹93 [AT 52W HIGH] +9pts</t>
+          <t>52W: 6.3% from ₹136 [NEAR 52W HIGH] +5pts</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>ATR-V: 14% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: 2% compressed [COMPRESSING (+2pts)]</t>
         </is>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
@@ -6065,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
@@ -6086,25 +6094,25 @@
         </is>
       </c>
       <c r="BG8" t="n">
-        <v>89.53</v>
+        <v>123.35</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>Initial stop ₹89.53</t>
+          <t>Initial stop ₹123.35</t>
         </is>
       </c>
       <c r="BI8" t="b">
         <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>4739</v>
+        <v>1760</v>
       </c>
       <c r="BK8" t="n">
-        <v>431770.29</v>
+        <v>224593.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>4739 shares · ₹431,770  (risk ₹7,500)</t>
+          <t>1760 shares · ₹224,594  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BM8" t="n">
@@ -6119,11 +6127,11 @@
         </is>
       </c>
       <c r="BP8" t="n">
-        <v>0.8</v>
+        <v>35</v>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 0.8%</t>
+          <t>⚠️ MC survival 35.0%</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -6153,19 +6161,19 @@
       </c>
       <c r="CA8" t="inlineStr"/>
       <c r="CB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>6.18</v>
+        <v>3.29</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.11</v>
+        <v>4.26</v>
       </c>
       <c r="CE8" t="n">
-        <v>23051911</v>
+        <v>18317845</v>
       </c>
       <c r="CF8" t="n">
-        <v>78.36</v>
+        <v>118.56</v>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
@@ -6174,7 +6182,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: general updates [sheets tab 4]</t>
         </is>
       </c>
       <c r="CI8" t="b">
@@ -6209,49 +6217,49 @@
         <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.111</v>
+        <v>0.263</v>
       </c>
       <c r="CU8" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="CV8" t="n">
         <v>-5</v>
       </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 11% — LOW</t>
+          <t>🧠 Sniper Bayes 26% — LOW</t>
         </is>
       </c>
       <c r="CX8" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="CY8" t="n">
-        <v>82.58</v>
+        <v>127.08</v>
       </c>
       <c r="CZ8" t="b">
         <v>1</v>
       </c>
       <c r="DA8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>89.53</v>
+        <v>123.35</v>
       </c>
       <c r="DC8" t="n">
-        <v>89.53</v>
+        <v>123.35</v>
       </c>
       <c r="DD8" t="n">
-        <v>101.87</v>
+        <v>154.13</v>
       </c>
       <c r="DE8" t="n">
-        <v>125.38</v>
+        <v>189.7</v>
       </c>
       <c r="DF8" t="n">
-        <v>156.72</v>
+        <v>237.12</v>
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹78.36</t>
+          <t>Sell 30% | Move stop to T1 ₹118.56</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
@@ -6265,11 +6273,11 @@
         </is>
       </c>
       <c r="DJ8" t="n">
-        <v>16.3</v>
+        <v>7.6</v>
       </c>
       <c r="DK8" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 50/100 · +16.3% vs T1</t>
+          <t>👁️ WATCHING — score 43/100 · +7.6% vs T1</t>
         </is>
       </c>
       <c r="DL8" t="inlineStr">
@@ -6311,7 +6319,7 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>4.22</v>
+        <v>8.52</v>
       </c>
       <c r="DY8" t="inlineStr">
         <is>
@@ -6322,16 +6330,16 @@
         <v>1</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.28</v>
+        <v>18.73</v>
       </c>
       <c r="EB8" t="n">
-        <v>-1.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6340,71 +6348,71 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>126.32</v>
+        <v>574</v>
       </c>
       <c r="D9" t="n">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="E9" t="n">
         <v>200</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🔵 PROBE</t>
+          <t>🟡 HIGH</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PROBE 10%</t>
+          <t>HALF 50%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M9" t="n">
-        <v>117.49</v>
+        <v>471.59</v>
       </c>
       <c r="N9" t="n">
-        <v>132.83</v>
+        <v>609.72</v>
       </c>
       <c r="O9" t="n">
-        <v>121.98</v>
+        <v>540.66</v>
       </c>
       <c r="P9" t="n">
-        <v>152.74</v>
+        <v>613.0700000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>187.98</v>
+        <v>754.54</v>
       </c>
       <c r="R9" t="n">
-        <v>234.98</v>
+        <v>943.1799999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>3.44</v>
+        <v>5.81</v>
       </c>
       <c r="T9" t="n">
-        <v>4.37</v>
+        <v>2.58</v>
       </c>
       <c r="U9" t="n">
-        <v>40.8</v>
+        <v>92.5</v>
       </c>
       <c r="V9" t="n">
-        <v>46.7</v>
+        <v>77.8</v>
       </c>
       <c r="W9" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -6418,7 +6426,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>NEUTRAL ↔</t>
+          <t>DISTRIBUTION 🔴</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -6428,31 +6436,31 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>₹114.26–₹120.68</t>
+          <t>₹455.94–₹486.09</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ATR-1.00× stop</t>
+          <t>ATR-1.40× stop</t>
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>12.38</v>
+        <v>17.21</v>
       </c>
       <c r="AF9" t="b">
         <v>0</v>
       </c>
       <c r="AG9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="b">
         <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>189.6</v>
+        <v>55.5</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -6464,12 +6472,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -6479,17 +6487,17 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>No recent filing</t>
+          <t>Record date [SHEETS Tab 4] | ⚠️ ROCE unverifiable — filing capped</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Results in 6td — caution</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>ROE quality data unavailable</t>
         </is>
       </c>
       <c r="AR9" t="b">
@@ -6497,15 +6505,15 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>52W: 7.2% from ₹136 [NEAR 52W HIGH] +5pts</t>
+          <t>52W: 0.2% from ₹575 [AT 52W HIGH] +9pts</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>ATR-V: -2% compressed [EXPANDING]</t>
+          <t>ATR-V: -45% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV9" t="n">
@@ -6519,7 +6527,7 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
@@ -6540,25 +6548,25 @@
         </is>
       </c>
       <c r="BG9" t="n">
-        <v>121.98</v>
+        <v>540.66</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>Initial stop ₹121.98</t>
+          <t>Initial stop ₹540.66</t>
         </is>
       </c>
       <c r="BI9" t="b">
         <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1728</v>
+        <v>224</v>
       </c>
       <c r="BK9" t="n">
-        <v>218280.96</v>
+        <v>128576</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1728 shares · ₹218,281  (risk ₹7,500)</t>
+          <t>224 shares · ₹128,576  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BM9" t="n">
@@ -6573,23 +6581,19 @@
         </is>
       </c>
       <c r="BP9" t="n">
-        <v>31.6</v>
+        <v>27.2</v>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 31.6%</t>
+          <t>⚠️ MC survival 27.2%</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>ACCUMULATION</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>🟢 CVD Accum — smart money</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr"/>
       <c r="BT9" t="b">
         <v>0</v>
       </c>
@@ -6607,23 +6611,27 @@
       </c>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="b">
-        <v>0</v>
-      </c>
-      <c r="CA9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>🚨 EXIT_LIQUIDITY (3/5) — upper wick 2×body · RSI 78&gt;70 · close&gt;VPOC+3ATR</t>
+        </is>
+      </c>
       <c r="CB9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.05</v>
+        <v>20.2</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.34</v>
+        <v>23.82</v>
       </c>
       <c r="CE9" t="n">
-        <v>18810817</v>
+        <v>671227</v>
       </c>
       <c r="CF9" t="n">
-        <v>117.49</v>
+        <v>471.59</v>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
@@ -6632,7 +6640,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: record date [sheets tab 4] | ⚠️ roce unverifiable ; 2/3 fortress layers at vpoc floor</t>
         </is>
       </c>
       <c r="CI9" t="b">
@@ -6667,49 +6675,49 @@
         <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.708</v>
+        <v>0.241</v>
       </c>
       <c r="CU9" t="n">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="CV9" t="n">
-        <v>8</v>
+        <v>-5</v>
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 71% — HIGH</t>
+          <t>🧠 Sniper Bayes 24% — LOW</t>
         </is>
       </c>
       <c r="CX9" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="CY9" t="n">
-        <v>126.17</v>
+        <v>519.23</v>
       </c>
       <c r="CZ9" t="b">
         <v>1</v>
       </c>
       <c r="DA9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB9" t="n">
-        <v>121.98</v>
+        <v>540.66</v>
       </c>
       <c r="DC9" t="n">
-        <v>121.98</v>
+        <v>540.66</v>
       </c>
       <c r="DD9" t="n">
-        <v>152.74</v>
+        <v>613.0700000000001</v>
       </c>
       <c r="DE9" t="n">
-        <v>187.98</v>
+        <v>754.54</v>
       </c>
       <c r="DF9" t="n">
-        <v>234.98</v>
+        <v>943.1799999999999</v>
       </c>
       <c r="DG9" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹117.49</t>
+          <t>Sell 30% | Move stop to T1 ₹471.59</t>
         </is>
       </c>
       <c r="DH9" t="inlineStr">
@@ -6723,11 +6731,11 @@
         </is>
       </c>
       <c r="DJ9" t="n">
-        <v>7.5</v>
+        <v>21.7</v>
       </c>
       <c r="DK9" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 49/100 · +7.5% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +21.7% vs T1</t>
         </is>
       </c>
       <c r="DL9" t="inlineStr">
@@ -6769,7 +6777,7 @@
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.68</v>
+        <v>47.64</v>
       </c>
       <c r="DY9" t="inlineStr">
         <is>
@@ -6780,16 +6788,16 @@
         <v>1</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.28</v>
+        <v>18.73</v>
       </c>
       <c r="EB9" t="n">
-        <v>-1.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6798,29 +6806,29 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>108.27</v>
+        <v>203.48</v>
       </c>
       <c r="D10" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="E10" t="n">
         <v>200</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🔵 PROBE</t>
+          <t>🟠 MODERATE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PROBE 10%</t>
+          <t>QTR 25%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -6829,40 +6837,40 @@
         <v>15</v>
       </c>
       <c r="L10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M10" t="n">
-        <v>76.77</v>
+        <v>191.01</v>
       </c>
       <c r="N10" t="n">
-        <v>117.94</v>
+        <v>216.69</v>
       </c>
       <c r="O10" t="n">
-        <v>101.82</v>
+        <v>194.67</v>
       </c>
       <c r="P10" t="n">
-        <v>99.8</v>
+        <v>248.31</v>
       </c>
       <c r="Q10" t="n">
-        <v>122.83</v>
+        <v>305.62</v>
       </c>
       <c r="R10" t="n">
-        <v>153.54</v>
+        <v>382.02</v>
       </c>
       <c r="S10" t="n">
-        <v>5.96</v>
+        <v>4.33</v>
       </c>
       <c r="T10" t="n">
-        <v>2.52</v>
+        <v>3.46</v>
       </c>
       <c r="U10" t="n">
-        <v>64.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="V10" t="n">
-        <v>41.9</v>
+        <v>62.1</v>
       </c>
       <c r="W10" t="n">
-        <v>51.1</v>
+        <v>37.2</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -6886,7 +6894,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>₹73.11–₹79.82</t>
+          <t>₹184.40–₹197.05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -6898,7 +6906,7 @@
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>5.88</v>
+        <v>11.67</v>
       </c>
       <c r="AF10" t="b">
         <v>0</v>
@@ -6910,7 +6918,7 @@
         <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>46.37</v>
+        <v>5.38</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -6922,12 +6930,12 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -6942,7 +6950,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>No result date found (neutral)</t>
+          <t>Results in 9td — caution</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -6955,7 +6963,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>52W: 31.2% from ₹157 [31% from 52W high] +0pts</t>
+          <t>52W: 24.8% from ₹271 [25% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AT10" t="n">
@@ -6963,21 +6971,25 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>ATR-V: -14% compressed [EXPANDING]</t>
+          <t>ATR-V: -22% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
       </c>
-      <c r="AW10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>🌀 VDU 3-bar mild (+3pts)</t>
+        </is>
+      </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
@@ -6998,25 +7010,25 @@
         </is>
       </c>
       <c r="BG10" t="n">
-        <v>101.82</v>
+        <v>194.67</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>Initial stop ₹101.82</t>
+          <t>Initial stop ₹194.67</t>
         </is>
       </c>
       <c r="BI10" t="b">
         <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1162</v>
+        <v>851</v>
       </c>
       <c r="BK10" t="n">
-        <v>125809.74</v>
+        <v>173161.48</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1162 shares · ₹125,810  (risk ₹7,500)</t>
+          <t>851 shares · ₹173,161  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BM10" t="n">
@@ -7031,11 +7043,11 @@
         </is>
       </c>
       <c r="BP10" t="n">
-        <v>20.8</v>
+        <v>26.2</v>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 20.8%</t>
+          <t>⚠️ MC survival 26.2%</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -7068,16 +7080,16 @@
         <v>1</v>
       </c>
       <c r="CC10" t="n">
-        <v>35.98</v>
+        <v>13.73</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.45</v>
+        <v>8.81</v>
       </c>
       <c r="CE10" t="n">
-        <v>8936634</v>
+        <v>1655879</v>
       </c>
       <c r="CF10" t="n">
-        <v>76.77</v>
+        <v>191.01</v>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
@@ -7086,17 +7098,13 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: no recent filing</t>
         </is>
       </c>
       <c r="CI10" t="b">
-        <v>1</v>
-      </c>
-      <c r="CJ10" t="inlineStr">
-        <is>
-          <t>⚠️ ROUND_TRIP_RISK — close 108 &lt; 90% of 128</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="inlineStr"/>
       <c r="CK10" t="b">
         <v>0</v>
       </c>
@@ -7139,35 +7147,35 @@
         </is>
       </c>
       <c r="CX10" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="CY10" t="n">
-        <v>89.67</v>
+        <v>208.63</v>
       </c>
       <c r="CZ10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>101.82</v>
+        <v>194.67</v>
       </c>
       <c r="DC10" t="n">
-        <v>101.82</v>
+        <v>194.67</v>
       </c>
       <c r="DD10" t="n">
-        <v>99.8</v>
+        <v>248.31</v>
       </c>
       <c r="DE10" t="n">
-        <v>122.83</v>
+        <v>305.62</v>
       </c>
       <c r="DF10" t="n">
-        <v>153.54</v>
+        <v>382.02</v>
       </c>
       <c r="DG10" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹76.77</t>
+          <t>Sell 30% | Move stop to T1 ₹191.01</t>
         </is>
       </c>
       <c r="DH10" t="inlineStr">
@@ -7181,11 +7189,11 @@
         </is>
       </c>
       <c r="DJ10" t="n">
-        <v>41</v>
+        <v>6.5</v>
       </c>
       <c r="DK10" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 49/100 · +41.0% vs T1</t>
+          <t>👁️ WATCHING — score 39/100 · +6.5% vs T1</t>
         </is>
       </c>
       <c r="DL10" t="inlineStr">
@@ -7227,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.9</v>
+        <v>17.62</v>
       </c>
       <c r="DY10" t="inlineStr">
         <is>
@@ -7238,47 +7246,47 @@
         <v>1</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.28</v>
+        <v>18.73</v>
       </c>
       <c r="EB10" t="n">
-        <v>-1.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>219.62</v>
+        <v>53.78</v>
       </c>
       <c r="D11" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="E11" t="n">
         <v>200</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🔵 PROBE</t>
+          <t>🟠 MODERATE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PROBE 10%</t>
+          <t>QTR 25%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -7287,40 +7295,40 @@
         <v>15</v>
       </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M11" t="n">
-        <v>195.59</v>
+        <v>50.9</v>
       </c>
       <c r="N11" t="n">
-        <v>225.65</v>
+        <v>56.68</v>
       </c>
       <c r="O11" t="n">
-        <v>215.6</v>
+        <v>52.33</v>
       </c>
       <c r="P11" t="n">
-        <v>254.27</v>
+        <v>66.17</v>
       </c>
       <c r="Q11" t="n">
-        <v>312.94</v>
+        <v>81.44</v>
       </c>
       <c r="R11" t="n">
-        <v>391.18</v>
+        <v>101.8</v>
       </c>
       <c r="S11" t="n">
-        <v>1.83</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>8.19</v>
+        <v>5.57</v>
       </c>
       <c r="U11" t="n">
-        <v>51.9</v>
+        <v>49.6</v>
       </c>
       <c r="V11" t="n">
-        <v>48.5</v>
+        <v>46.8</v>
       </c>
       <c r="W11" t="n">
-        <v>30.2</v>
+        <v>33</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -7344,19 +7352,19 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>₹192.72–₹199.34</t>
+          <t>₹49.43–₹52.32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ATR-1.00× stop</t>
+          <t>ATR-0.75× stop</t>
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AE11" t="n">
-        <v>20.55</v>
+        <v>2.11</v>
       </c>
       <c r="AF11" t="b">
         <v>0</v>
@@ -7368,7 +7376,7 @@
         <v>1</v>
       </c>
       <c r="AI11" t="n">
-        <v>1007.2</v>
+        <v>27.8</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -7376,16 +7384,16 @@
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -7395,12 +7403,12 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>No recent filing</t>
+          <t>Esop/esos/esps [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>⚠️ Results in 3td — risky, size to PROBE</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -7413,19 +7421,19 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>52W: -0.2% from ₹219 [AT 52W HIGH] +9pts</t>
+          <t>52W: 27.6% from ₹74 [28% from 52W high] +0pts</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>ATR-V: 20% compressed [🌀 COILING (+4pts)]</t>
+          <t>ATR-V: -18% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="n">
@@ -7435,7 +7443,7 @@
         <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="n">
@@ -7456,25 +7464,25 @@
         </is>
       </c>
       <c r="BG11" t="n">
-        <v>215.6</v>
+        <v>52.33</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>Initial stop ₹215.60</t>
+          <t>Initial stop ₹52.33</t>
         </is>
       </c>
       <c r="BI11" t="b">
         <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1865</v>
+        <v>5154</v>
       </c>
       <c r="BK11" t="n">
-        <v>409591.3</v>
+        <v>277182.12</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1865 shares · ₹409,591  (risk ₹7,500)</t>
+          <t>5154 shares · ₹277,182  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BM11" t="n">
@@ -7489,11 +7497,11 @@
         </is>
       </c>
       <c r="BP11" t="n">
-        <v>5</v>
+        <v>21.4</v>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 5.0%</t>
+          <t>⚠️ MC survival 21.4%</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -7523,19 +7531,19 @@
       </c>
       <c r="CA11" t="inlineStr"/>
       <c r="CB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>6.41</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.02</v>
+        <v>1.94</v>
       </c>
       <c r="CE11" t="n">
-        <v>23134685</v>
+        <v>119958835</v>
       </c>
       <c r="CF11" t="n">
-        <v>195.59</v>
+        <v>50.9</v>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
@@ -7544,7 +7552,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: esop/esos/esps [sheets tab 4]</t>
         </is>
       </c>
       <c r="CI11" t="b">
@@ -7558,7 +7566,7 @@
         <v>0</v>
       </c>
       <c r="CM11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN11" t="b">
         <v>0</v>
@@ -7573,55 +7581,55 @@
         <v>0</v>
       </c>
       <c r="CR11" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="CS11" t="n">
         <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.241</v>
+        <v>0.098</v>
       </c>
       <c r="CU11" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CV11" t="n">
         <v>-5</v>
       </c>
       <c r="CW11" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 24% — LOW</t>
+          <t>🧠 Sniper Bayes 10% — LOW</t>
         </is>
       </c>
       <c r="CX11" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="CY11" t="n">
-        <v>203.63</v>
+        <v>54.78</v>
       </c>
       <c r="CZ11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA11" t="b">
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>215.6</v>
+        <v>52.33</v>
       </c>
       <c r="DC11" t="n">
-        <v>215.6</v>
+        <v>52.33</v>
       </c>
       <c r="DD11" t="n">
-        <v>254.27</v>
+        <v>66.17</v>
       </c>
       <c r="DE11" t="n">
-        <v>312.94</v>
+        <v>81.44</v>
       </c>
       <c r="DF11" t="n">
-        <v>391.18</v>
+        <v>101.8</v>
       </c>
       <c r="DG11" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹195.59</t>
+          <t>Sell 30% | Move stop to T1 ₹50.90</t>
         </is>
       </c>
       <c r="DH11" t="inlineStr">
@@ -7635,11 +7643,11 @@
         </is>
       </c>
       <c r="DJ11" t="n">
-        <v>12.3</v>
+        <v>5.7</v>
       </c>
       <c r="DK11" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 44/100 · +12.3% vs T1</t>
+          <t>👁️ WATCHING — score 36/100 · +5.7% vs T1</t>
         </is>
       </c>
       <c r="DL11" t="inlineStr">
@@ -7681,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>8.039999999999999</v>
+        <v>3.88</v>
       </c>
       <c r="DY11" t="inlineStr">
         <is>
@@ -7692,47 +7700,47 @@
         <v>1</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.28</v>
+        <v>18.73</v>
       </c>
       <c r="EB11" t="n">
-        <v>-1.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NAVA</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>693.1</v>
+        <v>92.94</v>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E12" t="n">
         <v>200</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🔵 PROBE</t>
+          <t>🟠 MODERATE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PROBE 10%</t>
+          <t>QTR 25%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -7741,44 +7749,44 @@
         <v>15</v>
       </c>
       <c r="L12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M12" t="n">
-        <v>595.04</v>
+        <v>78.36</v>
       </c>
       <c r="N12" t="n">
-        <v>731.3</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>657.45</v>
+        <v>91.03</v>
       </c>
       <c r="P12" t="n">
-        <v>773.55</v>
+        <v>101.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>952.0599999999999</v>
+        <v>125.38</v>
       </c>
       <c r="R12" t="n">
-        <v>1190.08</v>
+        <v>156.72</v>
       </c>
       <c r="S12" t="n">
-        <v>5.14</v>
+        <v>2.06</v>
       </c>
       <c r="T12" t="n">
-        <v>2.92</v>
+        <v>7.3</v>
       </c>
       <c r="U12" t="n">
-        <v>59.7</v>
+        <v>68.3</v>
       </c>
       <c r="V12" t="n">
-        <v>55.5</v>
+        <v>63.2</v>
       </c>
       <c r="W12" t="n">
-        <v>51.1</v>
+        <v>22.5</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>TRANSITION</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -7788,7 +7796,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>NEUTRAL ↔</t>
+          <t>DISTRIBUTION 🔴</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -7798,19 +7806,19 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>₹577.55–₹611.92</t>
+          <t>₹76.64–₹80.22</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ATR-1.40× stop</t>
+          <t>ATR-0.75× stop</t>
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>0.75</v>
       </c>
       <c r="AE12" t="n">
-        <v>14.99</v>
+        <v>18.49</v>
       </c>
       <c r="AF12" t="b">
         <v>0</v>
@@ -7822,7 +7830,7 @@
         <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>24.81</v>
+        <v>61.39</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -7830,16 +7838,16 @@
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -7849,12 +7857,12 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>No recent filing</t>
+          <t>Copy of newspaper publication [SHEETS Tab 4]</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>⚠️ Results in 3td — risky, size to PROBE</t>
+          <t>No result date found (neutral)</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -7867,33 +7875,29 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>52W: 6.3% from ₹739 [NEAR 52W HIGH] +5pts</t>
+          <t>52W: -0.2% from ₹93 [AT 52W HIGH] +9pts</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>ATR-V: -10% compressed [EXPANDING]</t>
+          <t>ATR-V: -16% compressed [EXPANDING]</t>
         </is>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
       </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>🌀 VDU 3-bar mild (+3pts)</t>
-        </is>
-      </c>
+      <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="n">
@@ -7914,25 +7918,25 @@
         </is>
       </c>
       <c r="BG12" t="n">
-        <v>657.45</v>
+        <v>91.03</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>Initial stop ₹657.45</t>
+          <t>Initial stop ₹91.03</t>
         </is>
       </c>
       <c r="BI12" t="b">
         <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>210</v>
+        <v>3937</v>
       </c>
       <c r="BK12" t="n">
-        <v>145551</v>
+        <v>365904.78</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>210 shares · ₹145,551  (risk ₹7,500)</t>
+          <t>3937 shares · ₹365,905  (risk ₹7,500)</t>
         </is>
       </c>
       <c r="BM12" t="n">
@@ -7947,11 +7951,11 @@
         </is>
       </c>
       <c r="BP12" t="n">
-        <v>63.2</v>
+        <v>17.2</v>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>⚠️ MC survival 63.2%</t>
+          <t>⚠️ MC survival 17.2%</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -7984,16 +7988,16 @@
         <v>1</v>
       </c>
       <c r="CC12" t="n">
-        <v>13.9</v>
+        <v>6.62</v>
       </c>
       <c r="CD12" t="n">
-        <v>25.47</v>
+        <v>2.54</v>
       </c>
       <c r="CE12" t="n">
-        <v>1942516</v>
+        <v>24073621</v>
       </c>
       <c r="CF12" t="n">
-        <v>595.04</v>
+        <v>78.36</v>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
@@ -8002,7 +8006,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>Recent filing: no recent filing</t>
+          <t>Institutional tide is in — fii+dii both accumulating; recent filing: copy of newspaper publication [sheets tab 4]</t>
         </is>
       </c>
       <c r="CI12" t="b">
@@ -8037,24 +8041,24 @@
         <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.241</v>
+        <v>0.111</v>
       </c>
       <c r="CU12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="CV12" t="n">
         <v>-5</v>
       </c>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>🧠 Sniper Bayes 24% — LOW</t>
+          <t>🧠 Sniper Bayes 11% — LOW</t>
         </is>
       </c>
       <c r="CX12" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="CY12" t="n">
-        <v>645.98</v>
+        <v>83.44</v>
       </c>
       <c r="CZ12" t="b">
         <v>1</v>
@@ -8063,23 +8067,23 @@
         <v>1</v>
       </c>
       <c r="DB12" t="n">
-        <v>657.45</v>
+        <v>91.03</v>
       </c>
       <c r="DC12" t="n">
-        <v>657.45</v>
+        <v>91.03</v>
       </c>
       <c r="DD12" t="n">
-        <v>773.55</v>
+        <v>101.87</v>
       </c>
       <c r="DE12" t="n">
-        <v>952.0599999999999</v>
+        <v>125.38</v>
       </c>
       <c r="DF12" t="n">
-        <v>1190.08</v>
+        <v>156.72</v>
       </c>
       <c r="DG12" t="inlineStr">
         <is>
-          <t>Sell 30% | Move stop to T1 ₹595.04</t>
+          <t>Sell 30% | Move stop to T1 ₹78.36</t>
         </is>
       </c>
       <c r="DH12" t="inlineStr">
@@ -8093,11 +8097,11 @@
         </is>
       </c>
       <c r="DJ12" t="n">
-        <v>16.5</v>
+        <v>18.6</v>
       </c>
       <c r="DK12" t="inlineStr">
         <is>
-          <t>👁️ WATCHING — score 43/100 · +16.5% vs T1</t>
+          <t>👁️ WATCHING — score 34/100 · +18.6% vs T1</t>
         </is>
       </c>
       <c r="DL12" t="inlineStr">
@@ -8139,7 +8143,7 @@
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>50.94</v>
+        <v>5.08</v>
       </c>
       <c r="DY12" t="inlineStr">
         <is>
@@ -8150,1826 +8154,10 @@
         <v>1</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.28</v>
+        <v>18.73</v>
       </c>
       <c r="EB12" t="n">
-        <v>-1.83</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SUZLON</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>DIVERSIFIED</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>82</v>
-      </c>
-      <c r="E13" t="n">
-        <v>200</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>🟠 MODERATE</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>QTR 25%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>40</v>
-      </c>
-      <c r="I13" t="n">
-        <v>12</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>15</v>
-      </c>
-      <c r="L13" t="n">
-        <v>20</v>
-      </c>
-      <c r="M13" t="n">
-        <v>50.88</v>
-      </c>
-      <c r="N13" t="n">
-        <v>55.89</v>
-      </c>
-      <c r="O13" t="n">
-        <v>51.71</v>
-      </c>
-      <c r="P13" t="n">
-        <v>66.14</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>81.41</v>
-      </c>
-      <c r="R13" t="n">
-        <v>101.76</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="U13" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>32</v>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>LOOSE</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>NEUTRAL ↔</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>ABOVE</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>₹49.45–₹52.28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ATR-0.75× stop</t>
-        </is>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AF13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>490.87</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>MA200</t>
-        </is>
-      </c>
-      <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>↔ MIXED</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>No insider trades in 30d</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>No recent filing</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>No result date found (neutral)</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>Not checked</t>
-        </is>
-      </c>
-      <c r="AR13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>52W: 28.5% from ₹74 [29% from 52W high] +0pts</t>
-        </is>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>ATR-V: -14% compressed [EXPANDING]</t>
-        </is>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>EOD_FRESH</t>
-        </is>
-      </c>
-      <c r="BD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>CLEAR</t>
-        </is>
-      </c>
-      <c r="BG13" t="n">
-        <v>51.71</v>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>Initial stop ₹51.71</t>
-        </is>
-      </c>
-      <c r="BI13" t="b">
-        <v>0</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>5376</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>285465.6</v>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>5376 shares · ₹285,466  (risk ₹7,500)</t>
-        </is>
-      </c>
-      <c r="BM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>—  (see sn_bayes_label for 9-node result)</t>
-        </is>
-      </c>
-      <c r="BP13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>⚠️ MC survival 6.4%</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr"/>
-      <c r="BT13" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU13" t="inlineStr"/>
-      <c r="BV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW13" t="inlineStr">
-        <is>
-          <t>Standard weights</t>
-        </is>
-      </c>
-      <c r="BX13" t="b">
-        <v>0</v>
-      </c>
-      <c r="BY13" t="inlineStr"/>
-      <c r="BZ13" t="b">
-        <v>0</v>
-      </c>
-      <c r="CA13" t="inlineStr"/>
-      <c r="CB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC13" t="n">
-        <v>15.79</v>
-      </c>
-      <c r="CD13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CE13" t="n">
-        <v>126074660</v>
-      </c>
-      <c r="CF13" t="n">
-        <v>50.88</v>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>Smallcap circuit breaker: data unavailable (pass)</t>
-        </is>
-      </c>
-      <c r="CH13" t="inlineStr">
-        <is>
-          <t>Recent filing: no recent filing</t>
-        </is>
-      </c>
-      <c r="CI13" t="b">
-        <v>0</v>
-      </c>
-      <c r="CJ13" t="inlineStr"/>
-      <c r="CK13" t="b">
-        <v>0</v>
-      </c>
-      <c r="CL13" t="b">
-        <v>0</v>
-      </c>
-      <c r="CM13" t="b">
-        <v>0</v>
-      </c>
-      <c r="CN13" t="b">
-        <v>0</v>
-      </c>
-      <c r="CO13" t="b">
-        <v>1</v>
-      </c>
-      <c r="CP13" t="b">
-        <v>1</v>
-      </c>
-      <c r="CQ13" t="b">
-        <v>0</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>10</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>-5</v>
-      </c>
-      <c r="CW13" t="inlineStr">
-        <is>
-          <t>🧠 Sniper Bayes 10% — LOW</t>
-        </is>
-      </c>
-      <c r="CX13" t="n">
-        <v>42</v>
-      </c>
-      <c r="CY13" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="CZ13" t="b">
-        <v>0</v>
-      </c>
-      <c r="DA13" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>51.71</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>51.71</v>
-      </c>
-      <c r="DD13" t="n">
-        <v>66.14</v>
-      </c>
-      <c r="DE13" t="n">
-        <v>81.41</v>
-      </c>
-      <c r="DF13" t="n">
-        <v>101.76</v>
-      </c>
-      <c r="DG13" t="inlineStr">
-        <is>
-          <t>Sell 30% | Move stop to T1 ₹50.88</t>
-        </is>
-      </c>
-      <c r="DH13" t="inlineStr">
-        <is>
-          <t>Sell 30% | Trail 2.5×ATR</t>
-        </is>
-      </c>
-      <c r="DI13" t="inlineStr">
-        <is>
-          <t>Sell 40% | Trail rest aggressively</t>
-        </is>
-      </c>
-      <c r="DJ13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="DK13" t="inlineStr">
-        <is>
-          <t>👁️ WATCHING — score 42/100 · +4.4% vs T1</t>
-        </is>
-      </c>
-      <c r="DL13" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="DM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN13" t="inlineStr"/>
-      <c r="DO13" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP13" t="b">
-        <v>0</v>
-      </c>
-      <c r="DQ13" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR13" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS13" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV13" t="inlineStr">
-        <is>
-          <t>— (below min)</t>
-        </is>
-      </c>
-      <c r="DW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX13" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="DY13" t="inlineStr">
-        <is>
-          <t>CHOP</t>
-        </is>
-      </c>
-      <c r="DZ13" t="b">
-        <v>1</v>
-      </c>
-      <c r="EA13" t="n">
-        <v>19.28</v>
-      </c>
-      <c r="EB13" t="n">
-        <v>-1.83</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DIVERSIFIED</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>728.35</v>
-      </c>
-      <c r="D14" t="n">
-        <v>96</v>
-      </c>
-      <c r="E14" t="n">
-        <v>200</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>🟠 MODERATE</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>QTR 25%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>54</v>
-      </c>
-      <c r="I14" t="n">
-        <v>12</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>15</v>
-      </c>
-      <c r="L14" t="n">
-        <v>20</v>
-      </c>
-      <c r="M14" t="n">
-        <v>574.03</v>
-      </c>
-      <c r="N14" t="n">
-        <v>764.26</v>
-      </c>
-      <c r="O14" t="n">
-        <v>694.83</v>
-      </c>
-      <c r="P14" t="n">
-        <v>746.24</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>918.45</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1148.06</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U14" t="n">
-        <v>91</v>
-      </c>
-      <c r="V14" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="W14" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>LOOSE</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>DISTRIBUTION 🔴</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>ABOVE</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>₹558.93–₹589.20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ATR-1.40× stop</t>
-        </is>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>28.21</v>
-      </c>
-      <c r="AF14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>40.68</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>MA200</t>
-        </is>
-      </c>
-      <c r="AK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>↔ MIXED</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>No insider trades in 30d</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>No recent filing</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>No result date found (neutral)</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>Not checked</t>
-        </is>
-      </c>
-      <c r="AR14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>52W: 4.3% from ₹761 [AT 52W HIGH] +9pts</t>
-        </is>
-      </c>
-      <c r="AT14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>ATR-V: -13% compressed [EXPANDING]</t>
-        </is>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>EOD_FRESH</t>
-        </is>
-      </c>
-      <c r="BD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>CLEAR</t>
-        </is>
-      </c>
-      <c r="BG14" t="n">
-        <v>694.83</v>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>Initial stop ₹694.83</t>
-        </is>
-      </c>
-      <c r="BI14" t="b">
-        <v>0</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>223</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>162422.05</v>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>223 shares · ₹162,422  (risk ₹7,500)</t>
-        </is>
-      </c>
-      <c r="BM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>—  (see sn_bayes_label for 9-node result)</t>
-        </is>
-      </c>
-      <c r="BP14" t="n">
-        <v>64</v>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>⚠️ MC survival 64.0%</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr"/>
-      <c r="BT14" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU14" t="inlineStr"/>
-      <c r="BV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW14" t="inlineStr">
-        <is>
-          <t>Standard weights</t>
-        </is>
-      </c>
-      <c r="BX14" t="b">
-        <v>0</v>
-      </c>
-      <c r="BY14" t="inlineStr"/>
-      <c r="BZ14" t="b">
-        <v>0</v>
-      </c>
-      <c r="CA14" t="inlineStr"/>
-      <c r="CB14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CC14" t="n">
-        <v>15.17</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>23.94</v>
-      </c>
-      <c r="CE14" t="n">
-        <v>1737701</v>
-      </c>
-      <c r="CF14" t="n">
-        <v>574.03</v>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>Smallcap circuit breaker: data unavailable (pass)</t>
-        </is>
-      </c>
-      <c r="CH14" t="inlineStr">
-        <is>
-          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor</t>
-        </is>
-      </c>
-      <c r="CI14" t="b">
-        <v>0</v>
-      </c>
-      <c r="CJ14" t="inlineStr"/>
-      <c r="CK14" t="b">
-        <v>0</v>
-      </c>
-      <c r="CL14" t="b">
-        <v>0</v>
-      </c>
-      <c r="CM14" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN14" t="b">
-        <v>0</v>
-      </c>
-      <c r="CO14" t="b">
-        <v>1</v>
-      </c>
-      <c r="CP14" t="b">
-        <v>1</v>
-      </c>
-      <c r="CQ14" t="b">
-        <v>0</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>40</v>
-      </c>
-      <c r="CS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT14" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="CU14" t="n">
-        <v>24</v>
-      </c>
-      <c r="CV14" t="n">
-        <v>-5</v>
-      </c>
-      <c r="CW14" t="inlineStr">
-        <is>
-          <t>🧠 Sniper Bayes 24% — LOW</t>
-        </is>
-      </c>
-      <c r="CX14" t="n">
-        <v>39</v>
-      </c>
-      <c r="CY14" t="n">
-        <v>621.91</v>
-      </c>
-      <c r="CZ14" t="b">
-        <v>1</v>
-      </c>
-      <c r="DA14" t="b">
-        <v>1</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>694.83</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>694.83</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>746.24</v>
-      </c>
-      <c r="DE14" t="n">
-        <v>918.45</v>
-      </c>
-      <c r="DF14" t="n">
-        <v>1148.06</v>
-      </c>
-      <c r="DG14" t="inlineStr">
-        <is>
-          <t>Sell 30% | Move stop to T1 ₹574.03</t>
-        </is>
-      </c>
-      <c r="DH14" t="inlineStr">
-        <is>
-          <t>Sell 30% | Trail 2.5×ATR</t>
-        </is>
-      </c>
-      <c r="DI14" t="inlineStr">
-        <is>
-          <t>Sell 40% | Trail rest aggressively</t>
-        </is>
-      </c>
-      <c r="DJ14" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="DK14" t="inlineStr">
-        <is>
-          <t>👁️ WATCHING — score 39/100 · +26.9% vs T1</t>
-        </is>
-      </c>
-      <c r="DL14" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="DM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN14" t="inlineStr"/>
-      <c r="DO14" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP14" t="b">
-        <v>0</v>
-      </c>
-      <c r="DQ14" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR14" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS14" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV14" t="inlineStr">
-        <is>
-          <t>— (below min)</t>
-        </is>
-      </c>
-      <c r="DW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX14" t="n">
-        <v>47.88</v>
-      </c>
-      <c r="DY14" t="inlineStr">
-        <is>
-          <t>CHOP</t>
-        </is>
-      </c>
-      <c r="DZ14" t="b">
-        <v>1</v>
-      </c>
-      <c r="EA14" t="n">
-        <v>19.28</v>
-      </c>
-      <c r="EB14" t="n">
-        <v>-1.83</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>METROPOLIS</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>DIVERSIFIED</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>548</v>
-      </c>
-      <c r="D15" t="n">
-        <v>96</v>
-      </c>
-      <c r="E15" t="n">
-        <v>200</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>🟠 MODERATE</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>QTR 25%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>54</v>
-      </c>
-      <c r="I15" t="n">
-        <v>12</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>15</v>
-      </c>
-      <c r="L15" t="n">
-        <v>20</v>
-      </c>
-      <c r="M15" t="n">
-        <v>471.59</v>
-      </c>
-      <c r="N15" t="n">
-        <v>585.11</v>
-      </c>
-      <c r="O15" t="n">
-        <v>513.36</v>
-      </c>
-      <c r="P15" t="n">
-        <v>613.0700000000001</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>754.54</v>
-      </c>
-      <c r="R15" t="n">
-        <v>943.1799999999999</v>
-      </c>
-      <c r="S15" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="U15" t="n">
-        <v>92</v>
-      </c>
-      <c r="V15" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="W15" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>LOOSE</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>DISTRIBUTION 🔴</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>ABOVE</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>₹454.56–₹486.95</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ATR-1.40× stop</t>
-        </is>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>11.97</v>
-      </c>
-      <c r="AF15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>16.58</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>MA200</t>
-        </is>
-      </c>
-      <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>↔ MIXED</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>No insider trades in 30d</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>No recent filing</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>No result date found (neutral)</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>Not checked</t>
-        </is>
-      </c>
-      <c r="AR15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>52W: 4.7% from ₹575 [AT 52W HIGH] +9pts</t>
-        </is>
-      </c>
-      <c r="AT15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>ATR-V: -62% compressed [EXPANDING]</t>
-        </is>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>EOD_FRESH</t>
-        </is>
-      </c>
-      <c r="BD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>CLEAR</t>
-        </is>
-      </c>
-      <c r="BG15" t="n">
-        <v>513.36</v>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>Initial stop ₹513.36</t>
-        </is>
-      </c>
-      <c r="BI15" t="b">
-        <v>0</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>216</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>118368</v>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>216 shares · ₹118,368  (risk ₹7,500)</t>
-        </is>
-      </c>
-      <c r="BM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>—  (see sn_bayes_label for 9-node result)</t>
-        </is>
-      </c>
-      <c r="BP15" t="n">
-        <v>73</v>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>✅ MC survival 73.0% (500 sims, 20d)</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr"/>
-      <c r="BT15" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU15" t="inlineStr"/>
-      <c r="BV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>Standard weights</t>
-        </is>
-      </c>
-      <c r="BX15" t="b">
-        <v>0</v>
-      </c>
-      <c r="BY15" t="inlineStr"/>
-      <c r="BZ15" t="b">
-        <v>0</v>
-      </c>
-      <c r="CA15" t="inlineStr"/>
-      <c r="CB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC15" t="n">
-        <v>18.52</v>
-      </c>
-      <c r="CD15" t="n">
-        <v>24.74</v>
-      </c>
-      <c r="CE15" t="n">
-        <v>667974</v>
-      </c>
-      <c r="CF15" t="n">
-        <v>471.59</v>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>Smallcap circuit breaker: data unavailable (pass)</t>
-        </is>
-      </c>
-      <c r="CH15" t="inlineStr">
-        <is>
-          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor</t>
-        </is>
-      </c>
-      <c r="CI15" t="b">
-        <v>0</v>
-      </c>
-      <c r="CJ15" t="inlineStr"/>
-      <c r="CK15" t="b">
-        <v>0</v>
-      </c>
-      <c r="CL15" t="b">
-        <v>0</v>
-      </c>
-      <c r="CM15" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN15" t="b">
-        <v>0</v>
-      </c>
-      <c r="CO15" t="b">
-        <v>1</v>
-      </c>
-      <c r="CP15" t="b">
-        <v>1</v>
-      </c>
-      <c r="CQ15" t="b">
-        <v>0</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>40</v>
-      </c>
-      <c r="CS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT15" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="CU15" t="n">
-        <v>24</v>
-      </c>
-      <c r="CV15" t="n">
-        <v>-5</v>
-      </c>
-      <c r="CW15" t="inlineStr">
-        <is>
-          <t>🧠 Sniper Bayes 24% — LOW</t>
-        </is>
-      </c>
-      <c r="CX15" t="n">
-        <v>39</v>
-      </c>
-      <c r="CY15" t="n">
-        <v>521.0700000000001</v>
-      </c>
-      <c r="CZ15" t="b">
-        <v>1</v>
-      </c>
-      <c r="DA15" t="b">
-        <v>1</v>
-      </c>
-      <c r="DB15" t="n">
-        <v>513.36</v>
-      </c>
-      <c r="DC15" t="n">
-        <v>513.36</v>
-      </c>
-      <c r="DD15" t="n">
-        <v>613.0700000000001</v>
-      </c>
-      <c r="DE15" t="n">
-        <v>754.54</v>
-      </c>
-      <c r="DF15" t="n">
-        <v>943.1799999999999</v>
-      </c>
-      <c r="DG15" t="inlineStr">
-        <is>
-          <t>Sell 30% | Move stop to T1 ₹471.59</t>
-        </is>
-      </c>
-      <c r="DH15" t="inlineStr">
-        <is>
-          <t>Sell 30% | Trail 2.5×ATR</t>
-        </is>
-      </c>
-      <c r="DI15" t="inlineStr">
-        <is>
-          <t>Sell 40% | Trail rest aggressively</t>
-        </is>
-      </c>
-      <c r="DJ15" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="DK15" t="inlineStr">
-        <is>
-          <t>👁️ WATCHING — score 39/100 · +16.2% vs T1</t>
-        </is>
-      </c>
-      <c r="DL15" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="DM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN15" t="inlineStr"/>
-      <c r="DO15" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP15" t="b">
-        <v>0</v>
-      </c>
-      <c r="DQ15" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR15" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS15" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV15" t="inlineStr">
-        <is>
-          <t>— (below min)</t>
-        </is>
-      </c>
-      <c r="DW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX15" t="n">
-        <v>49.48</v>
-      </c>
-      <c r="DY15" t="inlineStr">
-        <is>
-          <t>CHOP</t>
-        </is>
-      </c>
-      <c r="DZ15" t="b">
-        <v>1</v>
-      </c>
-      <c r="EA15" t="n">
-        <v>19.28</v>
-      </c>
-      <c r="EB15" t="n">
-        <v>-1.83</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MARKSANS</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>DIVERSIFIED</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>200.13</v>
-      </c>
-      <c r="D16" t="n">
-        <v>85</v>
-      </c>
-      <c r="E16" t="n">
-        <v>200</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>🟠 MODERATE</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>QTR 25%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>45</v>
-      </c>
-      <c r="I16" t="n">
-        <v>12</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>15</v>
-      </c>
-      <c r="L16" t="n">
-        <v>18</v>
-      </c>
-      <c r="M16" t="n">
-        <v>182.85</v>
-      </c>
-      <c r="N16" t="n">
-        <v>214</v>
-      </c>
-      <c r="O16" t="n">
-        <v>190.89</v>
-      </c>
-      <c r="P16" t="n">
-        <v>237.71</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>292.56</v>
-      </c>
-      <c r="R16" t="n">
-        <v>365.7</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U16" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="V16" t="n">
-        <v>60</v>
-      </c>
-      <c r="W16" t="n">
-        <v>37</v>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>LOOSE</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>DISTRIBUTION 🔴</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>ABOVE</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>₹176.09–₹188.90</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ATR-1.00× stop</t>
-        </is>
-      </c>
-      <c r="AD16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>9.69</v>
-      </c>
-      <c r="AF16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>21.24</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>MA200</t>
-        </is>
-      </c>
-      <c r="AK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>↔ MIXED</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>No insider trades in 30d</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>No recent filing</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>Results in 10td — caution</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>Not checked</t>
-        </is>
-      </c>
-      <c r="AR16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>52W: 26.1% from ₹271 [26% from 52W high] +0pts</t>
-        </is>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>ATR-V: -36% compressed [EXPANDING]</t>
-        </is>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>EOD_FRESH</t>
-        </is>
-      </c>
-      <c r="BD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>CLEAR</t>
-        </is>
-      </c>
-      <c r="BG16" t="n">
-        <v>190.89</v>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>Initial stop ₹190.89</t>
-        </is>
-      </c>
-      <c r="BI16" t="b">
-        <v>0</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>811</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>162305.43</v>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>811 shares · ₹162,305  (risk ₹7,500)</t>
-        </is>
-      </c>
-      <c r="BM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>—  (see sn_bayes_label for 9-node result)</t>
-        </is>
-      </c>
-      <c r="BP16" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>⚠️ MC survival 29.2%</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr"/>
-      <c r="BT16" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU16" t="inlineStr"/>
-      <c r="BV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW16" t="inlineStr">
-        <is>
-          <t>Standard weights</t>
-        </is>
-      </c>
-      <c r="BX16" t="b">
-        <v>0</v>
-      </c>
-      <c r="BY16" t="inlineStr"/>
-      <c r="BZ16" t="b">
-        <v>0</v>
-      </c>
-      <c r="CA16" t="inlineStr"/>
-      <c r="CB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>9.24</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>1633387</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>182.85</v>
-      </c>
-      <c r="CG16" t="inlineStr">
-        <is>
-          <t>Smallcap circuit breaker: data unavailable (pass)</t>
-        </is>
-      </c>
-      <c r="CH16" t="inlineStr">
-        <is>
-          <t>Recent filing: no recent filing; 2/3 fortress layers at vpoc floor</t>
-        </is>
-      </c>
-      <c r="CI16" t="b">
-        <v>0</v>
-      </c>
-      <c r="CJ16" t="inlineStr"/>
-      <c r="CK16" t="b">
-        <v>0</v>
-      </c>
-      <c r="CL16" t="b">
-        <v>0</v>
-      </c>
-      <c r="CM16" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN16" t="b">
-        <v>0</v>
-      </c>
-      <c r="CO16" t="b">
-        <v>1</v>
-      </c>
-      <c r="CP16" t="b">
-        <v>1</v>
-      </c>
-      <c r="CQ16" t="b">
-        <v>0</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>40</v>
-      </c>
-      <c r="CS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="CU16" t="n">
-        <v>24</v>
-      </c>
-      <c r="CV16" t="n">
-        <v>-5</v>
-      </c>
-      <c r="CW16" t="inlineStr">
-        <is>
-          <t>🧠 Sniper Bayes 24% — LOW</t>
-        </is>
-      </c>
-      <c r="CX16" t="n">
-        <v>39</v>
-      </c>
-      <c r="CY16" t="n">
-        <v>201.33</v>
-      </c>
-      <c r="CZ16" t="b">
-        <v>0</v>
-      </c>
-      <c r="DA16" t="b">
-        <v>0</v>
-      </c>
-      <c r="DB16" t="n">
-        <v>190.89</v>
-      </c>
-      <c r="DC16" t="n">
-        <v>190.89</v>
-      </c>
-      <c r="DD16" t="n">
-        <v>237.71</v>
-      </c>
-      <c r="DE16" t="n">
-        <v>292.56</v>
-      </c>
-      <c r="DF16" t="n">
-        <v>365.7</v>
-      </c>
-      <c r="DG16" t="inlineStr">
-        <is>
-          <t>Sell 30% | Move stop to T1 ₹182.85</t>
-        </is>
-      </c>
-      <c r="DH16" t="inlineStr">
-        <is>
-          <t>Sell 30% | Trail 2.5×ATR</t>
-        </is>
-      </c>
-      <c r="DI16" t="inlineStr">
-        <is>
-          <t>Sell 40% | Trail rest aggressively</t>
-        </is>
-      </c>
-      <c r="DJ16" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="DK16" t="inlineStr">
-        <is>
-          <t>👁️ WATCHING — score 39/100 · +9.5% vs T1</t>
-        </is>
-      </c>
-      <c r="DL16" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="DM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN16" t="inlineStr"/>
-      <c r="DO16" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP16" t="b">
-        <v>0</v>
-      </c>
-      <c r="DQ16" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR16" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS16" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="inlineStr">
-        <is>
-          <t>— (below min)</t>
-        </is>
-      </c>
-      <c r="DW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>18.48</v>
-      </c>
-      <c r="DY16" t="inlineStr">
-        <is>
-          <t>CHOP</t>
-        </is>
-      </c>
-      <c r="DZ16" t="b">
-        <v>1</v>
-      </c>
-      <c r="EA16" t="n">
-        <v>19.28</v>
-      </c>
-      <c r="EB16" t="n">
-        <v>-1.83</v>
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -9983,7 +8171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10012,25 +8200,35 @@
           <t>detail</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>_fallback_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>14374</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>18873</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>↔ MIXED</t>
+          <t>🟢 FII+DII BUYING</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FII ₹+0 Cr | DII ₹+0 Cr [SHEETS Tab 2]</t>
+          <t>FII ₹+14,374 Cr | DII ₹+18,873 Cr [SHEETS Tab 2]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>⚠️ NSE+Sheets unavailable — yfinance fallback</t>
         </is>
       </c>
     </row>
